--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\02-PLC项目\江西沸腾炉烧嘴程序改造\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92ED4EC-3085-4308-A749-E6A3BFDF4EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90E1158-B327-471A-BCAB-B0FC4156D810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="EF03" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4579" uniqueCount="1729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4588" uniqueCount="1737">
   <si>
     <t>I</t>
   </si>
@@ -5576,6 +5576,33 @@
   <si>
     <t>报警蜂鸣器</t>
     <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>温度错误，DCS传送温度数据有误</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Temp_Error_FLG</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>VW_Sys_Status</t>
+  </si>
+  <si>
+    <t>VW814</t>
+  </si>
+  <si>
+    <t>系统状态，1.检漏中2.调节阀检测中3.停机4.启动中5.吹扫中6.高压放电打火7.小火运行8.大火运行9.故障报警</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>VW_Sys_Status_Time</t>
+  </si>
+  <si>
+    <t>VW816</t>
+  </si>
+  <si>
+    <t>系统状态时间</t>
   </si>
 </sst>
 </file>
@@ -5915,7 +5942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6219,12 +6246,231 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 4 2" xfId="1" xr:uid="{C97CC49E-8548-40A7-B373-8E3F8F01BD97}"/>
   </cellStyles>
   <dxfs count="87">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6492,216 +6738,6 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -8342,112 +8378,34 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G235" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
-  <autoFilter ref="A1:G235" xr:uid="{B3E6F695-5A5D-43F2-A4A9-C2D31569F3E9}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="R_Air_DiffAlow_SET"/>
-        <filter val="R_Air_Level_Ignite_SET"/>
-        <filter val="R_Air_Level_Stop_SET"/>
-        <filter val="R_Air_Level1_SET"/>
-        <filter val="R_Air_Level10_SET"/>
-        <filter val="R_Air_Level11_SET"/>
-        <filter val="R_Air_Level12_SET"/>
-        <filter val="R_Air_Level13_SET"/>
-        <filter val="R_Air_Level14_SET"/>
-        <filter val="R_Air_Level15_SET"/>
-        <filter val="R_Air_Level16_SET"/>
-        <filter val="R_Air_Level17_SET"/>
-        <filter val="R_Air_Level18_SET"/>
-        <filter val="R_Air_Level2_SET"/>
-        <filter val="R_Air_Level3_SET"/>
-        <filter val="R_Air_Level4_SET"/>
-        <filter val="R_Air_Level5_SET"/>
-        <filter val="R_Air_Level6_SET"/>
-        <filter val="R_Air_Level7_SET"/>
-        <filter val="R_Air_Level8_SET"/>
-        <filter val="R_Air_Level9_SET"/>
-        <filter val="R_Gas_DiffAlow_SET"/>
-        <filter val="R_Gas_Level_Ignite_SET"/>
-        <filter val="R_Gas_Level_Stop_SET"/>
-        <filter val="R_Gas_Level1_SET"/>
-        <filter val="R_Gas_Level10_SET"/>
-        <filter val="R_Gas_Level11_SET"/>
-        <filter val="R_Gas_Level12_SET"/>
-        <filter val="R_Gas_Level13_SET"/>
-        <filter val="R_Gas_Level14_SET"/>
-        <filter val="R_Gas_Level15_SET"/>
-        <filter val="R_Gas_Level16_SET"/>
-        <filter val="R_Gas_Level17_SET"/>
-        <filter val="R_Gas_Level18_SET"/>
-        <filter val="R_Gas_Level2_SET"/>
-        <filter val="R_Gas_Level3_SET"/>
-        <filter val="R_Gas_Level4_SET"/>
-        <filter val="R_Gas_Level5_SET"/>
-        <filter val="R_Gas_Level6_SET"/>
-        <filter val="R_Gas_Level7_SET"/>
-        <filter val="R_Gas_Level8_SET"/>
-        <filter val="R_Gas_Level9_SET"/>
-        <filter val="R_Level_Total_SET"/>
-        <filter val="R_Over_Temp_Stop_SET"/>
-        <filter val="R_PID_D_SET"/>
-        <filter val="R_PID_I_SET"/>
-        <filter val="R_PID_P_SET"/>
-        <filter val="R_PID_Ts_SET"/>
-        <filter val="R_Purge_Valve_Air_SET"/>
-        <filter val="R_Remote_Temp_SET"/>
-        <filter val="R_Stage1_Temp_SET"/>
-        <filter val="R_Stage2_Temp_SET"/>
-        <filter val="R_Stage3_Temp_SET"/>
-        <filter val="R_Stage4_Temp_SET"/>
-        <filter val="R_Stage5_Temp_SET"/>
-        <filter val="R_Stage6_Temp_SET"/>
-        <filter val="R_Temp_Lower_Limit_SET"/>
-        <filter val="R_Temp_Upper_Limit_SET"/>
-        <filter val="W_Flame_Build_Time_SET"/>
-        <filter val="W_Flame_Loss_Time_SET"/>
-        <filter val="W_Ignite_Delay_SET"/>
-        <filter val="W_Ignite_Spark_Time_SET"/>
-        <filter val="W_PreFlame_Time_SET"/>
-        <filter val="W_Purge_Time_SET"/>
-        <filter val="W_Stage1_Temp_Time_SET"/>
-        <filter val="W_Stage2_Temp_Time_SET"/>
-        <filter val="W_Stage3_Temp_Time_SET"/>
-        <filter val="W_Stage4_Temp_Time_SET"/>
-        <filter val="W_Stage5_Temp_Time_SET"/>
-        <filter val="W_Stage6_Temp_Time_SET"/>
-        <filter val="W_Valve_Ignite_Time_SET"/>
-        <filter val="W_ValveCut_Delay_SET"/>
-        <filter val="W_ValveDetect_Time_SET"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G236" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8">
+  <autoFilter ref="A1:G236" xr:uid="{B3E6F695-5A5D-43F2-A4A9-C2D31569F3E9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G223">
     <sortCondition ref="F1:F223"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:F21" xr:uid="{E517E8B6-ADC0-4F95-930E-5AF82CCFF0B4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27586,7 +27544,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67ABFE6-0E3D-41E3-A8E9-BDC84F153A78}">
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G236"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8" style="3" customWidth="1"/>
@@ -27595,7 +27553,7 @@
     <col min="4" max="4" width="9.875" style="11" customWidth="1"/>
     <col min="5" max="5" width="26.125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="73.75" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="109.25" style="54" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -27622,7 +27580,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="2" spans="1:7" ht="24.95" customHeight="1">
       <c r="A2" s="7" t="str">
         <f t="array" ref="A2">LEFT(F2, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F2 &amp; "0123456789")) - 1)</f>
         <v>AIW</v>
@@ -27646,7 +27604,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="3" spans="1:7" ht="24.95" customHeight="1">
       <c r="A3" s="7" t="str">
         <f t="array" ref="A3">LEFT(F3, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F3 &amp; "0123456789")) - 1)</f>
         <v>AIW</v>
@@ -27670,7 +27628,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="7" t="str">
         <f t="array" ref="A4">LEFT(F4, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F4 &amp; "0123456789")) - 1)</f>
         <v>AQW</v>
@@ -27694,7 +27652,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="5" spans="1:7" ht="24.95" customHeight="1">
       <c r="A5" s="7" t="str">
         <f t="array" ref="A5">LEFT(F5, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F5 &amp; "0123456789")) - 1)</f>
         <v>AQW</v>
@@ -27718,7 +27676,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="6" spans="1:7" ht="24.95" customHeight="1">
       <c r="A6" s="7" t="str">
         <f t="array" ref="A6">LEFT(F6, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F6 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27742,7 +27700,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="7" spans="1:7" ht="24.95" customHeight="1">
       <c r="A7" s="7" t="str">
         <f t="array" ref="A7">LEFT(F7, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F7 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27766,7 +27724,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="8" spans="1:7" ht="24.95" customHeight="1">
       <c r="A8" s="7" t="str">
         <f t="array" ref="A8">LEFT(F8, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F8 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27790,7 +27748,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="9" spans="1:7" ht="24.95" customHeight="1">
       <c r="A9" s="7" t="str">
         <f t="array" ref="A9">LEFT(F9, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F9 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27814,7 +27772,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="10" spans="1:7" ht="24.95" customHeight="1">
       <c r="A10" s="7" t="str">
         <f t="array" ref="A10">LEFT(F10, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F10 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27838,7 +27796,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="11" spans="1:7" ht="24.95" customHeight="1">
       <c r="A11" s="7" t="str">
         <f t="array" ref="A11">LEFT(F11, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F11 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27862,7 +27820,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="12" spans="1:7" ht="24.95" customHeight="1">
       <c r="A12" s="7" t="str">
         <f t="array" ref="A12">LEFT(F12, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F12 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27886,7 +27844,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="13" spans="1:7" ht="24.95" customHeight="1">
       <c r="A13" s="7" t="str">
         <f t="array" ref="A13">LEFT(F13, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F13 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27910,7 +27868,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="14" spans="1:7" ht="24.95" customHeight="1">
       <c r="A14" s="7" t="str">
         <f t="array" ref="A14">LEFT(F14, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F14 &amp; "0123456789")) - 1)</f>
         <v>C</v>
@@ -27934,7 +27892,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="15" spans="1:7" ht="24.95" customHeight="1">
       <c r="A15" s="7" t="str">
         <f t="array" ref="A15">LEFT(F15, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F15 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -27958,7 +27916,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="16" spans="1:7" ht="24.95" customHeight="1">
       <c r="A16" s="7" t="str">
         <f t="array" ref="A16">LEFT(F16, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F16 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -27982,7 +27940,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="17" spans="1:7" ht="24.95" customHeight="1">
       <c r="A17" s="7" t="str">
         <f t="array" ref="A17">LEFT(F17, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F17 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28006,7 +27964,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="18" spans="1:7" ht="24.95" customHeight="1">
       <c r="A18" s="7" t="str">
         <f t="array" ref="A18">LEFT(F18, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F18 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28030,7 +27988,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="19" spans="1:7" ht="24.95" customHeight="1">
       <c r="A19" s="7" t="str">
         <f t="array" ref="A19">LEFT(F19, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F19 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28054,7 +28012,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="20" spans="1:7" ht="24.95" customHeight="1">
       <c r="A20" s="7" t="str">
         <f t="array" ref="A20">LEFT(F20, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F20 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28078,7 +28036,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="21" spans="1:7" ht="24.95" customHeight="1">
       <c r="A21" s="7" t="str">
         <f t="array" ref="A21">LEFT(F21, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F21 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28102,7 +28060,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="22" spans="1:7" ht="24.95" customHeight="1">
       <c r="A22" s="7" t="str">
         <f t="array" ref="A22">LEFT(F22, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F22 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28126,7 +28084,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="23" spans="1:7" ht="24.95" customHeight="1">
       <c r="A23" s="7" t="str">
         <f t="array" ref="A23">LEFT(F23, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F23 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28150,7 +28108,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="24" spans="1:7" ht="24.95" customHeight="1">
       <c r="A24" s="7" t="str">
         <f t="array" ref="A24">LEFT(F24, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F24 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28174,7 +28132,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="25" spans="1:7" ht="24.95" customHeight="1">
       <c r="A25" s="7" t="str">
         <f t="array" ref="A25">LEFT(F25, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F25 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28198,7 +28156,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="26" spans="1:7" ht="24.95" customHeight="1">
       <c r="A26" s="7" t="str">
         <f t="array" ref="A26">LEFT(F26, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F26 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28222,7 +28180,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="27" spans="1:7" ht="24.95" customHeight="1">
       <c r="A27" s="7" t="str">
         <f t="array" ref="A27">LEFT(F27, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F27 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28246,7 +28204,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="28" spans="1:7" ht="24.95" customHeight="1">
       <c r="A28" s="7" t="str">
         <f t="array" ref="A28">LEFT(F28, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F28 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28270,7 +28228,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="29" spans="1:7" ht="24.95" customHeight="1">
       <c r="A29" s="7" t="str">
         <f t="array" ref="A29">LEFT(F29, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F29 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28294,7 +28252,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="30" spans="1:7" ht="24.95" customHeight="1">
       <c r="A30" s="7" t="str">
         <f t="array" ref="A30">LEFT(F30, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F30 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28318,7 +28276,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="31" spans="1:7" ht="24.95" customHeight="1">
       <c r="A31" s="7" t="str">
         <f t="array" ref="A31">LEFT(F31, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F31 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28342,7 +28300,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="32" spans="1:7" ht="24.95" customHeight="1">
       <c r="A32" s="7" t="str">
         <f t="array" ref="A32">LEFT(F32, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F32 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28366,7 +28324,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="33" spans="1:7" ht="24.95" customHeight="1">
       <c r="A33" s="7" t="str">
         <f t="array" ref="A33">LEFT(F33, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F33 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28390,7 +28348,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="34" spans="1:7" ht="24.95" customHeight="1">
       <c r="A34" s="7" t="str">
         <f t="array" ref="A34">LEFT(F34, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F34 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28414,7 +28372,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="35" spans="1:7" ht="24.95" customHeight="1">
       <c r="A35" s="7" t="str">
         <f t="array" ref="A35">LEFT(F35, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F35 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28438,7 +28396,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="36" spans="1:7" ht="24.95" customHeight="1">
       <c r="A36" s="7" t="str">
         <f t="array" ref="A36">LEFT(F36, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F36 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28462,7 +28420,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="37" spans="1:7" ht="24.95" customHeight="1">
       <c r="A37" s="7" t="str">
         <f t="array" ref="A37">LEFT(F37, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F37 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28486,7 +28444,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="38" spans="1:7" ht="24.95" customHeight="1">
       <c r="A38" s="7" t="str">
         <f t="array" ref="A38">LEFT(F38, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F38 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28510,7 +28468,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="39" spans="1:7" ht="24.95" customHeight="1">
       <c r="A39" s="7" t="str">
         <f t="array" ref="A39">LEFT(F39, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F39 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28534,7 +28492,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="40" spans="1:7" ht="24.95" customHeight="1">
       <c r="A40" s="7" t="str">
         <f t="array" ref="A40">LEFT(F40, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F40 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28558,7 +28516,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="41" spans="1:7" ht="24.95" customHeight="1">
       <c r="A41" s="7" t="str">
         <f t="array" ref="A41">LEFT(F41, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F41 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28582,7 +28540,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="42" spans="1:7" ht="24.95" customHeight="1">
       <c r="A42" s="7" t="str">
         <f t="array" ref="A42">LEFT(F42, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F42 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28606,7 +28564,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="43" spans="1:7" ht="24.95" customHeight="1">
       <c r="A43" s="7" t="str">
         <f t="array" ref="A43">LEFT(F43, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F43 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28630,7 +28588,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="44" spans="1:7" ht="24.95" customHeight="1">
       <c r="A44" s="7" t="str">
         <f t="array" ref="A44">LEFT(F44, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F44 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28654,7 +28612,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="45" spans="1:7" ht="24.95" customHeight="1">
       <c r="A45" s="7" t="str">
         <f t="array" ref="A45">LEFT(F45, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F45 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28678,7 +28636,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="46" spans="1:7" ht="24.95" customHeight="1">
       <c r="A46" s="7" t="str">
         <f t="array" ref="A46">LEFT(F46, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F46 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28702,7 +28660,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="47" spans="1:7" ht="24.95" customHeight="1">
       <c r="A47" s="7" t="str">
         <f t="array" ref="A47">LEFT(F47, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F47 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28726,7 +28684,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="48" spans="1:7" ht="24.95" customHeight="1">
       <c r="A48" s="7" t="str">
         <f t="array" ref="A48">LEFT(F48, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F48 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28750,7 +28708,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="49" spans="1:7" ht="24.95" customHeight="1">
       <c r="A49" s="7" t="str">
         <f t="array" ref="A49">LEFT(F49, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F49 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28774,7 +28732,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="50" spans="1:7" ht="24.95" customHeight="1">
       <c r="A50" s="7" t="str">
         <f t="array" ref="A50">LEFT(F50, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F50 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28798,7 +28756,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="51" spans="1:7" ht="24.95" customHeight="1">
       <c r="A51" s="7" t="str">
         <f t="array" ref="A51">LEFT(F51, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F51 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28822,7 +28780,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="52" spans="1:7" ht="24.95" customHeight="1">
       <c r="A52" s="7" t="str">
         <f t="array" ref="A52">LEFT(F52, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F52 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28846,7 +28804,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="53" spans="1:7" ht="24.95" customHeight="1">
       <c r="A53" s="7" t="str">
         <f t="array" ref="A53">LEFT(F53, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F53 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28870,7 +28828,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="54" spans="1:7" ht="24.95" customHeight="1">
       <c r="A54" s="7" t="str">
         <f t="array" ref="A54">LEFT(F54, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F54 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28894,7 +28852,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="55" spans="1:7" ht="24.95" customHeight="1">
       <c r="A55" s="7" t="str">
         <f t="array" ref="A55">LEFT(F55, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F55 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28918,7 +28876,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="56" spans="1:7" ht="24.95" customHeight="1">
       <c r="A56" s="7" t="str">
         <f t="array" ref="A56">LEFT(F56, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F56 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28942,7 +28900,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="57" spans="1:7" ht="24.95" customHeight="1">
       <c r="A57" s="7" t="str">
         <f t="array" ref="A57">LEFT(F57, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F57 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28966,7 +28924,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="58" spans="1:7" ht="24.95" customHeight="1">
       <c r="A58" s="7" t="str">
         <f t="array" ref="A58">LEFT(F58, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F58 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -28990,7 +28948,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="59" spans="1:7" ht="24.95" customHeight="1">
       <c r="A59" s="7" t="str">
         <f t="array" ref="A59">LEFT(F59, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F59 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29014,7 +28972,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="60" spans="1:7" ht="24.95" customHeight="1">
       <c r="A60" s="7" t="str">
         <f t="array" ref="A60">LEFT(F60, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F60 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29038,7 +28996,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="61" spans="1:7" ht="24.95" customHeight="1">
       <c r="A61" s="7" t="str">
         <f t="array" ref="A61">LEFT(F61, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F61 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29062,7 +29020,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="62" spans="1:7" ht="24.95" customHeight="1">
       <c r="A62" s="7" t="str">
         <f t="array" ref="A62">LEFT(F62, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F62 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29086,7 +29044,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="63" spans="1:7" ht="24.95" customHeight="1">
       <c r="A63" s="7" t="str">
         <f t="array" ref="A63">LEFT(F63, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F63 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29110,7 +29068,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="64" spans="1:7" ht="24.95" customHeight="1">
       <c r="A64" s="7" t="str">
         <f t="array" ref="A64">LEFT(F64, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F64 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29134,7 +29092,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="65" spans="1:7" ht="24.95" customHeight="1">
       <c r="A65" s="7" t="str">
         <f t="array" ref="A65">LEFT(F65, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F65 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29158,7 +29116,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="66" spans="1:7" ht="24.95" customHeight="1">
       <c r="A66" s="7" t="str">
         <f t="array" ref="A66">LEFT(F66, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F66 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29182,7 +29140,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="67" spans="1:7" ht="24.95" customHeight="1">
       <c r="A67" s="7" t="str">
         <f t="array" ref="A67">LEFT(F67, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F67 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29206,7 +29164,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="68" spans="1:7" ht="24.95" customHeight="1">
       <c r="A68" s="7" t="str">
         <f t="array" ref="A68">LEFT(F68, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F68 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29230,7 +29188,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="69" spans="1:7" ht="24.95" customHeight="1">
       <c r="A69" s="7" t="str">
         <f t="array" ref="A69">LEFT(F69, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F69 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29254,7 +29212,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="70" spans="1:7" ht="24.95" customHeight="1">
       <c r="A70" s="7" t="str">
         <f t="array" ref="A70">LEFT(F70, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F70 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29278,7 +29236,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="71" spans="1:7" ht="24.95" customHeight="1">
       <c r="A71" s="7" t="str">
         <f t="array" ref="A71">LEFT(F71, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F71 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29302,7 +29260,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="72" spans="1:7" ht="24.95" customHeight="1">
       <c r="A72" s="7" t="str">
         <f t="array" ref="A72">LEFT(F72, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F72 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29326,7 +29284,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="73" spans="1:7" ht="24.95" customHeight="1">
       <c r="A73" s="7" t="str">
         <f t="array" ref="A73">LEFT(F73, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F73 &amp; "0123456789")) - 1)</f>
         <v>M</v>
@@ -29350,7 +29308,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="74" spans="1:7" ht="24.95" customHeight="1">
       <c r="A74" s="7" t="str">
         <f t="array" ref="A74">LEFT(F74, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F74 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29374,7 +29332,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="75" spans="1:7" ht="24.95" customHeight="1">
       <c r="A75" s="7" t="str">
         <f t="array" ref="A75">LEFT(F75, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F75 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29398,7 +29356,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="76" spans="1:7" ht="24.95" customHeight="1">
       <c r="A76" s="7" t="str">
         <f t="array" ref="A76">LEFT(F76, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F76 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29422,7 +29380,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="77" spans="1:7" ht="24.95" customHeight="1">
       <c r="A77" s="7" t="str">
         <f t="array" ref="A77">LEFT(F77, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F77 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29446,7 +29404,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="78" spans="1:7" ht="24.95" customHeight="1">
       <c r="A78" s="7" t="str">
         <f t="array" ref="A78">LEFT(F78, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F78 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29470,7 +29428,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="79" spans="1:7" ht="24.95" customHeight="1">
       <c r="A79" s="7" t="str">
         <f t="array" ref="A79">LEFT(F79, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F79 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29494,7 +29452,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="80" spans="1:7" ht="24.95" customHeight="1">
       <c r="A80" s="7" t="str">
         <f t="array" ref="A80">LEFT(F80, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F80 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29518,7 +29476,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="81" spans="1:7" ht="24.95" customHeight="1">
       <c r="A81" s="7" t="str">
         <f t="array" ref="A81">LEFT(F81, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F81 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29542,7 +29500,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="82" spans="1:7" ht="24.95" customHeight="1">
       <c r="A82" s="7" t="str">
         <f t="array" ref="A82">LEFT(F82, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F82 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29566,7 +29524,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="83" spans="1:7" ht="24.95" customHeight="1">
       <c r="A83" s="7" t="str">
         <f t="array" ref="A83">LEFT(F83, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F83 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29590,7 +29548,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="84" spans="1:7" ht="24.95" customHeight="1">
       <c r="A84" s="7" t="str">
         <f t="array" ref="A84">LEFT(F84, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F84 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29614,7 +29572,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="85" spans="1:7" ht="24.95" customHeight="1">
       <c r="A85" s="7" t="str">
         <f t="array" ref="A85">LEFT(F85, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F85 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29638,7 +29596,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="86" spans="1:7" ht="24.95" customHeight="1">
       <c r="A86" s="7" t="str">
         <f t="array" ref="A86">LEFT(F86, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F86 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29662,7 +29620,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="87" spans="1:7" ht="24.95" customHeight="1">
       <c r="A87" s="7" t="str">
         <f t="array" ref="A87">LEFT(F87, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F87 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29686,7 +29644,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="88" spans="1:7" ht="24.95" customHeight="1">
       <c r="A88" s="7" t="str">
         <f t="array" ref="A88">LEFT(F88, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F88 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29710,7 +29668,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="89" spans="1:7" ht="24.95" customHeight="1">
       <c r="A89" s="7" t="str">
         <f t="array" ref="A89">LEFT(F89, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F89 &amp; "0123456789")) - 1)</f>
         <v>T</v>
@@ -29734,7 +29692,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="90" spans="1:7" ht="24.95" customHeight="1">
       <c r="A90" s="7" t="str">
         <f t="array" ref="A90">LEFT(F90, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F90 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29758,7 +29716,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="91" spans="1:7" ht="24.95" customHeight="1">
       <c r="A91" s="7" t="str">
         <f t="array" ref="A91">LEFT(F91, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F91 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29782,7 +29740,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="92" spans="1:7" ht="24.95" customHeight="1">
       <c r="A92" s="7" t="str">
         <f t="array" ref="A92">LEFT(F92, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F92 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29806,7 +29764,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="93" spans="1:7" ht="24.95" customHeight="1">
       <c r="A93" s="7" t="str">
         <f t="array" ref="A93">LEFT(F93, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F93 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29830,7 +29788,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="94" spans="1:7" ht="24.95" customHeight="1">
       <c r="A94" s="7" t="str">
         <f t="array" ref="A94">LEFT(F94, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F94 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29854,7 +29812,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="95" spans="1:7" ht="24.95" customHeight="1">
       <c r="A95" s="7" t="str">
         <f t="array" ref="A95">LEFT(F95, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F95 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29878,7 +29836,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="96" spans="1:7" ht="24.95" customHeight="1">
       <c r="A96" s="7" t="str">
         <f t="array" ref="A96">LEFT(F96, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F96 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29902,7 +29860,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="97" spans="1:7" ht="24.95" customHeight="1">
       <c r="A97" s="7" t="str">
         <f t="array" ref="A97">LEFT(F97, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F97 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29926,7 +29884,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="98" spans="1:7" ht="24.95" customHeight="1">
       <c r="A98" s="7" t="str">
         <f t="array" ref="A98">LEFT(F98, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F98 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29950,7 +29908,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="99" spans="1:7" ht="24.95" customHeight="1">
       <c r="A99" s="7" t="str">
         <f t="array" ref="A99">LEFT(F99, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F99 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29974,7 +29932,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="100" spans="1:7" ht="24.95" customHeight="1">
       <c r="A100" s="7" t="str">
         <f t="array" ref="A100">LEFT(F100, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F100 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -29998,7 +29956,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="101" spans="1:7" ht="24.95" customHeight="1">
       <c r="A101" s="7" t="str">
         <f t="array" ref="A101">LEFT(F101, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F101 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30022,7 +29980,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="102" spans="1:7" ht="24.95" customHeight="1">
       <c r="A102" s="7" t="str">
         <f t="array" ref="A102">LEFT(F102, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F102 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30046,7 +30004,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="103" spans="1:7" ht="24.95" customHeight="1">
       <c r="A103" s="7" t="str">
         <f t="array" ref="A103">LEFT(F103, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F103 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30070,7 +30028,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="104" spans="1:7" ht="24.95" customHeight="1">
       <c r="A104" s="7" t="str">
         <f t="array" ref="A104">LEFT(F104, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F104 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30094,7 +30052,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="105" spans="1:7" ht="24.95" customHeight="1">
       <c r="A105" s="7" t="str">
         <f t="array" ref="A105">LEFT(F105, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F105 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30118,7 +30076,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="106" spans="1:7" ht="24.95" customHeight="1">
       <c r="A106" s="7" t="str">
         <f t="array" ref="A106">LEFT(F106, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F106 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30142,7 +30100,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="107" spans="1:7" ht="24.95" customHeight="1">
       <c r="A107" s="7" t="str">
         <f t="array" ref="A107">LEFT(F107, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F107 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30166,7 +30124,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="108" spans="1:7" ht="24.95" customHeight="1">
       <c r="A108" s="7" t="str">
         <f t="array" ref="A108">LEFT(F108, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F108 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30190,7 +30148,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="109" spans="1:7" ht="24.95" customHeight="1">
       <c r="A109" s="7" t="str">
         <f t="array" ref="A109">LEFT(F109, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F109 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30214,7 +30172,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="110" spans="1:7" ht="24.95" customHeight="1">
       <c r="A110" s="7" t="str">
         <f t="array" ref="A110">LEFT(F110, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F110 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30238,7 +30196,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="111" spans="1:7" ht="24.95" customHeight="1">
       <c r="A111" s="7" t="str">
         <f t="array" ref="A111">LEFT(F111, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F111 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30262,7 +30220,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="112" spans="1:7" ht="24.95" customHeight="1">
       <c r="A112" s="7" t="str">
         <f t="array" ref="A112">LEFT(F112, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F112 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30286,7 +30244,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="113" spans="1:7" ht="24.95" customHeight="1">
       <c r="A113" s="7" t="str">
         <f t="array" ref="A113">LEFT(F113, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F113 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30310,7 +30268,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="114" spans="1:7" ht="24.95" customHeight="1">
       <c r="A114" s="7" t="str">
         <f t="array" ref="A114">LEFT(F114, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F114 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30334,7 +30292,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="115" spans="1:7" ht="24.95" customHeight="1">
       <c r="A115" s="7" t="str">
         <f t="array" ref="A115">LEFT(F115, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F115 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30358,7 +30316,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="116" spans="1:7" ht="24.95" customHeight="1">
       <c r="A116" s="7" t="str">
         <f t="array" ref="A116">LEFT(F116, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F116 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30382,7 +30340,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="117" spans="1:7" ht="24.95" customHeight="1">
       <c r="A117" s="7" t="str">
         <f t="array" ref="A117">LEFT(F117, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F117 &amp; "0123456789")) - 1)</f>
         <v>V</v>
@@ -30406,7 +30364,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="118" spans="1:7" ht="24.95" customHeight="1">
       <c r="A118" s="7" t="str">
         <f t="array" ref="A118">LEFT(F118, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F118 &amp; "0123456789")) - 1)</f>
         <v>VB</v>
@@ -30430,7 +30388,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="119" spans="1:7" ht="24.95" customHeight="1">
       <c r="A119" s="7" t="str">
         <f t="array" ref="A119">LEFT(F119, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F119 &amp; "0123456789")) - 1)</f>
         <v>VB</v>
@@ -30454,7 +30412,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="120" spans="1:7" ht="24.95" customHeight="1">
       <c r="A120" s="7" t="str">
         <f t="array" ref="A120">LEFT(F120, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F120 &amp; "0123456789")) - 1)</f>
         <v>VB</v>
@@ -30478,7 +30436,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="121" spans="1:7" ht="24.95" customHeight="1">
       <c r="A121" s="7" t="str">
         <f t="array" ref="A121">LEFT(F121, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F121 &amp; "0123456789")) - 1)</f>
         <v>VB</v>
@@ -30502,7 +30460,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="122" spans="1:7" ht="24.95" customHeight="1">
       <c r="A122" s="7" t="str">
         <f t="array" ref="A122">LEFT(F122, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F122 &amp; "0123456789")) - 1)</f>
         <v>VB</v>
@@ -30526,7 +30484,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="123" spans="1:7" ht="24.95" customHeight="1">
       <c r="A123" s="7" t="str">
         <f t="array" ref="A123">LEFT(F123, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F123 &amp; "0123456789")) - 1)</f>
         <v>VB</v>
@@ -30550,7 +30508,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="124" spans="1:7" ht="24.95" customHeight="1">
       <c r="A124" s="7" t="str">
         <f t="array" ref="A124">LEFT(F124, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F124 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30576,7 +30534,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="125" spans="1:7" ht="24.95" customHeight="1">
       <c r="A125" s="7" t="str">
         <f t="array" ref="A125">LEFT(F125, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F125 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30600,7 +30558,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="126" spans="1:7" ht="24.95" customHeight="1">
       <c r="A126" s="7" t="str">
         <f t="array" ref="A126">LEFT(F126, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F126 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30626,7 +30584,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="127" spans="1:7" ht="24.95" customHeight="1">
       <c r="A127" s="7" t="str">
         <f t="array" ref="A127">LEFT(F127, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F127 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30652,7 +30610,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="128" spans="1:7" ht="24.95" customHeight="1">
       <c r="A128" s="7" t="str">
         <f t="array" ref="A128">LEFT(F128, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F128 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30678,7 +30636,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="129" spans="1:7" ht="24.95" customHeight="1">
       <c r="A129" s="7" t="str">
         <f t="array" ref="A129">LEFT(F129, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F129 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30704,7 +30662,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="130" spans="1:7" ht="24.95" customHeight="1">
       <c r="A130" s="7" t="str">
         <f t="array" ref="A130">LEFT(F130, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F130 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30730,7 +30688,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="131" spans="1:7" ht="24.95" customHeight="1">
       <c r="A131" s="7" t="str">
         <f t="array" ref="A131">LEFT(F131, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F131 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30756,7 +30714,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="132" spans="1:7" ht="24.95" customHeight="1">
       <c r="A132" s="7" t="str">
         <f t="array" ref="A132">LEFT(F132, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F132 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30782,7 +30740,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="133" spans="1:7" ht="24.95" customHeight="1">
       <c r="A133" s="7" t="str">
         <f t="array" ref="A133">LEFT(F133, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F133 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30808,7 +30766,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="134" spans="1:7" ht="24.95" customHeight="1">
       <c r="A134" s="7" t="str">
         <f t="array" ref="A134">LEFT(F134, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F134 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30834,7 +30792,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="135" spans="1:7" ht="24.95" customHeight="1">
       <c r="A135" s="7" t="str">
         <f t="array" ref="A135">LEFT(F135, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F135 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30860,7 +30818,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="136" spans="1:7" ht="24.95" customHeight="1">
       <c r="A136" s="7" t="str">
         <f t="array" ref="A136">LEFT(F136, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F136 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30886,7 +30844,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="137" spans="1:7" ht="24.95" customHeight="1">
       <c r="A137" s="7" t="str">
         <f t="array" ref="A137">LEFT(F137, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F137 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30910,7 +30868,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="138" spans="1:7" ht="24.95" customHeight="1">
       <c r="A138" s="7" t="str">
         <f t="array" ref="A138">LEFT(F138, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F138 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30936,7 +30894,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="139" spans="1:7" ht="24.95" customHeight="1">
       <c r="A139" s="7" t="str">
         <f t="array" ref="A139">LEFT(F139, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F139 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30962,7 +30920,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="140" spans="1:7" ht="24.95" customHeight="1">
       <c r="A140" s="7" t="str">
         <f t="array" ref="A140">LEFT(F140, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F140 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -30988,7 +30946,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="141" spans="1:7" ht="24.95" customHeight="1">
       <c r="A141" s="7" t="str">
         <f t="array" ref="A141">LEFT(F141, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F141 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -31014,7 +30972,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="142" spans="1:7" ht="24.95" customHeight="1">
       <c r="A142" s="7" t="str">
         <f t="array" ref="A142">LEFT(F142, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F142 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32365,7 +32323,7 @@
         <v>348</v>
       </c>
       <c r="D194" s="9">
-        <f t="shared" ref="D194:D233" si="7">LEN(E194)</f>
+        <f t="shared" ref="D194:D235" si="7">LEN(E194)</f>
         <v>17</v>
       </c>
       <c r="E194" s="1" t="s">
@@ -32502,7 +32460,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="200" spans="1:7" ht="24.95" customHeight="1">
       <c r="A200" s="7" t="str">
         <f t="array" ref="A200">LEFT(F200, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F200 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32526,7 +32484,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="201" spans="1:7" ht="24.95" customHeight="1">
       <c r="A201" s="7" t="str">
         <f t="array" ref="A201">LEFT(F201, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F201 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32550,7 +32508,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="202" spans="1:7" ht="24.95" customHeight="1">
       <c r="A202" s="7" t="str">
         <f t="array" ref="A202">LEFT(F202, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F202 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32574,7 +32532,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="203" spans="1:7" ht="24.95" customHeight="1">
       <c r="A203" s="7" t="str">
         <f t="array" ref="A203">LEFT(F203, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F203 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32598,7 +32556,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="204" spans="1:7" ht="24.95" customHeight="1">
       <c r="A204" s="7" t="str">
         <f t="array" ref="A204">LEFT(F204, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F204 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32622,7 +32580,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="205" spans="1:7" ht="24.95" customHeight="1">
       <c r="A205" s="7" t="str">
         <f t="array" ref="A205">LEFT(F205, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F205 &amp; "0123456789")) - 1)</f>
         <v>VD</v>
@@ -32670,7 +32628,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="207" spans="1:7" ht="24.95" customHeight="1">
       <c r="A207" s="7" t="str">
         <f t="array" ref="A207">LEFT(F207, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F207 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32694,7 +32652,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="208" spans="1:7" ht="24.95" customHeight="1">
       <c r="A208" s="7" t="str">
         <f t="array" ref="A208">LEFT(F208, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F208 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32718,7 +32676,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="209" spans="1:7" ht="24.95" customHeight="1">
       <c r="A209" s="7" t="str">
         <f t="array" ref="A209">LEFT(F209, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F209 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32742,7 +32700,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="210" spans="1:7" ht="24.95" customHeight="1">
       <c r="A210" s="7" t="str">
         <f t="array" ref="A210">LEFT(F210, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F210 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32766,7 +32724,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="211" spans="1:7" ht="24.95" customHeight="1">
       <c r="A211" s="7" t="str">
         <f t="array" ref="A211">LEFT(F211, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F211 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32790,7 +32748,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="212" spans="1:7" ht="24.95" customHeight="1">
       <c r="A212" s="7" t="str">
         <f t="array" ref="A212">LEFT(F212, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F212 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32814,7 +32772,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="213" spans="1:7" ht="24.95" customHeight="1">
       <c r="A213" s="7" t="str">
         <f t="array" ref="A213">LEFT(F213, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F213 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32838,7 +32796,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="214" spans="1:7" ht="24.95" customHeight="1">
       <c r="A214" s="7" t="str">
         <f t="array" ref="A214">LEFT(F214, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F214 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32862,7 +32820,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="215" spans="1:7" ht="24.95" customHeight="1">
       <c r="A215" s="7" t="str">
         <f t="array" ref="A215">LEFT(F215, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F215 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -32886,7 +32844,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="216" spans="1:7" ht="24.95" customHeight="1">
       <c r="A216" s="7" t="str">
         <f t="array" ref="A216">LEFT(F216, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F216 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -33084,7 +33042,7 @@
         <v>VW</v>
       </c>
       <c r="B224" s="57">
-        <f t="shared" ref="B224:B233" si="8">VALUE(RIGHT(F224,LEN(F224)-LEN(A224)))</f>
+        <f t="shared" ref="B224:B235" si="8">VALUE(RIGHT(F224,LEN(F224)-LEN(A224)))</f>
         <v>556</v>
       </c>
       <c r="C224" s="57"/>
@@ -33270,7 +33228,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="232" spans="1:7" ht="24.95" customHeight="1">
       <c r="A232" s="94" t="str">
         <f t="array" ref="A232">LEFT(F232, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F232 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -33294,7 +33252,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="24.95" hidden="1" customHeight="1">
+    <row r="233" spans="1:7" ht="24.95" customHeight="1">
       <c r="A233" s="94" t="str">
         <f t="array" ref="A233">LEFT(F233, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F233 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
@@ -33318,23 +33276,77 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="24.95" hidden="1" customHeight="1">
-      <c r="A234" s="7"/>
-      <c r="B234" s="9"/>
+    <row r="234" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A234" s="94" t="str">
+        <f t="array" ref="A234">LEFT(F234, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F234 &amp; "0123456789")) - 1)</f>
+        <v>M</v>
+      </c>
+      <c r="B234" s="57">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
       <c r="C234" s="9"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="1"/>
-      <c r="F234" s="10"/>
-      <c r="G234" s="53"/>
-    </row>
-    <row r="235" spans="1:7" ht="24.95" hidden="1" customHeight="1">
-      <c r="A235" s="7"/>
-      <c r="B235" s="9"/>
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="1"/>
-      <c r="F235" s="10"/>
-      <c r="G235" s="53"/>
+      <c r="D234" s="57">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="E234" s="102" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="G234" s="101" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A235" s="94" t="str">
+        <f t="array" ref="A235">LEFT(F235, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F235 &amp; "0123456789")) - 1)</f>
+        <v>VW</v>
+      </c>
+      <c r="B235" s="57">
+        <f t="shared" si="8"/>
+        <v>814</v>
+      </c>
+      <c r="C235" s="57"/>
+      <c r="D235" s="57">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="E235" s="25" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F235" s="57" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G235" s="103" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A236" s="94" t="str">
+        <f t="array" ref="A236">LEFT(F236, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, F236 &amp; "0123456789")) - 1)</f>
+        <v>VW</v>
+      </c>
+      <c r="B236" s="57">
+        <f t="shared" ref="B236" si="9">VALUE(RIGHT(F236,LEN(F236)-LEN(A236)))</f>
+        <v>816</v>
+      </c>
+      <c r="C236" s="57"/>
+      <c r="D236" s="57">
+        <f t="shared" ref="D236" si="10">LEN(E236)</f>
+        <v>18</v>
+      </c>
+      <c r="E236" s="25" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F236" s="57" t="s">
+        <v>1735</v>
+      </c>
+      <c r="G236" s="58" t="s">
+        <v>1736</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>

--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\codes\04-electricity\01-plc\江铜\burnerControler_JXT\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B349EC95-C1BD-4C41-B3B9-CCCDA796619F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ABDC59-709F-4F66-A4EF-4DB7F8450ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="EF03" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="14415" yWindow="990" windowWidth="13560" windowHeight="13725" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
   </bookViews>
   <sheets>
     <sheet name="命名规范" sheetId="8" r:id="rId1"/>

--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -1,58 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\codes\04-electricity\01-plc\江铜\burnerControler_JXT\burnerController_JXXY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\02-PLC项目\江西沸腾炉烧嘴程序改造\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ABDC59-709F-4F66-A4EF-4DB7F8450ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookPassword="EF03" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D263828-DFB1-40EF-B1E0-02B05C273EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="622" activeTab="1" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
   </bookViews>
   <sheets>
     <sheet name="命名规范" sheetId="8" r:id="rId1"/>
-    <sheet name="端子1" sheetId="1" r:id="rId2"/>
-    <sheet name="符号表" sheetId="7" r:id="rId3"/>
-    <sheet name="通讯" sheetId="5" r:id="rId4"/>
-    <sheet name="符号模板" sheetId="9" r:id="rId5"/>
-    <sheet name="1英文命名" sheetId="11" r:id="rId6"/>
-    <sheet name="2命名后改地址" sheetId="12" r:id="rId7"/>
-    <sheet name="3符号地址校验" sheetId="13" r:id="rId8"/>
-    <sheet name="IO分配表" sheetId="14" r:id="rId9"/>
-    <sheet name="数据项" sheetId="6" r:id="rId10"/>
+    <sheet name="测试" sheetId="15" r:id="rId2"/>
+    <sheet name="端子1" sheetId="1" r:id="rId3"/>
+    <sheet name="符号表" sheetId="7" r:id="rId4"/>
+    <sheet name="通讯" sheetId="5" r:id="rId5"/>
+    <sheet name="符号模板" sheetId="9" r:id="rId6"/>
+    <sheet name="1英文命名" sheetId="11" r:id="rId7"/>
+    <sheet name="2命名后改地址" sheetId="12" r:id="rId8"/>
+    <sheet name="3符号地址校验" sheetId="13" r:id="rId9"/>
+    <sheet name="IO分配表" sheetId="14" r:id="rId10"/>
+    <sheet name="数据项" sheetId="6" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'1英文命名'!$C$1:$E$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2命名后改地址'!$C$1:$E$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'3符号地址校验'!$E$1:$G$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">端子1!$C$1:$E$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">符号表!$C$1:$E$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'1英文命名'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2命名后改地址'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'3符号地址校验'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">端子1!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">符号表!#REF!</definedName>
-    <definedName name="VW区" localSheetId="5">'1英文命名'!#REF!</definedName>
-    <definedName name="VW区" localSheetId="6">'2命名后改地址'!#REF!</definedName>
-    <definedName name="VW区" localSheetId="7">'3符号地址校验'!#REF!</definedName>
-    <definedName name="VW区" localSheetId="2">符号表!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'1英文命名'!$C$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2命名后改地址'!$C$1:$E$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'3符号地址校验'!$E$1:$G$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">端子1!$C$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">符号表!$C$1:$E$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'1英文命名'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'2命名后改地址'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'3符号地址校验'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">端子1!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">符号表!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">测试!$1:$1</definedName>
+    <definedName name="VW区" localSheetId="6">'1英文命名'!#REF!</definedName>
+    <definedName name="VW区" localSheetId="7">'2命名后改地址'!#REF!</definedName>
+    <definedName name="VW区" localSheetId="8">'3符号地址校验'!#REF!</definedName>
+    <definedName name="VW区" localSheetId="3">符号表!#REF!</definedName>
     <definedName name="VW区">端子1!#REF!</definedName>
-    <definedName name="V区" localSheetId="5">'1英文命名'!#REF!</definedName>
-    <definedName name="V区" localSheetId="6">'2命名后改地址'!#REF!</definedName>
-    <definedName name="V区" localSheetId="7">'3符号地址校验'!#REF!</definedName>
-    <definedName name="V区" localSheetId="2">符号表!#REF!</definedName>
+    <definedName name="V区" localSheetId="6">'1英文命名'!#REF!</definedName>
+    <definedName name="V区" localSheetId="7">'2命名后改地址'!#REF!</definedName>
+    <definedName name="V区" localSheetId="8">'3符号地址校验'!#REF!</definedName>
+    <definedName name="V区" localSheetId="3">符号表!#REF!</definedName>
     <definedName name="V区">端子1!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4588" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4678" uniqueCount="1792">
   <si>
     <t>I</t>
   </si>
@@ -5603,6 +5617,203 @@
 12.故障报警</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
+  <si>
+    <t>操作步骤</t>
+  </si>
+  <si>
+    <t>预期结果</t>
+  </si>
+  <si>
+    <t>实测结果</t>
+  </si>
+  <si>
+    <t>☐ 通过</t>
+  </si>
+  <si>
+    <t>异常</t>
+  </si>
+  <si>
+    <t>检漏异常报警，并且无法开机，必须再次检漏，通过后才能开机。</t>
+  </si>
+  <si>
+    <t>检测通过</t>
+  </si>
+  <si>
+    <t>不能启动</t>
+  </si>
+  <si>
+    <t>吹扫</t>
+  </si>
+  <si>
+    <t>正常吹扫</t>
+  </si>
+  <si>
+    <t>点火准备</t>
+  </si>
+  <si>
+    <t>正常进入点火</t>
+  </si>
+  <si>
+    <t>高压放电，持续【打火时长】秒时间，火焰稳定超过2秒</t>
+  </si>
+  <si>
+    <t>点火成功，转入小火运行</t>
+  </si>
+  <si>
+    <t>高压放电打火结束，没建立火焰或火焰无法稳定【火焰建立时长】1秒以上，点火失败</t>
+  </si>
+  <si>
+    <t>报警：点火失败</t>
+  </si>
+  <si>
+    <t>火焰丢失</t>
+  </si>
+  <si>
+    <t>正常运行中，火焰丢失超过2【火焰丢失延时】秒，报警</t>
+  </si>
+  <si>
+    <t>报警：火焰丢失</t>
+  </si>
+  <si>
+    <t>主火运行</t>
+  </si>
+  <si>
+    <t>开启主火阀V2、安全阀V1</t>
+  </si>
+  <si>
+    <t>阀正常开启</t>
+  </si>
+  <si>
+    <t>温控启停</t>
+  </si>
+  <si>
+    <t>调节当前温度为超过停机温度</t>
+  </si>
+  <si>
+    <t>超过设定温度，关闭主火阀、安全阀</t>
+  </si>
+  <si>
+    <t>手动模式</t>
+  </si>
+  <si>
+    <t>手动模式按屏幕上增档、减档</t>
+  </si>
+  <si>
+    <t>档位随增减档而变动</t>
+  </si>
+  <si>
+    <t>自动模式</t>
+  </si>
+  <si>
+    <t>自动模式升降档由PID控制，改变当前温度，观察档位变化情况</t>
+  </si>
+  <si>
+    <t>随温度升高而降档</t>
+  </si>
+  <si>
+    <t>阶段升温</t>
+  </si>
+  <si>
+    <t>观察目标温度是否按照设定的温度变化</t>
+  </si>
+  <si>
+    <t>会变化</t>
+  </si>
+  <si>
+    <t>485通讯</t>
+  </si>
+  <si>
+    <t>能看到</t>
+  </si>
+  <si>
+    <t>本地_远程</t>
+  </si>
+  <si>
+    <t>本地_远程互斥</t>
+  </si>
+  <si>
+    <t>上电-检漏
+手动-检漏</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1灯亮，接通燃气低压开关
+V2灯亮，关闭燃气低压开关</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>在30秒内
+空气调节阀打开至吹扫位置
+燃气调节阀打开至20%</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>上电-调节阀检测
+手动-调节阀检测</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1灯亮，不接通燃气低压开关
+V2灯亮，燃气低压开关接能，不关闭</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>在30秒内
+1、空气调节阀没有打开至吹扫位置
+2、燃气调节阀没有打开至20%</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>HMI 空气调节阀 闪红灯
+HMI 燃气调节阀 闪红灯</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>上电-检测中启动
+手动-检测中启动</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上四步
+在进行检测中，按启动按钮</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>调节阀走到位，开始吹扫
+调节阀没走到位，达到限制时长30秒，开始吹扫</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>调节阀走到位，开始点火
+调节阀没走到位，达到限制时长30秒，开始点火</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察远程是否能正常看到设备状态
+故障状态、自动状态、启动状态、停止状态、远程状态
+空气调节阀开度、燃气调节阀开度、当前温度、当前档位、PID温度（阶段6）</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>切换本地远程旋钮
+操作 启动、停止、复位</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>正常</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -5613,7 +5824,7 @@
     <numFmt numFmtId="177" formatCode="0.0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -5793,6 +6004,12 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5941,7 +6158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6182,12 +6399,143 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 4 2" xfId="1" xr:uid="{C97CC49E-8548-40A7-B373-8E3F8F01BD97}"/>
   </cellStyles>
-  <dxfs count="87">
+  <dxfs count="94">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color auto="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -8183,156 +8531,170 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BC6A3F09-E86C-49A8-B91A-E1B95FD203B0}" name="表8" displayName="表8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="86" dataDxfId="84" headerRowBorderDxfId="85" tableBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BC6A3F09-E86C-49A8-B91A-E1B95FD203B0}" name="表8" displayName="表8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="93" dataDxfId="91" headerRowBorderDxfId="92" tableBorderDxfId="90">
   <autoFilter ref="A1:F21" xr:uid="{31503A1A-3ED1-4869-9B93-C5ABFAC7625B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
     <sortCondition ref="A1:A21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="命名类型" dataDxfId="82"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="名称" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="代码" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="存储区域" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="示例" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="说明" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="命名类型" dataDxfId="89"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="名称" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="代码" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="存储区域" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="示例" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="说明" dataDxfId="84"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:F21" xr:uid="{E517E8B6-ADC0-4F95-930E-5AF82CCFF0B4}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF667D90-1EB1-4976-A8D5-70F378E47508}" name="表1" displayName="表1" ref="A1:F445" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73">
-  <autoFilter ref="A1:F445" xr:uid="{EAEC5D8C-41E3-481D-8A3D-D139585DF349}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F445">
-    <sortCondition ref="B1:B445"/>
-  </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="存储区" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="排序" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="符号" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="地址" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="注释" dataDxfId="68"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="停电保持" dataDxfId="67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}" name="表2" displayName="表2" ref="A1:E18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:E18" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{092C8F4C-750F-4A54-9775-0E878E7F692D}" name="类别" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{55E7343C-005A-47DD-BF51-A98FEB8687FA}" name="项目" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{E219FFED-DB05-4801-BA8C-E5182B5E135C}" name="操作步骤" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{37775F0D-5709-4D26-8B0D-3C61F165FF43}" name="预期结果" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{1DD79E4F-C3FB-4EA3-8CB8-5707D129384D}" name="实测结果" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{69D67C9D-053D-42BE-8EFD-926EE2DB3533}" name="表1_7" displayName="表1_7" ref="A1:F61" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63">
-  <autoFilter ref="A1:F61" xr:uid="{81970FAC-CFE7-4A1D-A5CF-A2EACBF101FD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F61">
-    <sortCondition ref="B1:B61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF667D90-1EB1-4976-A8D5-70F378E47508}" name="表1" displayName="表1" ref="A1:F445" totalsRowShown="0" headerRowDxfId="83" dataDxfId="81" headerRowBorderDxfId="82" tableBorderDxfId="80">
+  <autoFilter ref="A1:F445" xr:uid="{EAEC5D8C-41E3-481D-8A3D-D139585DF349}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F445">
+    <sortCondition ref="B1:B445"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="存储区" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="排序" dataDxfId="61">
-      <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="符号" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="地址" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="注释" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="停电保持" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="存储区" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="排序" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="符号" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="地址" dataDxfId="76"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="注释" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="停电保持" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{819FCED7-92C0-4647-B4B4-EBF1A26CEDAE}" name="表46" displayName="表46" ref="B1:G17" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="B1:G17" xr:uid="{94000AEE-EA2C-4D0D-8C4C-2ABB18A8C2A9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{69D67C9D-053D-42BE-8EFD-926EE2DB3533}" name="表1_7" displayName="表1_7" ref="A1:F61" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70">
+  <autoFilter ref="A1:F61" xr:uid="{81970FAC-CFE7-4A1D-A5CF-A2EACBF101FD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F61">
+    <sortCondition ref="B1:B61"/>
+  </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="从站 HoldStar=500" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="符号" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="从站 HoldStar=1500" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="注释" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Modbus主站地址" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="备注" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="存储区" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="排序" dataDxfId="68">
+      <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="符号" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="地址" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="注释" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="停电保持" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{90352B38-6F74-4B30-9D89-B1BBC62CC6D9}" name="表15" displayName="表15" ref="A1:B3" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
-  <autoFilter ref="A1:B3" xr:uid="{2D618419-CC93-4748-AC73-50D15728A337}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="设备" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="缩写" dataDxfId="42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{819FCED7-92C0-4647-B4B4-EBF1A26CEDAE}" name="表46" displayName="表46" ref="B1:G17" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="B1:G17" xr:uid="{94000AEE-EA2C-4D0D-8C4C-2ABB18A8C2A9}"/>
+  <tableColumns count="6">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="从站 HoldStar=500" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="符号" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="从站 HoldStar=1500" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="注释" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Modbus主站地址" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="备注" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{1B1EF626-8785-43D8-946F-EB282409C2A3}" name="表1_17" displayName="表1_17" ref="A1:F198" totalsRowShown="0" headerRowDxfId="41" dataDxfId="39" headerRowBorderDxfId="40" tableBorderDxfId="38">
-  <autoFilter ref="A1:F198" xr:uid="{3426D145-FA7C-4D4F-8D7A-5904FEA768E0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F198">
-    <sortCondition ref="B1:B198"/>
-  </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="存储区" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="排序" dataDxfId="36">
-      <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="符号" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="地址" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="注释" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="停电保持" dataDxfId="32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{90352B38-6F74-4B30-9D89-B1BBC62CC6D9}" name="表15" displayName="表15" ref="A1:B3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+  <autoFilter ref="A1:B3" xr:uid="{2D618419-CC93-4748-AC73-50D15728A337}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="设备" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="缩写" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4178DD1D-C394-4C90-A1E0-3503C781D35F}" name="表1_1718" displayName="表1_1718" ref="A1:F215" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
-  <autoFilter ref="A1:F215" xr:uid="{E8622A0D-4D7B-4CC8-BEC1-5B22455130E1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A83:F215">
-    <sortCondition ref="B1:B215"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{1B1EF626-8785-43D8-946F-EB282409C2A3}" name="表1_17" displayName="表1_17" ref="A1:F198" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45">
+  <autoFilter ref="A1:F198" xr:uid="{3426D145-FA7C-4D4F-8D7A-5904FEA768E0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F198">
+    <sortCondition ref="B1:B198"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="存储区" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="排序" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="存储区" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="排序" dataDxfId="43">
       <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="符号" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="地址" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="注释" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="停电保持" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="符号" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="地址" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="注释" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="停电保持" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G236" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
-  <autoFilter ref="A1:G236" xr:uid="{B3E6F695-5A5D-43F2-A4A9-C2D31569F3E9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G223">
-    <sortCondition ref="F1:F223"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4178DD1D-C394-4C90-A1E0-3503C781D35F}" name="表1_1718" displayName="表1_1718" ref="A1:F215" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35">
+  <autoFilter ref="A1:F215" xr:uid="{E8622A0D-4D7B-4CC8-BEC1-5B22455130E1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A83:F215">
+    <sortCondition ref="B1:B215"/>
   </sortState>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="11"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="存储区" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="排序" dataDxfId="33">
+      <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="符号" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="地址" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="注释" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="停电保持" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F21" xr:uid="{E517E8B6-ADC0-4F95-930E-5AF82CCFF0B4}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G236" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
+  <autoFilter ref="A1:G236" xr:uid="{B3E6F695-5A5D-43F2-A4A9-C2D31569F3E9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G223">
+    <sortCondition ref="F1:F223"/>
+  </sortState>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8950,6 +9312,426 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D43CC4C-71E3-46F9-8C94-C607BA6D0756}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20" style="42" customWidth="1"/>
+    <col min="5" max="5" width="6.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="58" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A1" s="55" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B1" s="75" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C1" s="75" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A2" s="50" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A3" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>558</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A4" s="50" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>559</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.5">
+      <c r="A5" s="50" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>811</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A6" s="50" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>562</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A7" s="50" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>563</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>815</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A8" s="50" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>818</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>817</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.5">
+      <c r="A9" s="50" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>820</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A10" s="76" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F10" s="46"/>
+    </row>
+    <row r="11" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A11" s="53" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>571</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F11" s="46"/>
+    </row>
+    <row r="12" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A12" s="53" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>572</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>827</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A13" s="53" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>573</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>829</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A14" s="53" t="s">
+        <v>832</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>574</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F14" s="46"/>
+    </row>
+    <row r="15" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A15" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>575</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F15" s="46"/>
+    </row>
+    <row r="16" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A16" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>576</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A17" s="50" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>577</v>
+      </c>
+      <c r="D17" s="59" t="s">
+        <v>836</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F17" s="51"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A18" s="53" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="48" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E18" s="54" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A19" s="50" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C19" s="46"/>
+      <c r="D19" s="59" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A20" s="53" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="48" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="54" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="24.95" customHeight="1">
+      <c r="A21" s="50" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C21" s="51"/>
+      <c r="D21" s="59" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="21" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA1DE75-66A2-4BB5-9D6E-88BAB39F5A48}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -9056,6 +9838,345 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8628761D-8897-4103-9A07-B5EE77259803}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="42" customWidth="1"/>
+    <col min="3" max="3" width="30.625" style="42" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="42" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="80" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="80" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.5">
+      <c r="A2" s="78" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>678</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75">
+      <c r="A3" s="82" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>1742</v>
+      </c>
+      <c r="E3" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="42.75">
+      <c r="A4" s="81" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D4" s="87" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E4" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="57">
+      <c r="A5" s="82" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B5" s="87" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E5" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.5">
+      <c r="A6" s="81" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D6" s="87" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="42.75">
+      <c r="A7" s="81" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B7" s="87" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D7" s="87" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="42.75">
+      <c r="A8" s="83" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D8" s="87" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.5">
+      <c r="A9" s="83" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B9" s="87" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="87" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D9" s="87" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="42.75">
+      <c r="A10" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B10" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="87" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D10" s="87" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.5">
+      <c r="A11" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B11" s="87" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C11" s="87" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D11" s="87" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A12" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B12" s="87" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C12" s="87" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D12" s="87" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.5">
+      <c r="A13" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B13" s="87" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C13" s="87" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D13" s="87" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A14" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B14" s="87" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C14" s="87" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D14" s="87" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.5">
+      <c r="A15" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B15" s="87" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C15" s="87" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D15" s="87" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.5">
+      <c r="A16" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B16" s="87" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C16" s="87" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D16" s="87" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="85.5">
+      <c r="A17" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B17" s="87" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D17" s="87" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.5">
+      <c r="A18" s="83" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B18" s="87" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D18" s="87" t="s">
+        <v>1774</v>
+      </c>
+      <c r="E18" s="82" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A19" s="84"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="84"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E2">
+    <sortCondition ref="A1:A2"/>
+  </sortState>
+  <phoneticPr fontId="32" type="noConversion"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832CE4E-6640-4F77-AE2C-2BCFE1960A83}">
   <dimension ref="A1:K445"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
@@ -17384,7 +18505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2AA81C-8F1F-4458-8028-A2B83F85B815}">
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
@@ -18558,7 +19679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CB5D3A-60EF-41A0-A517-7415BF086DA6}">
   <dimension ref="B1:G17"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="24.95" customHeight="1"/>
@@ -18922,7 +20043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D004169C-3805-4C15-8A78-8EFBD42CAEA3}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
@@ -18964,7 +20085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04810001-19A2-4057-9492-DAB102C978CB}">
   <dimension ref="A1:F198"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
@@ -23145,7 +24266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777D3A3F-8E01-42AE-AC20-239C93F52F98}">
   <dimension ref="A1:F215"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
@@ -27469,7 +28590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67ABFE6-0E3D-41E3-A8E9-BDC84F153A78}">
   <dimension ref="A1:G236"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
@@ -33289,424 +34410,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D43CC4C-71E3-46F9-8C94-C607BA6D0756}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20" style="42" customWidth="1"/>
-    <col min="5" max="5" width="6.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="58" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="55" t="s">
-        <v>1563</v>
-      </c>
-      <c r="B1" s="75" t="s">
-        <v>1726</v>
-      </c>
-      <c r="C1" s="75" t="s">
-        <v>1727</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>1535</v>
-      </c>
-      <c r="E1" s="57" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>1537</v>
-      </c>
-      <c r="B2" s="51" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>1516</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>1539</v>
-      </c>
-      <c r="E2" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A3" s="50" t="s">
-        <v>1567</v>
-      </c>
-      <c r="B3" s="51" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A4" s="50" t="s">
-        <v>1568</v>
-      </c>
-      <c r="B4" s="51" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.5">
-      <c r="A5" s="50" t="s">
-        <v>1569</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>1547</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>811</v>
-      </c>
-      <c r="E5" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F5" s="74" t="s">
-        <v>1554</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A6" s="50" t="s">
-        <v>1541</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>562</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E6" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>1556</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A7" s="50" t="s">
-        <v>1542</v>
-      </c>
-      <c r="B7" s="51" t="s">
-        <v>1549</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>815</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A8" s="50" t="s">
-        <v>1543</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>818</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>817</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>1558</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.5">
-      <c r="A9" s="50" t="s">
-        <v>1544</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>1551</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>820</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F9" s="60" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A10" s="76" t="s">
-        <v>1728</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>1562</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F10" s="46"/>
-    </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A11" s="53" t="s">
-        <v>1564</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>571</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>1507</v>
-      </c>
-      <c r="E11" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F11" s="46"/>
-    </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A12" s="53" t="s">
-        <v>1565</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>572</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>827</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F12" s="46"/>
-    </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A13" s="53" t="s">
-        <v>1559</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>573</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>829</v>
-      </c>
-      <c r="E13" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F13" s="46"/>
-    </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A14" s="53" t="s">
-        <v>832</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>574</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>1480</v>
-      </c>
-      <c r="E14" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F14" s="46"/>
-    </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A15" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>575</v>
-      </c>
-      <c r="D15" s="48" t="s">
-        <v>1481</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F15" s="46"/>
-    </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A16" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>576</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>1482</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F16" s="46"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A17" s="50" t="s">
-        <v>1560</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>577</v>
-      </c>
-      <c r="D17" s="59" t="s">
-        <v>836</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F17" s="51"/>
-    </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A18" s="53" t="s">
-        <v>1573</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="48" t="s">
-        <v>1498</v>
-      </c>
-      <c r="E18" s="54" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>1572</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A19" s="50" t="s">
-        <v>1574</v>
-      </c>
-      <c r="B19" s="51" t="s">
-        <v>1454</v>
-      </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="59" t="s">
-        <v>1499</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>1577</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A20" s="53" t="s">
-        <v>1575</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>1445</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="48" t="s">
-        <v>1500</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>1578</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A21" s="50" t="s">
-        <v>1576</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>1448</v>
-      </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="59" t="s">
-        <v>1501</v>
-      </c>
-      <c r="E21" s="52" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>1579</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\02-PLC项目\江西沸腾炉烧嘴程序改造\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D263828-DFB1-40EF-B1E0-02B05C273EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78038438-C0D1-4CFA-869D-FC3DA5214BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="622" activeTab="1" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
   </bookViews>
@@ -6432,110 +6432,6 @@
     <cellStyle name="常规 4 2" xfId="1" xr:uid="{C97CC49E-8548-40A7-B373-8E3F8F01BD97}"/>
   </cellStyles>
   <dxfs count="94">
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color auto="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -8199,6 +8095,110 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color auto="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -8549,152 +8549,152 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F21" xr:uid="{E517E8B6-ADC0-4F95-930E-5AF82CCFF0B4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}" name="表2" displayName="表2" ref="A1:E18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}" name="表2" displayName="表2" ref="A1:E18" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:E18" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{092C8F4C-750F-4A54-9775-0E878E7F692D}" name="类别" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{55E7343C-005A-47DD-BF51-A98FEB8687FA}" name="项目" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{E219FFED-DB05-4801-BA8C-E5182B5E135C}" name="操作步骤" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{37775F0D-5709-4D26-8B0D-3C61F165FF43}" name="预期结果" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{1DD79E4F-C3FB-4EA3-8CB8-5707D129384D}" name="实测结果" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{092C8F4C-750F-4A54-9775-0E878E7F692D}" name="类别" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{55E7343C-005A-47DD-BF51-A98FEB8687FA}" name="项目" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{E219FFED-DB05-4801-BA8C-E5182B5E135C}" name="操作步骤" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{37775F0D-5709-4D26-8B0D-3C61F165FF43}" name="预期结果" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{1DD79E4F-C3FB-4EA3-8CB8-5707D129384D}" name="实测结果" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF667D90-1EB1-4976-A8D5-70F378E47508}" name="表1" displayName="表1" ref="A1:F445" totalsRowShown="0" headerRowDxfId="83" dataDxfId="81" headerRowBorderDxfId="82" tableBorderDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF667D90-1EB1-4976-A8D5-70F378E47508}" name="表1" displayName="表1" ref="A1:F445" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73">
   <autoFilter ref="A1:F445" xr:uid="{EAEC5D8C-41E3-481D-8A3D-D139585DF349}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F445">
     <sortCondition ref="B1:B445"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="存储区" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="排序" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="符号" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="地址" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="注释" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="停电保持" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="存储区" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="排序" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="符号" dataDxfId="70"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="地址" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="注释" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="停电保持" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{69D67C9D-053D-42BE-8EFD-926EE2DB3533}" name="表1_7" displayName="表1_7" ref="A1:F61" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{69D67C9D-053D-42BE-8EFD-926EE2DB3533}" name="表1_7" displayName="表1_7" ref="A1:F61" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63">
   <autoFilter ref="A1:F61" xr:uid="{81970FAC-CFE7-4A1D-A5CF-A2EACBF101FD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F61">
     <sortCondition ref="B1:B61"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="存储区" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="排序" dataDxfId="68">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="存储区" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="排序" dataDxfId="61">
       <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="符号" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="地址" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="注释" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="停电保持" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="符号" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="地址" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="注释" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="停电保持" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{819FCED7-92C0-4647-B4B4-EBF1A26CEDAE}" name="表46" displayName="表46" ref="B1:G17" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{819FCED7-92C0-4647-B4B4-EBF1A26CEDAE}" name="表46" displayName="表46" ref="B1:G17" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="B1:G17" xr:uid="{94000AEE-EA2C-4D0D-8C4C-2ABB18A8C2A9}"/>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="从站 HoldStar=500" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="符号" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="从站 HoldStar=1500" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="注释" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Modbus主站地址" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="备注" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="从站 HoldStar=500" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="符号" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="从站 HoldStar=1500" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="注释" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Modbus主站地址" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="备注" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{90352B38-6F74-4B30-9D89-B1BBC62CC6D9}" name="表15" displayName="表15" ref="A1:B3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{90352B38-6F74-4B30-9D89-B1BBC62CC6D9}" name="表15" displayName="表15" ref="A1:B3" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="A1:B3" xr:uid="{2D618419-CC93-4748-AC73-50D15728A337}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="设备" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="缩写" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="设备" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="缩写" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{1B1EF626-8785-43D8-946F-EB282409C2A3}" name="表1_17" displayName="表1_17" ref="A1:F198" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{1B1EF626-8785-43D8-946F-EB282409C2A3}" name="表1_17" displayName="表1_17" ref="A1:F198" totalsRowShown="0" headerRowDxfId="41" dataDxfId="39" headerRowBorderDxfId="40" tableBorderDxfId="38">
   <autoFilter ref="A1:F198" xr:uid="{3426D145-FA7C-4D4F-8D7A-5904FEA768E0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F198">
     <sortCondition ref="B1:B198"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="存储区" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="排序" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="存储区" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="排序" dataDxfId="36">
       <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="符号" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="地址" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="注释" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="停电保持" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="符号" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="地址" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="注释" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="停电保持" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4178DD1D-C394-4C90-A1E0-3503C781D35F}" name="表1_1718" displayName="表1_1718" ref="A1:F215" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4178DD1D-C394-4C90-A1E0-3503C781D35F}" name="表1_1718" displayName="表1_1718" ref="A1:F215" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
   <autoFilter ref="A1:F215" xr:uid="{E8622A0D-4D7B-4CC8-BEC1-5B22455130E1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A83:F215">
     <sortCondition ref="B1:B215"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="存储区" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="排序" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="存储区" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="排序" dataDxfId="26">
       <calculatedColumnFormula>VALUE(RIGHT(D2,LEN(D2)-LEN(A2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="符号" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="地址" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="注释" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="停电保持" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="符号" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="地址" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="注释" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="停电保持" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G236" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G236" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
   <autoFilter ref="A1:G236" xr:uid="{B3E6F695-5A5D-43F2-A4A9-C2D31569F3E9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G223">
     <sortCondition ref="F1:F223"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\codes\04-electricity\01-plc\江铜\burnerControler_JXT\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8A5AEF-6D66-4502-A067-1A9A4AA5E720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55386B8-0723-4115-B4DE-2E7F4306434F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="622" activeTab="9" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
+    <workbookView xWindow="1065" yWindow="2685" windowWidth="21600" windowHeight="11295" tabRatio="622" activeTab="4" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
   </bookViews>
   <sheets>
     <sheet name="命名规范" sheetId="8" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="1851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="1850">
   <si>
     <t>I</t>
   </si>
@@ -5259,10 +5259,6 @@
   </si>
   <si>
     <t>DCS端 显示</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DCS端 设定</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -6344,7 +6340,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6612,29 +6608,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6642,98 +6626,6 @@
     <cellStyle name="常规 4 2" xfId="1" xr:uid="{C97CC49E-8548-40A7-B373-8E3F8F01BD97}"/>
   </cellStyles>
   <dxfs count="99">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7012,6 +6904,98 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -8851,15 +8835,15 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6DC73BD-6F51-4BCF-84E1-56C5A6AFF38F}" name="表3" displayName="表3" ref="A1:C40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6DC73BD-6F51-4BCF-84E1-56C5A6AFF38F}" name="表3" displayName="表3" ref="A1:C40" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:C40" xr:uid="{B6DC73BD-6F51-4BCF-84E1-56C5A6AFF38F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
     <sortCondition ref="B1:B40"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C9EC5542-3176-4CF9-AACC-E9B37EB87292}" name="存储区" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{B8E7CB01-86AB-4B99-82DC-6E4AF1B67DCA}" name="地址" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{17BBCF5F-DF23-4029-9CA9-3FFC00CBE4FD}" name="差值" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{C9EC5542-3176-4CF9-AACC-E9B37EB87292}" name="存储区" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{B8E7CB01-86AB-4B99-82DC-6E4AF1B67DCA}" name="地址" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{17BBCF5F-DF23-4029-9CA9-3FFC00CBE4FD}" name="差值" dataDxfId="11">
       <calculatedColumnFormula>B2-N(B1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8868,15 +8852,15 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F21" xr:uid="{E517E8B6-ADC0-4F95-930E-5AF82CCFF0B4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9651,35 +9635,35 @@
   <sheetData>
     <row r="1" spans="1:15" ht="24.95" customHeight="1">
       <c r="A1" s="83" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B1" s="83" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C1" s="83" t="s">
         <v>1848</v>
-      </c>
-      <c r="C1" s="83" t="s">
-        <v>1849</v>
       </c>
       <c r="I1" s="72" t="str">
         <f t="array" ref="I1">LEFT(N1, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, N1 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
       </c>
-      <c r="J1" s="94">
+      <c r="J1" s="90">
         <f>VALUE(RIGHT(N1,LEN(N1)-LEN(I1)))</f>
         <v>814</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94">
+      <c r="K1" s="90"/>
+      <c r="L1" s="90">
         <f>LEN(M1)</f>
         <v>12</v>
       </c>
-      <c r="M1" s="93" t="s">
-        <v>1842</v>
-      </c>
-      <c r="N1" s="95" t="s">
-        <v>1711</v>
-      </c>
-      <c r="O1" s="96" t="s">
-        <v>1847</v>
+      <c r="M1" s="89" t="s">
+        <v>1841</v>
+      </c>
+      <c r="N1" s="89" t="s">
+        <v>1710</v>
+      </c>
+      <c r="O1" s="91" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24.95" customHeight="1">
@@ -9690,7 +9674,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="1">
-        <f>B2-N(B1)</f>
+        <f t="shared" ref="C2:C40" si="0">B2-N(B1)</f>
         <v>20</v>
       </c>
     </row>
@@ -9702,7 +9686,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="1">
-        <f>B3-N(B2)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9714,7 +9698,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="1">
-        <f>B4-N(B3)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -9726,7 +9710,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="1">
-        <f>B5-N(B4)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9738,7 +9722,7 @@
         <v>40</v>
       </c>
       <c r="C6" s="1">
-        <f>B6-N(B5)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9750,7 +9734,7 @@
         <v>44</v>
       </c>
       <c r="C7" s="1">
-        <f>B7-N(B6)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9762,7 +9746,7 @@
         <v>48</v>
       </c>
       <c r="C8" s="1">
-        <f>B8-N(B7)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9774,7 +9758,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="1">
-        <f>B9-N(B8)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9786,7 +9770,7 @@
         <v>56</v>
       </c>
       <c r="C10" s="1">
-        <f>B10-N(B9)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9798,7 +9782,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="1">
-        <f>B11-N(B10)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9810,7 +9794,7 @@
         <v>64</v>
       </c>
       <c r="C12" s="1">
-        <f>B12-N(B11)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9822,7 +9806,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="1">
-        <f>B13-N(B12)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9834,7 +9818,7 @@
         <v>72</v>
       </c>
       <c r="C14" s="1">
-        <f>B14-N(B13)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9846,7 +9830,7 @@
         <v>76</v>
       </c>
       <c r="C15" s="1">
-        <f>B15-N(B14)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9858,7 +9842,7 @@
         <v>80</v>
       </c>
       <c r="C16" s="1">
-        <f>B16-N(B15)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9870,7 +9854,7 @@
         <v>84</v>
       </c>
       <c r="C17" s="1">
-        <f>B17-N(B16)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9882,7 +9866,7 @@
         <v>88</v>
       </c>
       <c r="C18" s="1">
-        <f>B18-N(B17)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9894,7 +9878,7 @@
         <v>92</v>
       </c>
       <c r="C19" s="1">
-        <f>B19-N(B18)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9906,7 +9890,7 @@
         <v>96</v>
       </c>
       <c r="C20" s="1">
-        <f>B20-N(B19)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9918,7 +9902,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="1">
-        <f>B21-N(B20)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9930,7 +9914,7 @@
         <v>100</v>
       </c>
       <c r="C22" s="1">
-        <f>B22-N(B21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9942,7 +9926,7 @@
         <v>104</v>
       </c>
       <c r="C23" s="1">
-        <f>B23-N(B22)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9954,7 +9938,7 @@
         <v>108</v>
       </c>
       <c r="C24" s="1">
-        <f>B24-N(B23)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9966,7 +9950,7 @@
         <v>112</v>
       </c>
       <c r="C25" s="1">
-        <f>B25-N(B24)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9978,7 +9962,7 @@
         <v>116</v>
       </c>
       <c r="C26" s="1">
-        <f>B26-N(B25)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -9990,7 +9974,7 @@
         <v>120</v>
       </c>
       <c r="C27" s="1">
-        <f>B27-N(B26)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10002,7 +9986,7 @@
         <v>124</v>
       </c>
       <c r="C28" s="1">
-        <f>B28-N(B27)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10014,7 +9998,7 @@
         <v>128</v>
       </c>
       <c r="C29" s="1">
-        <f>B29-N(B28)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10026,7 +10010,7 @@
         <v>132</v>
       </c>
       <c r="C30" s="1">
-        <f>B30-N(B29)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10038,7 +10022,7 @@
         <v>136</v>
       </c>
       <c r="C31" s="1">
-        <f>B31-N(B30)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10050,7 +10034,7 @@
         <v>138</v>
       </c>
       <c r="C32" s="1">
-        <f>B32-N(B31)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -10062,7 +10046,7 @@
         <v>140</v>
       </c>
       <c r="C33" s="1">
-        <f>B33-N(B32)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -10074,7 +10058,7 @@
         <v>142</v>
       </c>
       <c r="C34" s="1">
-        <f>B34-N(B33)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -10086,7 +10070,7 @@
         <v>144</v>
       </c>
       <c r="C35" s="1">
-        <f>B35-N(B34)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -10098,7 +10082,7 @@
         <v>146</v>
       </c>
       <c r="C36" s="1">
-        <f>B36-N(B35)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -10110,7 +10094,7 @@
         <v>150</v>
       </c>
       <c r="C37" s="1">
-        <f>B37-N(B36)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10122,7 +10106,7 @@
         <v>154</v>
       </c>
       <c r="C38" s="1">
-        <f>B38-N(B37)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -10134,7 +10118,7 @@
         <v>156</v>
       </c>
       <c r="C39" s="1">
-        <f>B39-N(B38)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -10146,7 +10130,7 @@
         <v>300</v>
       </c>
       <c r="C40" s="1">
-        <f>B40-N(B39)</f>
+        <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
@@ -10183,10 +10167,10 @@
         <v>1563</v>
       </c>
       <c r="B1" s="75" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C1" s="75" t="s">
         <v>1708</v>
-      </c>
-      <c r="C1" s="75" t="s">
-        <v>1709</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>1535</v>
@@ -10360,7 +10344,7 @@
     </row>
     <row r="10" spans="1:6" ht="24.95" customHeight="1">
       <c r="A10" s="76" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B10" s="46" t="s">
         <v>13</v>
@@ -10705,308 +10689,308 @@
   <sheetData>
     <row r="1" spans="1:5" s="80" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="80" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1" s="85" t="s">
         <v>1767</v>
       </c>
-      <c r="B1" s="85" t="s">
-        <v>1768</v>
-      </c>
       <c r="C1" s="85" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>1714</v>
       </c>
-      <c r="D1" s="85" t="s">
+      <c r="E1" s="80" t="s">
         <v>1715</v>
-      </c>
-      <c r="E1" s="80" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5">
       <c r="A2" s="78" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B2" s="86" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C2" s="86" t="s">
         <v>1752</v>
-      </c>
-      <c r="C2" s="86" t="s">
-        <v>1753</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>678</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="42.75">
       <c r="A3" s="82" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D3" s="87" t="s">
         <v>1718</v>
       </c>
-      <c r="B3" s="86" t="s">
-        <v>1752</v>
-      </c>
-      <c r="C3" s="86" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D3" s="87" t="s">
-        <v>1719</v>
-      </c>
       <c r="E3" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="42.75">
       <c r="A4" s="81" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="C4" s="86" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D4" s="87" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="57">
       <c r="A5" s="82" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B5" s="87" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="C5" s="86" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D5" s="86" t="s">
         <v>1757</v>
       </c>
-      <c r="D5" s="86" t="s">
-        <v>1758</v>
-      </c>
       <c r="E5" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.5">
       <c r="A6" s="81" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B6" s="86" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C6" s="86" t="s">
         <v>1759</v>
       </c>
-      <c r="C6" s="86" t="s">
-        <v>1760</v>
-      </c>
       <c r="D6" s="87" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E6" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="42.75">
       <c r="A7" s="81" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B7" s="87" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D7" s="87" t="s">
         <v>1722</v>
       </c>
-      <c r="C7" s="86" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D7" s="87" t="s">
-        <v>1723</v>
-      </c>
       <c r="E7" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="42.75">
       <c r="A8" s="83" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B8" s="87" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D8" s="87" t="s">
         <v>1724</v>
       </c>
-      <c r="C8" s="86" t="s">
-        <v>1762</v>
-      </c>
-      <c r="D8" s="87" t="s">
-        <v>1725</v>
-      </c>
       <c r="E8" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="83" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B9" s="87" t="s">
         <v>216</v>
       </c>
       <c r="C9" s="87" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D9" s="87" t="s">
         <v>1726</v>
       </c>
-      <c r="D9" s="87" t="s">
-        <v>1727</v>
-      </c>
       <c r="E9" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="42.75">
       <c r="A10" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B10" s="87" t="s">
         <v>220</v>
       </c>
       <c r="C10" s="87" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D10" s="87" t="s">
         <v>1728</v>
       </c>
-      <c r="D10" s="87" t="s">
-        <v>1729</v>
-      </c>
       <c r="E10" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.5">
       <c r="A11" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B11" s="87" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C11" s="87" t="s">
         <v>1730</v>
       </c>
-      <c r="C11" s="87" t="s">
+      <c r="D11" s="87" t="s">
         <v>1731</v>
       </c>
-      <c r="D11" s="87" t="s">
-        <v>1732</v>
-      </c>
       <c r="E11" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="24.95" customHeight="1">
       <c r="A12" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B12" s="87" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C12" s="87" t="s">
         <v>1733</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="D12" s="87" t="s">
         <v>1734</v>
       </c>
-      <c r="D12" s="87" t="s">
-        <v>1735</v>
-      </c>
       <c r="E12" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5">
       <c r="A13" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B13" s="87" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C13" s="87" t="s">
         <v>1736</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="D13" s="87" t="s">
         <v>1737</v>
       </c>
-      <c r="D13" s="87" t="s">
-        <v>1738</v>
-      </c>
       <c r="E13" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="24.95" customHeight="1">
       <c r="A14" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B14" s="87" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C14" s="87" t="s">
         <v>1739</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="D14" s="87" t="s">
         <v>1740</v>
       </c>
-      <c r="D14" s="87" t="s">
-        <v>1741</v>
-      </c>
       <c r="E14" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.5">
       <c r="A15" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B15" s="87" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>1742</v>
       </c>
-      <c r="C15" s="87" t="s">
+      <c r="D15" s="87" t="s">
         <v>1743</v>
       </c>
-      <c r="D15" s="87" t="s">
-        <v>1744</v>
-      </c>
       <c r="E15" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.5">
       <c r="A16" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B16" s="87" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C16" s="87" t="s">
         <v>1745</v>
       </c>
-      <c r="C16" s="87" t="s">
+      <c r="D16" s="87" t="s">
         <v>1746</v>
       </c>
-      <c r="D16" s="87" t="s">
-        <v>1747</v>
-      </c>
       <c r="E16" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="85.5">
       <c r="A17" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B17" s="87" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D17" s="87" t="s">
         <v>1748</v>
       </c>
-      <c r="C17" s="86" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D17" s="87" t="s">
-        <v>1749</v>
-      </c>
       <c r="E17" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.5">
       <c r="A18" s="83" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B18" s="87" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D18" s="87" t="s">
         <v>1750</v>
       </c>
-      <c r="C18" s="86" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D18" s="87" t="s">
-        <v>1751</v>
-      </c>
       <c r="E18" s="82" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="24.95" customHeight="1">
@@ -20686,7 +20670,7 @@
         <v>40061.129999999976</v>
       </c>
       <c r="G7" s="63" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="24.95" customHeight="1">
@@ -20706,7 +20690,7 @@
         <v>40061.13999999997</v>
       </c>
       <c r="G8" s="63" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="24.95" customHeight="1">
@@ -20726,7 +20710,7 @@
         <v>40061.149999999965</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="24.95" customHeight="1">
@@ -20746,7 +20730,7 @@
         <v>40061</v>
       </c>
       <c r="G10" s="63" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="24.95" customHeight="1">
@@ -20766,7 +20750,7 @@
         <v>40061.1</v>
       </c>
       <c r="G11" s="63" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="24.95" customHeight="1">
@@ -20833,7 +20817,7 @@
       <c r="B15" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="92" t="s">
         <v>1629</v>
       </c>
       <c r="D15" s="63" t="s">
@@ -20845,8 +20829,8 @@
       <c r="F15" s="65">
         <v>40191</v>
       </c>
-      <c r="G15" s="63" t="s">
-        <v>1633</v>
+      <c r="G15" s="92" t="s">
+        <v>1632</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="24.95" customHeight="1">
@@ -20871,7 +20855,7 @@
     <row r="17" spans="2:7" ht="24.95" customHeight="1">
       <c r="B17" s="69"/>
       <c r="C17" s="69" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D17" s="69" t="str">
         <f>"VW"&amp;1500+2*(F17-40000-1)</f>
@@ -29487,12 +29471,12 @@
         <v>AIW</v>
       </c>
       <c r="B2" s="1">
-        <f>VALUE(RIGHT(F2,LEN(F2)-LEN(A2)))</f>
+        <f t="shared" ref="B2:B65" si="0">VALUE(RIGHT(F2,LEN(F2)-LEN(A2)))</f>
         <v>18</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1">
-        <f>LEN(E2)</f>
+        <f t="shared" ref="D2:D65" si="1">LEN(E2)</f>
         <v>15</v>
       </c>
       <c r="E2" s="46" t="s">
@@ -29511,12 +29495,12 @@
         <v>AIW</v>
       </c>
       <c r="B3" s="1">
-        <f>VALUE(RIGHT(F3,LEN(F3)-LEN(A3)))</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
-        <f>LEN(E3)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E3" s="46" t="s">
@@ -29535,12 +29519,12 @@
         <v>AQW</v>
       </c>
       <c r="B4" s="1">
-        <f>VALUE(RIGHT(F4,LEN(F4)-LEN(A4)))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
-        <f>LEN(E4)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E4" s="46" t="s">
@@ -29559,12 +29543,12 @@
         <v>AQW</v>
       </c>
       <c r="B5" s="1">
-        <f>VALUE(RIGHT(F5,LEN(F5)-LEN(A5)))</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
-        <f>LEN(E5)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E5" s="46" t="s">
@@ -29583,12 +29567,12 @@
         <v>C</v>
       </c>
       <c r="B6" s="1">
-        <f>VALUE(RIGHT(F6,LEN(F6)-LEN(A6)))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
-        <f>LEN(E6)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -29598,7 +29582,7 @@
         <v>720</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24.95" customHeight="1">
@@ -29607,12 +29591,12 @@
         <v>C</v>
       </c>
       <c r="B7" s="1">
-        <f>VALUE(RIGHT(F7,LEN(F7)-LEN(A7)))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
-        <f>LEN(E7)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -29622,7 +29606,7 @@
         <v>723</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24.95" customHeight="1">
@@ -29631,12 +29615,12 @@
         <v>C</v>
       </c>
       <c r="B8" s="1">
-        <f>VALUE(RIGHT(F8,LEN(F8)-LEN(A8)))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
-        <f>LEN(E8)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -29646,7 +29630,7 @@
         <v>726</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24.95" customHeight="1">
@@ -29655,12 +29639,12 @@
         <v>C</v>
       </c>
       <c r="B9" s="1">
-        <f>VALUE(RIGHT(F9,LEN(F9)-LEN(A9)))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
-        <f>LEN(E9)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -29670,7 +29654,7 @@
         <v>729</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24.95" customHeight="1">
@@ -29679,12 +29663,12 @@
         <v>C</v>
       </c>
       <c r="B10" s="1">
-        <f>VALUE(RIGHT(F10,LEN(F10)-LEN(A10)))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
-        <f>LEN(E10)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -29694,7 +29678,7 @@
         <v>732</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24.95" customHeight="1">
@@ -29703,12 +29687,12 @@
         <v>C</v>
       </c>
       <c r="B11" s="1">
-        <f>VALUE(RIGHT(F11,LEN(F11)-LEN(A11)))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
-        <f>LEN(E11)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -29718,7 +29702,7 @@
         <v>735</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24.95" customHeight="1">
@@ -29727,12 +29711,12 @@
         <v>C</v>
       </c>
       <c r="B12" s="1">
-        <f>VALUE(RIGHT(F12,LEN(F12)-LEN(A12)))</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
-        <f>LEN(E12)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -29742,7 +29726,7 @@
         <v>738</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24.95" customHeight="1">
@@ -29751,12 +29735,12 @@
         <v>C</v>
       </c>
       <c r="B13" s="1">
-        <f>VALUE(RIGHT(F13,LEN(F13)-LEN(A13)))</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
-        <f>LEN(E13)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -29766,7 +29750,7 @@
         <v>741</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24.95" customHeight="1">
@@ -29775,12 +29759,12 @@
         <v>C</v>
       </c>
       <c r="B14" s="1">
-        <f>VALUE(RIGHT(F14,LEN(F14)-LEN(A14)))</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
-        <f>LEN(E14)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -29790,7 +29774,7 @@
         <v>744</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24.95" customHeight="1">
@@ -29799,22 +29783,22 @@
         <v>C</v>
       </c>
       <c r="B15" s="1">
-        <f>VALUE(RIGHT(F15,LEN(F15)-LEN(A15)))</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
-        <f>LEN(E15)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>1769</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="26" t="s">
         <v>1770</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24.95" customHeight="1">
@@ -29823,22 +29807,22 @@
         <v>C</v>
       </c>
       <c r="B16" s="1">
-        <f>VALUE(RIGHT(F16,LEN(F16)-LEN(A16)))</f>
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
-        <f>LEN(E16)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>1772</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="26" t="s">
         <v>1773</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24.95" customHeight="1">
@@ -29847,22 +29831,22 @@
         <v>C</v>
       </c>
       <c r="B17" s="1">
-        <f>VALUE(RIGHT(F17,LEN(F17)-LEN(A17)))</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
-        <f>LEN(E17)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>1775</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="26" t="s">
         <v>1776</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24.95" customHeight="1">
@@ -29871,22 +29855,22 @@
         <v>C</v>
       </c>
       <c r="B18" s="1">
-        <f>VALUE(RIGHT(F18,LEN(F18)-LEN(A18)))</f>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
-        <f>LEN(E18)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>1778</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="26" t="s">
         <v>1779</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24.95" customHeight="1">
@@ -29895,12 +29879,12 @@
         <v>M</v>
       </c>
       <c r="B19" s="1">
-        <f>VALUE(RIGHT(F19,LEN(F19)-LEN(A19)))</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
-        <f>LEN(E19)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E19" s="46" t="s">
@@ -29910,7 +29894,7 @@
         <v>1315</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24.95" customHeight="1">
@@ -29919,12 +29903,12 @@
         <v>M</v>
       </c>
       <c r="B20" s="1">
-        <f>VALUE(RIGHT(F20,LEN(F20)-LEN(A20)))</f>
+        <f t="shared" si="0"/>
         <v>20.100000000000001</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
-        <f>LEN(E20)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -29943,12 +29927,12 @@
         <v>M</v>
       </c>
       <c r="B21" s="1">
-        <f>VALUE(RIGHT(F21,LEN(F21)-LEN(A21)))</f>
+        <f t="shared" si="0"/>
         <v>20.2</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
-        <f>LEN(E21)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -29967,12 +29951,12 @@
         <v>M</v>
       </c>
       <c r="B22" s="1">
-        <f>VALUE(RIGHT(F22,LEN(F22)-LEN(A22)))</f>
+        <f t="shared" si="0"/>
         <v>20.3</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
-        <f>LEN(E22)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -29991,12 +29975,12 @@
         <v>M</v>
       </c>
       <c r="B23" s="1">
-        <f>VALUE(RIGHT(F23,LEN(F23)-LEN(A23)))</f>
+        <f t="shared" si="0"/>
         <v>20.399999999999999</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
-        <f>LEN(E23)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E23" s="5" t="s">
@@ -30015,12 +29999,12 @@
         <v>M</v>
       </c>
       <c r="B24" s="1">
-        <f>VALUE(RIGHT(F24,LEN(F24)-LEN(A24)))</f>
+        <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
-        <f>LEN(E24)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -30039,12 +30023,12 @@
         <v>M</v>
       </c>
       <c r="B25" s="1">
-        <f>VALUE(RIGHT(F25,LEN(F25)-LEN(A25)))</f>
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
-        <f>LEN(E25)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -30063,12 +30047,12 @@
         <v>M</v>
       </c>
       <c r="B26" s="1">
-        <f>VALUE(RIGHT(F26,LEN(F26)-LEN(A26)))</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
-        <f>LEN(E26)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E26" s="6" t="s">
@@ -30087,12 +30071,12 @@
         <v>M</v>
       </c>
       <c r="B27" s="1">
-        <f>VALUE(RIGHT(F27,LEN(F27)-LEN(A27)))</f>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
-        <f>LEN(E27)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -30111,22 +30095,22 @@
         <v>M</v>
       </c>
       <c r="B28" s="1">
-        <f>VALUE(RIGHT(F28,LEN(F28)-LEN(A28)))</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
-        <f>LEN(E28)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24.95" customHeight="1">
@@ -30135,12 +30119,12 @@
         <v>M</v>
       </c>
       <c r="B29" s="1">
-        <f>VALUE(RIGHT(F29,LEN(F29)-LEN(A29)))</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
-        <f>LEN(E29)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -30159,12 +30143,12 @@
         <v>M</v>
       </c>
       <c r="B30" s="1">
-        <f>VALUE(RIGHT(F30,LEN(F30)-LEN(A30)))</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
-        <f>LEN(E30)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -30183,12 +30167,12 @@
         <v>M</v>
       </c>
       <c r="B31" s="1">
-        <f>VALUE(RIGHT(F31,LEN(F31)-LEN(A31)))</f>
+        <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
-        <f>LEN(E31)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -30207,12 +30191,12 @@
         <v>M</v>
       </c>
       <c r="B32" s="1">
-        <f>VALUE(RIGHT(F32,LEN(F32)-LEN(A32)))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
-        <f>LEN(E32)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -30231,12 +30215,12 @@
         <v>M</v>
       </c>
       <c r="B33" s="1">
-        <f>VALUE(RIGHT(F33,LEN(F33)-LEN(A33)))</f>
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
-        <f>LEN(E33)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -30255,12 +30239,12 @@
         <v>M</v>
       </c>
       <c r="B34" s="1">
-        <f>VALUE(RIGHT(F34,LEN(F34)-LEN(A34)))</f>
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
-        <f>LEN(E34)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -30279,12 +30263,12 @@
         <v>M</v>
       </c>
       <c r="B35" s="1">
-        <f>VALUE(RIGHT(F35,LEN(F35)-LEN(A35)))</f>
+        <f t="shared" si="0"/>
         <v>1.3</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
-        <f>LEN(E35)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -30303,12 +30287,12 @@
         <v>M</v>
       </c>
       <c r="B36" s="1">
-        <f>VALUE(RIGHT(F36,LEN(F36)-LEN(A36)))</f>
+        <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
-        <f>LEN(E36)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -30327,22 +30311,22 @@
         <v>M</v>
       </c>
       <c r="B37" s="1">
-        <f>VALUE(RIGHT(F37,LEN(F37)-LEN(A37)))</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
-        <f>LEN(E37)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24.95" customHeight="1">
@@ -30351,12 +30335,12 @@
         <v>M</v>
       </c>
       <c r="B38" s="1">
-        <f>VALUE(RIGHT(F38,LEN(F38)-LEN(A38)))</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
-        <f>LEN(E38)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -30375,12 +30359,12 @@
         <v>M</v>
       </c>
       <c r="B39" s="1">
-        <f>VALUE(RIGHT(F39,LEN(F39)-LEN(A39)))</f>
+        <f t="shared" si="0"/>
         <v>1.7</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
-        <f>LEN(E39)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -30399,12 +30383,12 @@
         <v>M</v>
       </c>
       <c r="B40" s="1">
-        <f>VALUE(RIGHT(F40,LEN(F40)-LEN(A40)))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
-        <f>LEN(E40)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E40" s="6" t="s">
@@ -30423,12 +30407,12 @@
         <v>M</v>
       </c>
       <c r="B41" s="1">
-        <f>VALUE(RIGHT(F41,LEN(F41)-LEN(A41)))</f>
+        <f t="shared" si="0"/>
         <v>2.1</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
-        <f>LEN(E41)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -30447,12 +30431,12 @@
         <v>M</v>
       </c>
       <c r="B42" s="1">
-        <f>VALUE(RIGHT(F42,LEN(F42)-LEN(A42)))</f>
+        <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
-        <f>LEN(E42)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -30471,12 +30455,12 @@
         <v>M</v>
       </c>
       <c r="B43" s="1">
-        <f>VALUE(RIGHT(F43,LEN(F43)-LEN(A43)))</f>
+        <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
-        <f>LEN(E43)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E43" s="46" t="s">
@@ -30495,12 +30479,12 @@
         <v>M</v>
       </c>
       <c r="B44" s="1">
-        <f>VALUE(RIGHT(F44,LEN(F44)-LEN(A44)))</f>
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
-        <f>LEN(E44)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -30519,12 +30503,12 @@
         <v>M</v>
       </c>
       <c r="B45" s="1">
-        <f>VALUE(RIGHT(F45,LEN(F45)-LEN(A45)))</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
-        <f>LEN(E45)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E45" s="6" t="s">
@@ -30543,12 +30527,12 @@
         <v>M</v>
       </c>
       <c r="B46" s="1">
-        <f>VALUE(RIGHT(F46,LEN(F46)-LEN(A46)))</f>
+        <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
-        <f>LEN(E46)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E46" s="8" t="s">
@@ -30567,12 +30551,12 @@
         <v>M</v>
       </c>
       <c r="B47" s="1">
-        <f>VALUE(RIGHT(F47,LEN(F47)-LEN(A47)))</f>
+        <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
-        <f>LEN(E47)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E47" s="5" t="s">
@@ -30591,12 +30575,12 @@
         <v>M</v>
       </c>
       <c r="B48" s="1">
-        <f>VALUE(RIGHT(F48,LEN(F48)-LEN(A48)))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
-        <f>LEN(E48)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E48" s="8" t="s">
@@ -30615,12 +30599,12 @@
         <v>M</v>
       </c>
       <c r="B49" s="1">
-        <f>VALUE(RIGHT(F49,LEN(F49)-LEN(A49)))</f>
+        <f t="shared" si="0"/>
         <v>3.1</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
-        <f>LEN(E49)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -30639,12 +30623,12 @@
         <v>M</v>
       </c>
       <c r="B50" s="1">
-        <f>VALUE(RIGHT(F50,LEN(F50)-LEN(A50)))</f>
+        <f t="shared" si="0"/>
         <v>3.4</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
-        <f>LEN(E50)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E50" s="8" t="s">
@@ -30663,12 +30647,12 @@
         <v>M</v>
       </c>
       <c r="B51" s="1">
-        <f>VALUE(RIGHT(F51,LEN(F51)-LEN(A51)))</f>
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
-        <f>LEN(E51)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -30687,22 +30671,22 @@
         <v>M</v>
       </c>
       <c r="B52" s="1">
-        <f>VALUE(RIGHT(F52,LEN(F52)-LEN(A52)))</f>
+        <f t="shared" si="0"/>
         <v>3.7</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
-        <f>LEN(E52)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>197</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="24.95" customHeight="1">
@@ -30711,22 +30695,22 @@
         <v>M</v>
       </c>
       <c r="B53" s="1">
-        <f>VALUE(RIGHT(F53,LEN(F53)-LEN(A53)))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
-        <f>LEN(E53)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>765</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="24.95" customHeight="1">
@@ -30735,22 +30719,22 @@
         <v>M</v>
       </c>
       <c r="B54" s="1">
-        <f>VALUE(RIGHT(F54,LEN(F54)-LEN(A54)))</f>
+        <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
-        <f>LEN(E54)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>203</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="24.95" customHeight="1">
@@ -30759,22 +30743,22 @@
         <v>M</v>
       </c>
       <c r="B55" s="1">
-        <f>VALUE(RIGHT(F55,LEN(F55)-LEN(A55)))</f>
+        <f t="shared" si="0"/>
         <v>4.2</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
-        <f>LEN(E55)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>207</v>
       </c>
       <c r="G55" s="26" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="24.95" customHeight="1">
@@ -30783,22 +30767,22 @@
         <v>M</v>
       </c>
       <c r="B56" s="1">
-        <f>VALUE(RIGHT(F56,LEN(F56)-LEN(A56)))</f>
+        <f t="shared" si="0"/>
         <v>4.3</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
-        <f>LEN(E56)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>211</v>
       </c>
       <c r="G56" s="26" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="24.95" customHeight="1">
@@ -30807,22 +30791,22 @@
         <v>M</v>
       </c>
       <c r="B57" s="1">
-        <f>VALUE(RIGHT(F57,LEN(F57)-LEN(A57)))</f>
+        <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
-        <f>LEN(E57)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="24.95" customHeight="1">
@@ -30831,22 +30815,22 @@
         <v>M</v>
       </c>
       <c r="B58" s="1">
-        <f>VALUE(RIGHT(F58,LEN(F58)-LEN(A58)))</f>
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
-        <f>LEN(E58)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>219</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="24.95" customHeight="1">
@@ -30855,12 +30839,12 @@
         <v>M</v>
       </c>
       <c r="B59" s="1">
-        <f>VALUE(RIGHT(F59,LEN(F59)-LEN(A59)))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
-        <f>LEN(E59)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E59" s="46" t="s">
@@ -30879,12 +30863,12 @@
         <v>M</v>
       </c>
       <c r="B60" s="1">
-        <f>VALUE(RIGHT(F60,LEN(F60)-LEN(A60)))</f>
+        <f t="shared" si="0"/>
         <v>10.1</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
-        <f>LEN(E60)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E60" s="46" t="s">
@@ -30903,12 +30887,12 @@
         <v>M</v>
       </c>
       <c r="B61" s="1">
-        <f>VALUE(RIGHT(F61,LEN(F61)-LEN(A61)))</f>
+        <f t="shared" si="0"/>
         <v>10.199999999999999</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
-        <f>LEN(E61)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E61" s="46" t="s">
@@ -30927,12 +30911,12 @@
         <v>M</v>
       </c>
       <c r="B62" s="1">
-        <f>VALUE(RIGHT(F62,LEN(F62)-LEN(A62)))</f>
+        <f t="shared" si="0"/>
         <v>10.3</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1">
-        <f>LEN(E62)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -30951,12 +30935,12 @@
         <v>M</v>
       </c>
       <c r="B63" s="1">
-        <f>VALUE(RIGHT(F63,LEN(F63)-LEN(A63)))</f>
+        <f t="shared" si="0"/>
         <v>10.4</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1">
-        <f>LEN(E63)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -30975,12 +30959,12 @@
         <v>M</v>
       </c>
       <c r="B64" s="1">
-        <f>VALUE(RIGHT(F64,LEN(F64)-LEN(A64)))</f>
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1">
-        <f>LEN(E64)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -30999,12 +30983,12 @@
         <v>M</v>
       </c>
       <c r="B65" s="1">
-        <f>VALUE(RIGHT(F65,LEN(F65)-LEN(A65)))</f>
+        <f t="shared" si="0"/>
         <v>10.6</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1">
-        <f>LEN(E65)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -31023,12 +31007,12 @@
         <v>M</v>
       </c>
       <c r="B66" s="1">
-        <f>VALUE(RIGHT(F66,LEN(F66)-LEN(A66)))</f>
+        <f t="shared" ref="B66:B129" si="2">VALUE(RIGHT(F66,LEN(F66)-LEN(A66)))</f>
         <v>10.7</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1">
-        <f>LEN(E66)</f>
+        <f t="shared" ref="D66:D129" si="3">LEN(E66)</f>
         <v>19</v>
       </c>
       <c r="E66" s="8" t="s">
@@ -31047,12 +31031,12 @@
         <v>M</v>
       </c>
       <c r="B67" s="1">
-        <f>VALUE(RIGHT(F67,LEN(F67)-LEN(A67)))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1">
-        <f>LEN(E67)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -31071,12 +31055,12 @@
         <v>M</v>
       </c>
       <c r="B68" s="1">
-        <f>VALUE(RIGHT(F68,LEN(F68)-LEN(A68)))</f>
+        <f t="shared" si="2"/>
         <v>11.1</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1">
-        <f>LEN(E68)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -31095,16 +31079,16 @@
         <v>M</v>
       </c>
       <c r="B69" s="1">
-        <f>VALUE(RIGHT(F69,LEN(F69)-LEN(A69)))</f>
+        <f t="shared" si="2"/>
         <v>11.2</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1">
-        <f>LEN(E69)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>375</v>
@@ -31119,12 +31103,12 @@
         <v>M</v>
       </c>
       <c r="B70" s="1">
-        <f>VALUE(RIGHT(F70,LEN(F70)-LEN(A70)))</f>
+        <f t="shared" si="2"/>
         <v>11.3</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1">
-        <f>LEN(E70)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -31143,16 +31127,16 @@
         <v>M</v>
       </c>
       <c r="B71" s="1">
-        <f>VALUE(RIGHT(F71,LEN(F71)-LEN(A71)))</f>
+        <f t="shared" si="2"/>
         <v>11.4</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1">
-        <f>LEN(E71)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>379</v>
@@ -31167,22 +31151,22 @@
         <v>M</v>
       </c>
       <c r="B72" s="1">
-        <f>VALUE(RIGHT(F72,LEN(F72)-LEN(A72)))</f>
+        <f t="shared" si="2"/>
         <v>11.5</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
-        <f>LEN(E72)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>381</v>
       </c>
       <c r="G72" s="41" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="24.95" customHeight="1">
@@ -31191,22 +31175,22 @@
         <v>M</v>
       </c>
       <c r="B73" s="1">
-        <f>VALUE(RIGHT(F73,LEN(F73)-LEN(A73)))</f>
+        <f t="shared" si="2"/>
         <v>11.6</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1">
-        <f>LEN(E73)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>383</v>
       </c>
       <c r="G73" s="41" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="24.95" customHeight="1">
@@ -31215,22 +31199,22 @@
         <v>M</v>
       </c>
       <c r="B74" s="1">
-        <f>VALUE(RIGHT(F74,LEN(F74)-LEN(A74)))</f>
+        <f t="shared" si="2"/>
         <v>11.7</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1">
-        <f>LEN(E74)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>385</v>
       </c>
       <c r="G74" s="41" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24.95" customHeight="1">
@@ -31239,22 +31223,22 @@
         <v>M</v>
       </c>
       <c r="B75" s="1">
-        <f>VALUE(RIGHT(F75,LEN(F75)-LEN(A75)))</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1">
-        <f>LEN(E75)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>1658</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="41" t="s">
         <v>1659</v>
-      </c>
-      <c r="G75" s="41" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24.95" customHeight="1">
@@ -31263,22 +31247,22 @@
         <v>M</v>
       </c>
       <c r="B76" s="1">
-        <f>VALUE(RIGHT(F76,LEN(F76)-LEN(A76)))</f>
+        <f t="shared" si="2"/>
         <v>12.1</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
-        <f>LEN(E76)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>387</v>
       </c>
       <c r="G76" s="41" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="24.95" customHeight="1">
@@ -31287,22 +31271,22 @@
         <v>M</v>
       </c>
       <c r="B77" s="1">
-        <f>VALUE(RIGHT(F77,LEN(F77)-LEN(A77)))</f>
+        <f t="shared" si="2"/>
         <v>12.2</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1">
-        <f>LEN(E77)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>389</v>
       </c>
       <c r="G77" s="41" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="24.95" customHeight="1">
@@ -31311,22 +31295,22 @@
         <v>M</v>
       </c>
       <c r="B78" s="1">
-        <f>VALUE(RIGHT(F78,LEN(F78)-LEN(A78)))</f>
+        <f t="shared" si="2"/>
         <v>12.3</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
-        <f>LEN(E78)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>390</v>
       </c>
       <c r="G78" s="41" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="24.95" customHeight="1">
@@ -31335,12 +31319,12 @@
         <v>M</v>
       </c>
       <c r="B79" s="1">
-        <f>VALUE(RIGHT(F79,LEN(F79)-LEN(A79)))</f>
+        <f t="shared" si="2"/>
         <v>20.6</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
-        <f>LEN(E79)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E79" s="46" t="s">
@@ -31359,16 +31343,16 @@
         <v>M</v>
       </c>
       <c r="B80" s="1">
-        <f>VALUE(RIGHT(F80,LEN(F80)-LEN(A80)))</f>
+        <f t="shared" si="2"/>
         <v>20.7</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1">
-        <f>LEN(E80)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>1323</v>
@@ -31383,19 +31367,19 @@
         <v>M</v>
       </c>
       <c r="B81" s="1">
-        <f>VALUE(RIGHT(F81,LEN(F81)-LEN(A81)))</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
-        <f>LEN(E81)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="E81" s="46" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="G81" s="48" t="s">
         <v>1297</v>
@@ -31407,19 +31391,19 @@
         <v>M</v>
       </c>
       <c r="B82" s="1">
-        <f>VALUE(RIGHT(F82,LEN(F82)-LEN(A82)))</f>
+        <f t="shared" si="2"/>
         <v>21.1</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1">
-        <f>LEN(E82)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>1502</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>1077</v>
@@ -31431,19 +31415,19 @@
         <v>M</v>
       </c>
       <c r="B83" s="1">
-        <f>VALUE(RIGHT(F83,LEN(F83)-LEN(A83)))</f>
+        <f t="shared" si="2"/>
         <v>21.2</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1">
-        <f>LEN(E83)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>1503</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>1080</v>
@@ -31455,12 +31439,12 @@
         <v>T</v>
       </c>
       <c r="B84" s="1">
-        <f>VALUE(RIGHT(F84,LEN(F84)-LEN(A84)))</f>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1">
-        <f>LEN(E84)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -31479,12 +31463,12 @@
         <v>T</v>
       </c>
       <c r="B85" s="1">
-        <f>VALUE(RIGHT(F85,LEN(F85)-LEN(A85)))</f>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1">
-        <f>LEN(E85)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -31494,7 +31478,7 @@
         <v>40</v>
       </c>
       <c r="G85" s="26" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="24.95" customHeight="1">
@@ -31503,22 +31487,22 @@
         <v>T</v>
       </c>
       <c r="B86" s="1">
-        <f>VALUE(RIGHT(F86,LEN(F86)-LEN(A86)))</f>
+        <f t="shared" si="2"/>
         <v>103</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1">
-        <f>LEN(E86)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>54</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="24.95" customHeight="1">
@@ -31527,12 +31511,12 @@
         <v>T</v>
       </c>
       <c r="B87" s="1">
-        <f>VALUE(RIGHT(F87,LEN(F87)-LEN(A87)))</f>
+        <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1">
-        <f>LEN(E87)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -31551,12 +31535,12 @@
         <v>T</v>
       </c>
       <c r="B88" s="1">
-        <f>VALUE(RIGHT(F88,LEN(F88)-LEN(A88)))</f>
+        <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1">
-        <f>LEN(E88)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -31575,12 +31559,12 @@
         <v>T</v>
       </c>
       <c r="B89" s="1">
-        <f>VALUE(RIGHT(F89,LEN(F89)-LEN(A89)))</f>
+        <f t="shared" si="2"/>
         <v>106</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1">
-        <f>LEN(E89)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E89" s="6" t="s">
@@ -31599,12 +31583,12 @@
         <v>T</v>
       </c>
       <c r="B90" s="1">
-        <f>VALUE(RIGHT(F90,LEN(F90)-LEN(A90)))</f>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1">
-        <f>LEN(E90)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -31623,12 +31607,12 @@
         <v>T</v>
       </c>
       <c r="B91" s="1">
-        <f>VALUE(RIGHT(F91,LEN(F91)-LEN(A91)))</f>
+        <f t="shared" si="2"/>
         <v>110</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1">
-        <f>LEN(E91)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -31647,12 +31631,12 @@
         <v>T</v>
       </c>
       <c r="B92" s="1">
-        <f>VALUE(RIGHT(F92,LEN(F92)-LEN(A92)))</f>
+        <f t="shared" si="2"/>
         <v>111</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1">
-        <f>LEN(E92)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -31671,12 +31655,12 @@
         <v>T</v>
       </c>
       <c r="B93" s="1">
-        <f>VALUE(RIGHT(F93,LEN(F93)-LEN(A93)))</f>
+        <f t="shared" si="2"/>
         <v>112</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1">
-        <f>LEN(E93)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E93" s="6" t="s">
@@ -31695,12 +31679,12 @@
         <v>T</v>
       </c>
       <c r="B94" s="1">
-        <f>VALUE(RIGHT(F94,LEN(F94)-LEN(A94)))</f>
+        <f t="shared" si="2"/>
         <v>113</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1">
-        <f>LEN(E94)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -31719,12 +31703,12 @@
         <v>T</v>
       </c>
       <c r="B95" s="1">
-        <f>VALUE(RIGHT(F95,LEN(F95)-LEN(A95)))</f>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1">
-        <f>LEN(E95)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -31734,7 +31718,7 @@
         <v>136</v>
       </c>
       <c r="G95" s="26" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="24.95" customHeight="1">
@@ -31743,12 +31727,12 @@
         <v>T</v>
       </c>
       <c r="B96" s="1">
-        <f>VALUE(RIGHT(F96,LEN(F96)-LEN(A96)))</f>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1">
-        <f>LEN(E96)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -31767,12 +31751,12 @@
         <v>T</v>
       </c>
       <c r="B97" s="1">
-        <f>VALUE(RIGHT(F97,LEN(F97)-LEN(A97)))</f>
+        <f t="shared" si="2"/>
         <v>118</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1">
-        <f>LEN(E97)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -31791,12 +31775,12 @@
         <v>T</v>
       </c>
       <c r="B98" s="1">
-        <f>VALUE(RIGHT(F98,LEN(F98)-LEN(A98)))</f>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
-        <f>LEN(E98)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -31815,12 +31799,12 @@
         <v>T</v>
       </c>
       <c r="B99" s="1">
-        <f>VALUE(RIGHT(F99,LEN(F99)-LEN(A99)))</f>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
-        <f>LEN(E99)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -31839,22 +31823,22 @@
         <v>T</v>
       </c>
       <c r="B100" s="1">
-        <f>VALUE(RIGHT(F100,LEN(F100)-LEN(A100)))</f>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
-        <f>LEN(E100)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="F100" s="63" t="s">
         <v>156</v>
       </c>
       <c r="G100" s="71" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="24.95" customHeight="1">
@@ -31863,22 +31847,22 @@
         <v>T</v>
       </c>
       <c r="B101" s="1">
-        <f>VALUE(RIGHT(F101,LEN(F101)-LEN(A101)))</f>
+        <f t="shared" si="2"/>
         <v>122</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
-        <f>LEN(E101)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F101" s="63" t="s">
         <v>160</v>
       </c>
       <c r="G101" s="71" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="24.95" customHeight="1">
@@ -31887,22 +31871,22 @@
         <v>T</v>
       </c>
       <c r="B102" s="1">
-        <f>VALUE(RIGHT(F102,LEN(F102)-LEN(A102)))</f>
+        <f t="shared" si="2"/>
         <v>123</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
-        <f>LEN(E102)</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="F102" s="63" t="s">
         <v>164</v>
       </c>
       <c r="G102" s="71" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="24.95" customHeight="1">
@@ -31911,22 +31895,22 @@
         <v>V</v>
       </c>
       <c r="B103" s="1">
-        <f>VALUE(RIGHT(F103,LEN(F103)-LEN(A103)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
-        <f>LEN(E103)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="F103" s="63" t="s">
         <v>803</v>
       </c>
       <c r="G103" s="71" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="24.95" customHeight="1">
@@ -31935,12 +31919,12 @@
         <v>V</v>
       </c>
       <c r="B104" s="1">
-        <f>VALUE(RIGHT(F104,LEN(F104)-LEN(A104)))</f>
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
-        <f>LEN(E104)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -31959,12 +31943,12 @@
         <v>V</v>
       </c>
       <c r="B105" s="1">
-        <f>VALUE(RIGHT(F105,LEN(F105)-LEN(A105)))</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
-        <f>LEN(E105)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E105" s="46" t="s">
@@ -31983,12 +31967,12 @@
         <v>V</v>
       </c>
       <c r="B106" s="1">
-        <f>VALUE(RIGHT(F106,LEN(F106)-LEN(A106)))</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
-        <f>LEN(E106)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E106" s="46" t="s">
@@ -32007,22 +31991,22 @@
         <v>V</v>
       </c>
       <c r="B107" s="1">
-        <f>VALUE(RIGHT(F107,LEN(F107)-LEN(A107)))</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
-        <f>LEN(E107)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>560</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="24.95" customHeight="1">
@@ -32031,12 +32015,12 @@
         <v>V</v>
       </c>
       <c r="B108" s="1">
-        <f>VALUE(RIGHT(F108,LEN(F108)-LEN(A108)))</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
-        <f>LEN(E108)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -32055,12 +32039,12 @@
         <v>V</v>
       </c>
       <c r="B109" s="1">
-        <f>VALUE(RIGHT(F109,LEN(F109)-LEN(A109)))</f>
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
-        <f>LEN(E109)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="E109" s="1" t="s">
@@ -32079,12 +32063,12 @@
         <v>V</v>
       </c>
       <c r="B110" s="1">
-        <f>VALUE(RIGHT(F110,LEN(F110)-LEN(A110)))</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
-        <f>LEN(E110)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -32103,12 +32087,12 @@
         <v>V</v>
       </c>
       <c r="B111" s="1">
-        <f>VALUE(RIGHT(F111,LEN(F111)-LEN(A111)))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
-        <f>LEN(E111)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="E111" s="46" t="s">
@@ -32127,12 +32111,12 @@
         <v>V</v>
       </c>
       <c r="B112" s="1">
-        <f>VALUE(RIGHT(F112,LEN(F112)-LEN(A112)))</f>
+        <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
-        <f>LEN(E112)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E112" s="1" t="s">
@@ -32151,22 +32135,22 @@
         <v>V</v>
       </c>
       <c r="B113" s="1">
-        <f>VALUE(RIGHT(F113,LEN(F113)-LEN(A113)))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
-        <f>LEN(E113)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F113" s="46" t="s">
         <v>823</v>
       </c>
       <c r="G113" s="26" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="24.95" customHeight="1">
@@ -32175,16 +32159,16 @@
         <v>V</v>
       </c>
       <c r="B114" s="1">
-        <f>VALUE(RIGHT(F114,LEN(F114)-LEN(A114)))</f>
+        <f t="shared" si="2"/>
         <v>2.1</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
-        <f>LEN(E114)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F114" s="46" t="s">
         <v>571</v>
@@ -32199,16 +32183,16 @@
         <v>V</v>
       </c>
       <c r="B115" s="1">
-        <f>VALUE(RIGHT(F115,LEN(F115)-LEN(A115)))</f>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
-        <f>LEN(E115)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="F115" s="46" t="s">
         <v>572</v>
@@ -32223,12 +32207,12 @@
         <v>V</v>
       </c>
       <c r="B116" s="1">
-        <f>VALUE(RIGHT(F116,LEN(F116)-LEN(A116)))</f>
+        <f t="shared" si="2"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
-        <f>LEN(E116)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="E116" s="1" t="s">
@@ -32247,12 +32231,12 @@
         <v>V</v>
       </c>
       <c r="B117" s="1">
-        <f>VALUE(RIGHT(F117,LEN(F117)-LEN(A117)))</f>
+        <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
-        <f>LEN(E117)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E117" s="1" t="s">
@@ -32271,12 +32255,12 @@
         <v>V</v>
       </c>
       <c r="B118" s="1">
-        <f>VALUE(RIGHT(F118,LEN(F118)-LEN(A118)))</f>
+        <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
-        <f>LEN(E118)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E118" s="1" t="s">
@@ -32295,12 +32279,12 @@
         <v>V</v>
       </c>
       <c r="B119" s="1">
-        <f>VALUE(RIGHT(F119,LEN(F119)-LEN(A119)))</f>
+        <f t="shared" si="2"/>
         <v>2.6</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
-        <f>LEN(E119)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E119" s="1" t="s">
@@ -32319,16 +32303,16 @@
         <v>V</v>
       </c>
       <c r="B120" s="1">
-        <f>VALUE(RIGHT(F120,LEN(F120)-LEN(A120)))</f>
+        <f t="shared" si="2"/>
         <v>2.7</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
-        <f>LEN(E120)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>577</v>
@@ -32343,19 +32327,19 @@
         <v>V</v>
       </c>
       <c r="B121" s="1">
-        <f>VALUE(RIGHT(F121,LEN(F121)-LEN(A121)))</f>
+        <f t="shared" si="2"/>
         <v>1620</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
-        <f>LEN(E121)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>1594</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="G121" s="26" t="s">
         <v>1595</v>
@@ -32367,12 +32351,12 @@
         <v>V</v>
       </c>
       <c r="B122" s="1">
-        <f>VALUE(RIGHT(F122,LEN(F122)-LEN(A122)))</f>
+        <f t="shared" si="2"/>
         <v>1620.1</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
-        <f>LEN(E122)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="E122" s="1" t="s">
@@ -32391,12 +32375,12 @@
         <v>V</v>
       </c>
       <c r="B123" s="1">
-        <f>VALUE(RIGHT(F123,LEN(F123)-LEN(A123)))</f>
+        <f t="shared" si="2"/>
         <v>1620.2</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
-        <f>LEN(E123)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E123" s="1" t="s">
@@ -32415,14 +32399,14 @@
         <v>V</v>
       </c>
       <c r="B124" s="1">
-        <f>VALUE(RIGHT(F124,LEN(F124)-LEN(A124)))</f>
+        <f t="shared" si="2"/>
         <v>1620.3</v>
       </c>
       <c r="C124" s="1">
         <v>300</v>
       </c>
       <c r="D124" s="1">
-        <f>LEN(E124)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="E124" s="1" t="s">
@@ -32441,12 +32425,12 @@
         <v>V</v>
       </c>
       <c r="B125" s="1">
-        <f>VALUE(RIGHT(F125,LEN(F125)-LEN(A125)))</f>
+        <f t="shared" si="2"/>
         <v>1620.4</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
-        <f>LEN(E125)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="E125" s="46" t="s">
@@ -32456,7 +32440,7 @@
         <v>1588</v>
       </c>
       <c r="G125" s="26" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="24.95" customHeight="1">
@@ -32465,14 +32449,14 @@
         <v>V</v>
       </c>
       <c r="B126" s="1">
-        <f>VALUE(RIGHT(F126,LEN(F126)-LEN(A126)))</f>
+        <f t="shared" si="2"/>
         <v>1620.5</v>
       </c>
       <c r="C126" s="1">
         <v>360</v>
       </c>
       <c r="D126" s="1">
-        <f>LEN(E126)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E126" s="1" t="s">
@@ -32482,7 +32466,7 @@
         <v>1589</v>
       </c>
       <c r="G126" s="26" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="24.95" customHeight="1">
@@ -32491,14 +32475,14 @@
         <v>V</v>
       </c>
       <c r="B127" s="1">
-        <f>VALUE(RIGHT(F127,LEN(F127)-LEN(A127)))</f>
+        <f t="shared" si="2"/>
         <v>1620.6</v>
       </c>
       <c r="C127" s="1">
         <v>364</v>
       </c>
       <c r="D127" s="1">
-        <f>LEN(E127)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E127" s="1" t="s">
@@ -32508,7 +32492,7 @@
         <v>1590</v>
       </c>
       <c r="G127" s="26" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="24.95" customHeight="1">
@@ -32517,14 +32501,14 @@
         <v>V</v>
       </c>
       <c r="B128" s="1">
-        <f>VALUE(RIGHT(F128,LEN(F128)-LEN(A128)))</f>
+        <f t="shared" si="2"/>
         <v>1620.7</v>
       </c>
       <c r="C128" s="1">
         <v>368</v>
       </c>
       <c r="D128" s="1">
-        <f>LEN(E128)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E128" s="1" t="s">
@@ -32534,7 +32518,7 @@
         <v>1591</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="24.95" customHeight="1">
@@ -32543,14 +32527,14 @@
         <v>V</v>
       </c>
       <c r="B129" s="1">
-        <f>VALUE(RIGHT(F129,LEN(F129)-LEN(A129)))</f>
+        <f t="shared" si="2"/>
         <v>1621</v>
       </c>
       <c r="C129" s="1">
         <v>372</v>
       </c>
       <c r="D129" s="1">
-        <f>LEN(E129)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E129" s="1" t="s">
@@ -32560,7 +32544,7 @@
         <v>1592</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="24.95" customHeight="1">
@@ -32569,14 +32553,14 @@
         <v>V</v>
       </c>
       <c r="B130" s="1">
-        <f>VALUE(RIGHT(F130,LEN(F130)-LEN(A130)))</f>
+        <f t="shared" ref="B130:B193" si="4">VALUE(RIGHT(F130,LEN(F130)-LEN(A130)))</f>
         <v>1621.1</v>
       </c>
       <c r="C130" s="1">
         <v>304</v>
       </c>
       <c r="D130" s="1">
-        <f>LEN(E130)</f>
+        <f t="shared" ref="D130:D193" si="5">LEN(E130)</f>
         <v>21</v>
       </c>
       <c r="E130" s="1" t="s">
@@ -32586,7 +32570,7 @@
         <v>1593</v>
       </c>
       <c r="G130" s="26" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="24.95" customHeight="1">
@@ -32595,14 +32579,14 @@
         <v>VB</v>
       </c>
       <c r="B131" s="1">
-        <f>VALUE(RIGHT(F131,LEN(F131)-LEN(A131)))</f>
+        <f t="shared" si="4"/>
         <v>800</v>
       </c>
       <c r="C131" s="1">
         <v>376</v>
       </c>
       <c r="D131" s="1">
-        <f>LEN(E131)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="E131" s="1" t="s">
@@ -32621,14 +32605,14 @@
         <v>VB</v>
       </c>
       <c r="B132" s="1">
-        <f>VALUE(RIGHT(F132,LEN(F132)-LEN(A132)))</f>
+        <f t="shared" si="4"/>
         <v>802</v>
       </c>
       <c r="C132" s="1">
         <v>380</v>
       </c>
       <c r="D132" s="1">
-        <f>LEN(E132)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E132" s="1" t="s">
@@ -32647,14 +32631,14 @@
         <v>VB</v>
       </c>
       <c r="B133" s="1">
-        <f>VALUE(RIGHT(F133,LEN(F133)-LEN(A133)))</f>
+        <f t="shared" si="4"/>
         <v>804</v>
       </c>
       <c r="C133" s="1">
         <v>384</v>
       </c>
       <c r="D133" s="1">
-        <f>LEN(E133)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="E133" s="1" t="s">
@@ -32673,14 +32657,14 @@
         <v>VB</v>
       </c>
       <c r="B134" s="1">
-        <f>VALUE(RIGHT(F134,LEN(F134)-LEN(A134)))</f>
+        <f t="shared" si="4"/>
         <v>806</v>
       </c>
       <c r="C134" s="1">
         <v>388</v>
       </c>
       <c r="D134" s="1">
-        <f>LEN(E134)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="E134" s="1" t="s">
@@ -32699,14 +32683,14 @@
         <v>VB</v>
       </c>
       <c r="B135" s="1">
-        <f>VALUE(RIGHT(F135,LEN(F135)-LEN(A135)))</f>
+        <f t="shared" si="4"/>
         <v>808</v>
       </c>
       <c r="C135" s="1">
         <v>392</v>
       </c>
       <c r="D135" s="1">
-        <f>LEN(E135)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="E135" s="1" t="s">
@@ -32725,14 +32709,14 @@
         <v>VB</v>
       </c>
       <c r="B136" s="1">
-        <f>VALUE(RIGHT(F136,LEN(F136)-LEN(A136)))</f>
+        <f t="shared" si="4"/>
         <v>810</v>
       </c>
       <c r="C136" s="1">
         <v>396</v>
       </c>
       <c r="D136" s="1">
-        <f>LEN(E136)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="E136" s="1" t="s">
@@ -32751,22 +32735,22 @@
         <v>VB</v>
       </c>
       <c r="B137" s="1">
-        <f>VALUE(RIGHT(F137,LEN(F137)-LEN(A137)))</f>
+        <f t="shared" si="4"/>
         <v>812</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
-        <f>LEN(E137)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E137" s="46" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F137" s="7" t="s">
         <v>1805</v>
       </c>
-      <c r="F137" s="7" t="s">
+      <c r="G137" s="26" t="s">
         <v>1806</v>
-      </c>
-      <c r="G137" s="26" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="24.95" customHeight="1">
@@ -32775,14 +32759,14 @@
         <v>VD</v>
       </c>
       <c r="B138" s="1">
-        <f>VALUE(RIGHT(F138,LEN(F138)-LEN(A138)))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="C138" s="1">
         <v>400</v>
       </c>
       <c r="D138" s="1">
-        <f>LEN(E138)</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="E138" s="1" t="s">
@@ -32801,14 +32785,14 @@
         <v>VD</v>
       </c>
       <c r="B139" s="1">
-        <f>VALUE(RIGHT(F139,LEN(F139)-LEN(A139)))</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="C139" s="1">
         <v>404</v>
       </c>
       <c r="D139" s="1">
-        <f>LEN(E139)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E139" s="1" t="s">
@@ -32827,14 +32811,14 @@
         <v>VD</v>
       </c>
       <c r="B140" s="1">
-        <f>VALUE(RIGHT(F140,LEN(F140)-LEN(A140)))</f>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="C140" s="1">
         <v>408</v>
       </c>
       <c r="D140" s="1">
-        <f>LEN(E140)</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="E140" s="1" t="s">
@@ -32853,14 +32837,14 @@
         <v>VD</v>
       </c>
       <c r="B141" s="1">
-        <f>VALUE(RIGHT(F141,LEN(F141)-LEN(A141)))</f>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="C141" s="1">
         <v>308</v>
       </c>
       <c r="D141" s="1">
-        <f>LEN(E141)</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="E141" s="1" t="s">
@@ -32879,18 +32863,18 @@
         <v>VD</v>
       </c>
       <c r="B142" s="1">
-        <f>VALUE(RIGHT(F142,LEN(F142)-LEN(A142)))</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="C142" s="1">
         <v>412</v>
       </c>
       <c r="D142" s="1">
-        <f>LEN(E142)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>1348</v>
@@ -32905,18 +32889,18 @@
         <v>VD</v>
       </c>
       <c r="B143" s="1">
-        <f>VALUE(RIGHT(F143,LEN(F143)-LEN(A143)))</f>
+        <f t="shared" si="4"/>
         <v>44</v>
       </c>
       <c r="C143" s="1">
         <v>416</v>
       </c>
       <c r="D143" s="1">
-        <f>LEN(E143)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>1349</v>
@@ -32931,14 +32915,14 @@
         <v>VD</v>
       </c>
       <c r="B144" s="1">
-        <f>VALUE(RIGHT(F144,LEN(F144)-LEN(A144)))</f>
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="C144" s="1">
         <v>420</v>
       </c>
       <c r="D144" s="1">
-        <f>LEN(E144)</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="E144" s="1" t="s">
@@ -32957,14 +32941,14 @@
         <v>VD</v>
       </c>
       <c r="B145" s="1">
-        <f>VALUE(RIGHT(F145,LEN(F145)-LEN(A145)))</f>
+        <f t="shared" si="4"/>
         <v>52</v>
       </c>
       <c r="C145" s="1">
         <v>424</v>
       </c>
       <c r="D145" s="1">
-        <f>LEN(E145)</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="E145" s="1" t="s">
@@ -32983,14 +32967,14 @@
         <v>VD</v>
       </c>
       <c r="B146" s="1">
-        <f>VALUE(RIGHT(F146,LEN(F146)-LEN(A146)))</f>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="C146" s="1">
         <v>428</v>
       </c>
       <c r="D146" s="1">
-        <f>LEN(E146)</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="E146" s="1" t="s">
@@ -33009,14 +32993,14 @@
         <v>VD</v>
       </c>
       <c r="B147" s="1">
-        <f>VALUE(RIGHT(F147,LEN(F147)-LEN(A147)))</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="C147" s="1">
         <v>432</v>
       </c>
       <c r="D147" s="1">
-        <f>LEN(E147)</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="E147" s="1" t="s">
@@ -33035,14 +33019,14 @@
         <v>VD</v>
       </c>
       <c r="B148" s="1">
-        <f>VALUE(RIGHT(F148,LEN(F148)-LEN(A148)))</f>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="C148" s="1">
         <v>436</v>
       </c>
       <c r="D148" s="1">
-        <f>LEN(E148)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="E148" s="1" t="s">
@@ -33061,12 +33045,12 @@
         <v>VD</v>
       </c>
       <c r="B149" s="1">
-        <f>VALUE(RIGHT(F149,LEN(F149)-LEN(A149)))</f>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
-        <f>LEN(E149)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="E149" s="46" t="s">
@@ -33085,24 +33069,24 @@
         <v>VD</v>
       </c>
       <c r="B150" s="1">
-        <f>VALUE(RIGHT(F150,LEN(F150)-LEN(A150)))</f>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="C150" s="1">
         <v>440</v>
       </c>
       <c r="D150" s="1">
-        <f>LEN(E150)</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="F150" s="7" t="s">
         <v>1360</v>
       </c>
       <c r="G150" s="26" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="24.95" customHeight="1">
@@ -33111,14 +33095,14 @@
         <v>VD</v>
       </c>
       <c r="B151" s="1">
-        <f>VALUE(RIGHT(F151,LEN(F151)-LEN(A151)))</f>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="C151" s="1">
         <v>444</v>
       </c>
       <c r="D151" s="1">
-        <f>LEN(E151)</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="E151" s="1" t="s">
@@ -33137,14 +33121,14 @@
         <v>VD</v>
       </c>
       <c r="B152" s="1">
-        <f>VALUE(RIGHT(F152,LEN(F152)-LEN(A152)))</f>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="C152" s="1">
         <v>312</v>
       </c>
       <c r="D152" s="1">
-        <f>LEN(E152)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E152" s="1" t="s">
@@ -33163,14 +33147,14 @@
         <v>VD</v>
       </c>
       <c r="B153" s="1">
-        <f>VALUE(RIGHT(F153,LEN(F153)-LEN(A153)))</f>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="C153" s="1">
         <v>448</v>
       </c>
       <c r="D153" s="1">
-        <f>LEN(E153)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="E153" s="1" t="s">
@@ -33189,14 +33173,14 @@
         <v>VD</v>
       </c>
       <c r="B154" s="1">
-        <f>VALUE(RIGHT(F154,LEN(F154)-LEN(A154)))</f>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="C154" s="1">
         <v>452</v>
       </c>
       <c r="D154" s="1">
-        <f>LEN(E154)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="E154" s="1" t="s">
@@ -33215,24 +33199,24 @@
         <v>VD</v>
       </c>
       <c r="B155" s="1">
-        <f>VALUE(RIGHT(F155,LEN(F155)-LEN(A155)))</f>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="C155" s="1">
         <v>456</v>
       </c>
       <c r="D155" s="1">
-        <f>LEN(E155)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E155" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>1693</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="G155" s="26" t="s">
         <v>1694</v>
-      </c>
-      <c r="G155" s="26" t="s">
-        <v>1695</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="24.95" customHeight="1">
@@ -33241,24 +33225,24 @@
         <v>VD</v>
       </c>
       <c r="B156" s="1">
-        <f>VALUE(RIGHT(F156,LEN(F156)-LEN(A156)))</f>
+        <f t="shared" si="4"/>
         <v>96</v>
       </c>
       <c r="C156" s="1">
         <v>460</v>
       </c>
       <c r="D156" s="1">
-        <f>LEN(E156)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E156" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>1696</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="G156" s="26" t="s">
         <v>1697</v>
-      </c>
-      <c r="G156" s="26" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="24.95" customHeight="1">
@@ -33267,24 +33251,24 @@
         <v>VD</v>
       </c>
       <c r="B157" s="1">
-        <f>VALUE(RIGHT(F157,LEN(F157)-LEN(A157)))</f>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="C157" s="1">
         <v>464</v>
       </c>
       <c r="D157" s="1">
-        <f>LEN(E157)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E157" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="F157" s="1" t="s">
+      <c r="G157" s="26" t="s">
         <v>1809</v>
-      </c>
-      <c r="G157" s="26" t="s">
-        <v>1810</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="24.95" customHeight="1">
@@ -33293,24 +33277,24 @@
         <v>VD</v>
       </c>
       <c r="B158" s="1">
-        <f>VALUE(RIGHT(F158,LEN(F158)-LEN(A158)))</f>
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
       <c r="C158" s="1">
         <v>468</v>
       </c>
       <c r="D158" s="1">
-        <f>LEN(E158)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>1811</v>
       </c>
-      <c r="F158" s="1" t="s">
+      <c r="G158" s="26" t="s">
         <v>1812</v>
-      </c>
-      <c r="G158" s="26" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="24.95" customHeight="1">
@@ -33319,24 +33303,24 @@
         <v>VD</v>
       </c>
       <c r="B159" s="1">
-        <f>VALUE(RIGHT(F159,LEN(F159)-LEN(A159)))</f>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="C159" s="1">
         <v>472</v>
       </c>
       <c r="D159" s="1">
-        <f>LEN(E159)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F159" s="7" t="s">
         <v>1814</v>
       </c>
-      <c r="F159" s="7" t="s">
+      <c r="G159" s="26" t="s">
         <v>1815</v>
-      </c>
-      <c r="G159" s="26" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="24.95" customHeight="1">
@@ -33345,14 +33329,14 @@
         <v>VD</v>
       </c>
       <c r="B160" s="1">
-        <f>VALUE(RIGHT(F160,LEN(F160)-LEN(A160)))</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="C160" s="1">
         <v>476</v>
       </c>
       <c r="D160" s="1">
-        <f>LEN(E160)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E160" s="5" t="s">
@@ -33371,12 +33355,12 @@
         <v>VD</v>
       </c>
       <c r="B161" s="1">
-        <f>VALUE(RIGHT(F161,LEN(F161)-LEN(A161)))</f>
+        <f t="shared" si="4"/>
         <v>304</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1">
-        <f>LEN(E161)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E161" s="46" t="s">
@@ -33395,14 +33379,14 @@
         <v>VD</v>
       </c>
       <c r="B162" s="1">
-        <f>VALUE(RIGHT(F162,LEN(F162)-LEN(A162)))</f>
+        <f t="shared" si="4"/>
         <v>308</v>
       </c>
       <c r="C162" s="1">
         <v>480</v>
       </c>
       <c r="D162" s="1">
-        <f>LEN(E162)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E162" s="5" t="s">
@@ -33421,14 +33405,14 @@
         <v>VD</v>
       </c>
       <c r="B163" s="1">
-        <f>VALUE(RIGHT(F163,LEN(F163)-LEN(A163)))</f>
+        <f t="shared" si="4"/>
         <v>312</v>
       </c>
       <c r="C163" s="1">
         <v>316</v>
       </c>
       <c r="D163" s="1">
-        <f>LEN(E163)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="E163" s="1" t="s">
@@ -33447,14 +33431,14 @@
         <v>VD</v>
       </c>
       <c r="B164" s="1">
-        <f>VALUE(RIGHT(F164,LEN(F164)-LEN(A164)))</f>
+        <f t="shared" si="4"/>
         <v>316</v>
       </c>
       <c r="C164" s="1">
         <v>484</v>
       </c>
       <c r="D164" s="1">
-        <f>LEN(E164)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="E164" s="5" t="s">
@@ -33473,14 +33457,14 @@
         <v>VD</v>
       </c>
       <c r="B165" s="1">
-        <f>VALUE(RIGHT(F165,LEN(F165)-LEN(A165)))</f>
+        <f t="shared" si="4"/>
         <v>320</v>
       </c>
       <c r="C165" s="1">
         <v>488</v>
       </c>
       <c r="D165" s="1">
-        <f>LEN(E165)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="E165" s="5" t="s">
@@ -33499,14 +33483,14 @@
         <v>VD</v>
       </c>
       <c r="B166" s="1">
-        <f>VALUE(RIGHT(F166,LEN(F166)-LEN(A166)))</f>
+        <f t="shared" si="4"/>
         <v>324</v>
       </c>
       <c r="C166" s="1">
         <v>492</v>
       </c>
       <c r="D166" s="1">
-        <f>LEN(E166)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="E166" s="5" t="s">
@@ -33525,14 +33509,14 @@
         <v>VD</v>
       </c>
       <c r="B167" s="1">
-        <f>VALUE(RIGHT(F167,LEN(F167)-LEN(A167)))</f>
+        <f t="shared" si="4"/>
         <v>328</v>
       </c>
       <c r="C167" s="1">
         <v>496</v>
       </c>
       <c r="D167" s="1">
-        <f>LEN(E167)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="E167" s="5" t="s">
@@ -33551,14 +33535,14 @@
         <v>VD</v>
       </c>
       <c r="B168" s="1">
-        <f>VALUE(RIGHT(F168,LEN(F168)-LEN(A168)))</f>
+        <f t="shared" si="4"/>
         <v>332</v>
       </c>
       <c r="C168" s="1">
         <v>500</v>
       </c>
       <c r="D168" s="1">
-        <f>LEN(E168)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="E168" s="1" t="s">
@@ -33577,14 +33561,14 @@
         <v>VD</v>
       </c>
       <c r="B169" s="1">
-        <f>VALUE(RIGHT(F169,LEN(F169)-LEN(A169)))</f>
+        <f t="shared" si="4"/>
         <v>336</v>
       </c>
       <c r="C169" s="1">
         <v>504</v>
       </c>
       <c r="D169" s="1">
-        <f>LEN(E169)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="E169" s="1" t="s">
@@ -33603,14 +33587,14 @@
         <v>VD</v>
       </c>
       <c r="B170" s="1">
-        <f>VALUE(RIGHT(F170,LEN(F170)-LEN(A170)))</f>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="C170" s="1">
         <v>508</v>
       </c>
       <c r="D170" s="1">
-        <f>LEN(E170)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E170" s="1" t="s">
@@ -33629,14 +33613,14 @@
         <v>VD</v>
       </c>
       <c r="B171" s="1">
-        <f>VALUE(RIGHT(F171,LEN(F171)-LEN(A171)))</f>
+        <f t="shared" si="4"/>
         <v>344</v>
       </c>
       <c r="C171" s="1">
         <v>512</v>
       </c>
       <c r="D171" s="1">
-        <f>LEN(E171)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E171" s="1" t="s">
@@ -33655,14 +33639,14 @@
         <v>VD</v>
       </c>
       <c r="B172" s="1">
-        <f>VALUE(RIGHT(F172,LEN(F172)-LEN(A172)))</f>
+        <f t="shared" si="4"/>
         <v>348</v>
       </c>
       <c r="C172" s="1">
         <v>516</v>
       </c>
       <c r="D172" s="1">
-        <f>LEN(E172)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E172" s="1" t="s">
@@ -33681,12 +33665,12 @@
         <v>VD</v>
       </c>
       <c r="B173" s="1">
-        <f>VALUE(RIGHT(F173,LEN(F173)-LEN(A173)))</f>
+        <f t="shared" si="4"/>
         <v>352</v>
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="1">
-        <f>LEN(E173)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E173" s="46" t="s">
@@ -33705,12 +33689,12 @@
         <v>VD</v>
       </c>
       <c r="B174" s="1">
-        <f>VALUE(RIGHT(F174,LEN(F174)-LEN(A174)))</f>
+        <f t="shared" si="4"/>
         <v>356</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1">
-        <f>LEN(E174)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E174" s="46" t="s">
@@ -33729,14 +33713,14 @@
         <v>VD</v>
       </c>
       <c r="B175" s="1">
-        <f>VALUE(RIGHT(F175,LEN(F175)-LEN(A175)))</f>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="C175" s="1">
         <v>520</v>
       </c>
       <c r="D175" s="1">
-        <f>LEN(E175)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E175" s="1" t="s">
@@ -33755,14 +33739,14 @@
         <v>VD</v>
       </c>
       <c r="B176" s="1">
-        <f>VALUE(RIGHT(F176,LEN(F176)-LEN(A176)))</f>
+        <f t="shared" si="4"/>
         <v>364</v>
       </c>
       <c r="C176" s="1">
         <v>524</v>
       </c>
       <c r="D176" s="1">
-        <f>LEN(E176)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E176" s="1" t="s">
@@ -33781,12 +33765,12 @@
         <v>VD</v>
       </c>
       <c r="B177" s="1">
-        <f>VALUE(RIGHT(F177,LEN(F177)-LEN(A177)))</f>
+        <f t="shared" si="4"/>
         <v>368</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1">
-        <f>LEN(E177)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E177" s="1" t="s">
@@ -33805,12 +33789,12 @@
         <v>VD</v>
       </c>
       <c r="B178" s="1">
-        <f>VALUE(RIGHT(F178,LEN(F178)-LEN(A178)))</f>
+        <f t="shared" si="4"/>
         <v>372</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1">
-        <f>LEN(E178)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E178" s="1" t="s">
@@ -33829,12 +33813,12 @@
         <v>VD</v>
       </c>
       <c r="B179" s="1">
-        <f>VALUE(RIGHT(F179,LEN(F179)-LEN(A179)))</f>
+        <f t="shared" si="4"/>
         <v>376</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1">
-        <f>LEN(E179)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E179" s="1" t="s">
@@ -33853,14 +33837,14 @@
         <v>VD</v>
       </c>
       <c r="B180" s="1">
-        <f>VALUE(RIGHT(F180,LEN(F180)-LEN(A180)))</f>
+        <f t="shared" si="4"/>
         <v>380</v>
       </c>
       <c r="C180" s="1">
         <v>640</v>
       </c>
       <c r="D180" s="1">
-        <f>LEN(E180)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E180" s="1" t="s">
@@ -33879,14 +33863,14 @@
         <v>VD</v>
       </c>
       <c r="B181" s="1">
-        <f>VALUE(RIGHT(F181,LEN(F181)-LEN(A181)))</f>
+        <f t="shared" si="4"/>
         <v>384</v>
       </c>
       <c r="C181" s="1">
         <v>644</v>
       </c>
       <c r="D181" s="1">
-        <f>LEN(E181)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E181" s="1" t="s">
@@ -33905,14 +33889,14 @@
         <v>VD</v>
       </c>
       <c r="B182" s="1">
-        <f>VALUE(RIGHT(F182,LEN(F182)-LEN(A182)))</f>
+        <f t="shared" si="4"/>
         <v>388</v>
       </c>
       <c r="C182" s="1">
         <v>648</v>
       </c>
       <c r="D182" s="1">
-        <f>LEN(E182)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E182" s="1" t="s">
@@ -33931,14 +33915,14 @@
         <v>VD</v>
       </c>
       <c r="B183" s="1">
-        <f>VALUE(RIGHT(F183,LEN(F183)-LEN(A183)))</f>
+        <f t="shared" si="4"/>
         <v>392</v>
       </c>
       <c r="C183" s="1">
         <v>652</v>
       </c>
       <c r="D183" s="1">
-        <f>LEN(E183)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E183" s="5" t="s">
@@ -33957,14 +33941,14 @@
         <v>VD</v>
       </c>
       <c r="B184" s="1">
-        <f>VALUE(RIGHT(F184,LEN(F184)-LEN(A184)))</f>
+        <f t="shared" si="4"/>
         <v>396</v>
       </c>
       <c r="C184" s="1">
         <v>68</v>
       </c>
       <c r="D184" s="1">
-        <f>LEN(E184)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E184" s="1" t="s">
@@ -33983,14 +33967,14 @@
         <v>VD</v>
       </c>
       <c r="B185" s="1">
-        <f>VALUE(RIGHT(F185,LEN(F185)-LEN(A185)))</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
       <c r="C185" s="1">
         <v>320</v>
       </c>
       <c r="D185" s="1">
-        <f>LEN(E185)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E185" s="46" t="s">
@@ -34009,14 +33993,14 @@
         <v>VD</v>
       </c>
       <c r="B186" s="1">
-        <f>VALUE(RIGHT(F186,LEN(F186)-LEN(A186)))</f>
+        <f t="shared" si="4"/>
         <v>404</v>
       </c>
       <c r="C186" s="1">
         <v>72</v>
       </c>
       <c r="D186" s="1">
-        <f>LEN(E186)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E186" s="1" t="s">
@@ -34035,14 +34019,14 @@
         <v>VD</v>
       </c>
       <c r="B187" s="1">
-        <f>VALUE(RIGHT(F187,LEN(F187)-LEN(A187)))</f>
+        <f t="shared" si="4"/>
         <v>408</v>
       </c>
       <c r="C187" s="1">
         <v>76</v>
       </c>
       <c r="D187" s="1">
-        <f>LEN(E187)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E187" s="1" t="s">
@@ -34061,14 +34045,14 @@
         <v>VD</v>
       </c>
       <c r="B188" s="1">
-        <f>VALUE(RIGHT(F188,LEN(F188)-LEN(A188)))</f>
+        <f t="shared" si="4"/>
         <v>412</v>
       </c>
       <c r="C188" s="1">
         <v>324</v>
       </c>
       <c r="D188" s="1">
-        <f>LEN(E188)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E188" s="1" t="s">
@@ -34087,14 +34071,14 @@
         <v>VD</v>
       </c>
       <c r="B189" s="1">
-        <f>VALUE(RIGHT(F189,LEN(F189)-LEN(A189)))</f>
+        <f t="shared" si="4"/>
         <v>416</v>
       </c>
       <c r="C189" s="1">
         <v>328</v>
       </c>
       <c r="D189" s="1">
-        <f>LEN(E189)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E189" s="1" t="s">
@@ -34113,14 +34097,14 @@
         <v>VD</v>
       </c>
       <c r="B190" s="1">
-        <f>VALUE(RIGHT(F190,LEN(F190)-LEN(A190)))</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="C190" s="1">
         <v>332</v>
       </c>
       <c r="D190" s="1">
-        <f>LEN(E190)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E190" s="1" t="s">
@@ -34139,14 +34123,14 @@
         <v>VD</v>
       </c>
       <c r="B191" s="1">
-        <f>VALUE(RIGHT(F191,LEN(F191)-LEN(A191)))</f>
+        <f t="shared" si="4"/>
         <v>424</v>
       </c>
       <c r="C191" s="1">
         <v>336</v>
       </c>
       <c r="D191" s="1">
-        <f>LEN(E191)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E191" s="1" t="s">
@@ -34165,14 +34149,14 @@
         <v>VD</v>
       </c>
       <c r="B192" s="1">
-        <f>VALUE(RIGHT(F192,LEN(F192)-LEN(A192)))</f>
+        <f t="shared" si="4"/>
         <v>428</v>
       </c>
       <c r="C192" s="1">
         <v>340</v>
       </c>
       <c r="D192" s="1">
-        <f>LEN(E192)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E192" s="1" t="s">
@@ -34191,14 +34175,14 @@
         <v>VD</v>
       </c>
       <c r="B193" s="1">
-        <f>VALUE(RIGHT(F193,LEN(F193)-LEN(A193)))</f>
+        <f t="shared" si="4"/>
         <v>432</v>
       </c>
       <c r="C193" s="1">
         <v>344</v>
       </c>
       <c r="D193" s="1">
-        <f>LEN(E193)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E193" s="1" t="s">
@@ -34217,14 +34201,14 @@
         <v>VD</v>
       </c>
       <c r="B194" s="1">
-        <f>VALUE(RIGHT(F194,LEN(F194)-LEN(A194)))</f>
+        <f t="shared" ref="B194:B257" si="6">VALUE(RIGHT(F194,LEN(F194)-LEN(A194)))</f>
         <v>436</v>
       </c>
       <c r="C194" s="1">
         <v>348</v>
       </c>
       <c r="D194" s="1">
-        <f>LEN(E194)</f>
+        <f t="shared" ref="D194:D257" si="7">LEN(E194)</f>
         <v>16</v>
       </c>
       <c r="E194" s="1" t="s">
@@ -34243,14 +34227,14 @@
         <v>VD</v>
       </c>
       <c r="B195" s="1">
-        <f>VALUE(RIGHT(F195,LEN(F195)-LEN(A195)))</f>
+        <f t="shared" si="6"/>
         <v>440</v>
       </c>
       <c r="C195" s="1">
         <v>352</v>
       </c>
       <c r="D195" s="1">
-        <f>LEN(E195)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E195" s="1" t="s">
@@ -34269,14 +34253,14 @@
         <v>VD</v>
       </c>
       <c r="B196" s="1">
-        <f>VALUE(RIGHT(F196,LEN(F196)-LEN(A196)))</f>
+        <f t="shared" si="6"/>
         <v>444</v>
       </c>
       <c r="C196" s="1">
         <v>356</v>
       </c>
       <c r="D196" s="1">
-        <f>LEN(E196)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E196" s="1" t="s">
@@ -34295,12 +34279,12 @@
         <v>VD</v>
       </c>
       <c r="B197" s="1">
-        <f>VALUE(RIGHT(F197,LEN(F197)-LEN(A197)))</f>
+        <f t="shared" si="6"/>
         <v>448</v>
       </c>
       <c r="C197" s="1"/>
       <c r="D197" s="1">
-        <f>LEN(E197)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E197" s="1" t="s">
@@ -34319,12 +34303,12 @@
         <v>VD</v>
       </c>
       <c r="B198" s="1">
-        <f>VALUE(RIGHT(F198,LEN(F198)-LEN(A198)))</f>
+        <f t="shared" si="6"/>
         <v>452</v>
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="1">
-        <f>LEN(E198)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E198" s="1" t="s">
@@ -34343,12 +34327,12 @@
         <v>VD</v>
       </c>
       <c r="B199" s="1">
-        <f>VALUE(RIGHT(F199,LEN(F199)-LEN(A199)))</f>
+        <f t="shared" si="6"/>
         <v>456</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1">
-        <f>LEN(E199)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E199" s="1" t="s">
@@ -34367,12 +34351,12 @@
         <v>VD</v>
       </c>
       <c r="B200" s="1">
-        <f>VALUE(RIGHT(F200,LEN(F200)-LEN(A200)))</f>
+        <f t="shared" si="6"/>
         <v>460</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1">
-        <f>LEN(E200)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E200" s="1" t="s">
@@ -34391,12 +34375,12 @@
         <v>VD</v>
       </c>
       <c r="B201" s="1">
-        <f>VALUE(RIGHT(F201,LEN(F201)-LEN(A201)))</f>
+        <f t="shared" si="6"/>
         <v>464</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1">
-        <f>LEN(E201)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E201" s="1" t="s">
@@ -34415,12 +34399,12 @@
         <v>VD</v>
       </c>
       <c r="B202" s="1">
-        <f>VALUE(RIGHT(F202,LEN(F202)-LEN(A202)))</f>
+        <f t="shared" si="6"/>
         <v>468</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="1">
-        <f>LEN(E202)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E202" s="1" t="s">
@@ -34439,12 +34423,12 @@
         <v>VD</v>
       </c>
       <c r="B203" s="1">
-        <f>VALUE(RIGHT(F203,LEN(F203)-LEN(A203)))</f>
+        <f t="shared" si="6"/>
         <v>472</v>
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="1">
-        <f>LEN(E203)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E203" s="1" t="s">
@@ -34463,12 +34447,12 @@
         <v>VD</v>
       </c>
       <c r="B204" s="1">
-        <f>VALUE(RIGHT(F204,LEN(F204)-LEN(A204)))</f>
+        <f t="shared" si="6"/>
         <v>476</v>
       </c>
       <c r="C204" s="1"/>
       <c r="D204" s="1">
-        <f>LEN(E204)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E204" s="1" t="s">
@@ -34487,12 +34471,12 @@
         <v>VD</v>
       </c>
       <c r="B205" s="1">
-        <f>VALUE(RIGHT(F205,LEN(F205)-LEN(A205)))</f>
+        <f t="shared" si="6"/>
         <v>480</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="1">
-        <f>LEN(E205)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E205" s="1" t="s">
@@ -34511,12 +34495,12 @@
         <v>VD</v>
       </c>
       <c r="B206" s="1">
-        <f>VALUE(RIGHT(F206,LEN(F206)-LEN(A206)))</f>
+        <f t="shared" si="6"/>
         <v>484</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1">
-        <f>LEN(E206)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E206" s="46" t="s">
@@ -34535,12 +34519,12 @@
         <v>VD</v>
       </c>
       <c r="B207" s="1">
-        <f>VALUE(RIGHT(F207,LEN(F207)-LEN(A207)))</f>
+        <f t="shared" si="6"/>
         <v>488</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="1">
-        <f>LEN(E207)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E207" s="46" t="s">
@@ -34559,12 +34543,12 @@
         <v>VD</v>
       </c>
       <c r="B208" s="1">
-        <f>VALUE(RIGHT(F208,LEN(F208)-LEN(A208)))</f>
+        <f t="shared" si="6"/>
         <v>492</v>
       </c>
       <c r="C208" s="1"/>
       <c r="D208" s="1">
-        <f>LEN(E208)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E208" s="1" t="s">
@@ -34583,12 +34567,12 @@
         <v>VD</v>
       </c>
       <c r="B209" s="1">
-        <f>VALUE(RIGHT(F209,LEN(F209)-LEN(A209)))</f>
+        <f t="shared" si="6"/>
         <v>496</v>
       </c>
       <c r="C209" s="1"/>
       <c r="D209" s="1">
-        <f>LEN(E209)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E209" s="1" t="s">
@@ -34607,12 +34591,12 @@
         <v>VD</v>
       </c>
       <c r="B210" s="1">
-        <f>VALUE(RIGHT(F210,LEN(F210)-LEN(A210)))</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1">
-        <f>LEN(E210)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E210" s="1" t="s">
@@ -34631,12 +34615,12 @@
         <v>VD</v>
       </c>
       <c r="B211" s="1">
-        <f>VALUE(RIGHT(F211,LEN(F211)-LEN(A211)))</f>
+        <f t="shared" si="6"/>
         <v>504</v>
       </c>
       <c r="C211" s="1"/>
       <c r="D211" s="1">
-        <f>LEN(E211)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E211" s="1" t="s">
@@ -34655,12 +34639,12 @@
         <v>VD</v>
       </c>
       <c r="B212" s="1">
-        <f>VALUE(RIGHT(F212,LEN(F212)-LEN(A212)))</f>
+        <f t="shared" si="6"/>
         <v>508</v>
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1">
-        <f>LEN(E212)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E212" s="1" t="s">
@@ -34679,12 +34663,12 @@
         <v>VD</v>
       </c>
       <c r="B213" s="1">
-        <f>VALUE(RIGHT(F213,LEN(F213)-LEN(A213)))</f>
+        <f t="shared" si="6"/>
         <v>512</v>
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="1">
-        <f>LEN(E213)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E213" s="1" t="s">
@@ -34703,12 +34687,12 @@
         <v>VD</v>
       </c>
       <c r="B214" s="1">
-        <f>VALUE(RIGHT(F214,LEN(F214)-LEN(A214)))</f>
+        <f t="shared" si="6"/>
         <v>516</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1">
-        <f>LEN(E214)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E214" s="1" t="s">
@@ -34727,12 +34711,12 @@
         <v>VD</v>
       </c>
       <c r="B215" s="1">
-        <f>VALUE(RIGHT(F215,LEN(F215)-LEN(A215)))</f>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1">
-        <f>LEN(E215)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E215" s="1" t="s">
@@ -34751,12 +34735,12 @@
         <v>VD</v>
       </c>
       <c r="B216" s="1">
-        <f>VALUE(RIGHT(F216,LEN(F216)-LEN(A216)))</f>
+        <f t="shared" si="6"/>
         <v>524</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1">
-        <f>LEN(E216)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E216" s="1" t="s">
@@ -34775,22 +34759,22 @@
         <v>VD</v>
       </c>
       <c r="B217" s="1">
-        <f>VALUE(RIGHT(F217,LEN(F217)-LEN(A217)))</f>
+        <f t="shared" si="6"/>
         <v>586</v>
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1">
-        <f>LEN(E217)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="E217" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>1817</v>
       </c>
-      <c r="F217" s="1" t="s">
+      <c r="G217" s="26" t="s">
         <v>1818</v>
-      </c>
-      <c r="G217" s="26" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="24.95" customHeight="1">
@@ -34799,12 +34783,12 @@
         <v>VD</v>
       </c>
       <c r="B218" s="1">
-        <f>VALUE(RIGHT(F218,LEN(F218)-LEN(A218)))</f>
+        <f t="shared" si="6"/>
         <v>1640</v>
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="1">
-        <f>LEN(E218)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E218" s="1" t="s">
@@ -34823,12 +34807,12 @@
         <v>VD</v>
       </c>
       <c r="B219" s="1">
-        <f>VALUE(RIGHT(F219,LEN(F219)-LEN(A219)))</f>
+        <f t="shared" si="6"/>
         <v>1644</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1">
-        <f>LEN(E219)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E219" s="1" t="s">
@@ -34847,22 +34831,22 @@
         <v>VD</v>
       </c>
       <c r="B220" s="1">
-        <f>VALUE(RIGHT(F220,LEN(F220)-LEN(A220)))</f>
+        <f t="shared" si="6"/>
         <v>1648</v>
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="1">
-        <f>LEN(E220)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>1392</v>
       </c>
       <c r="F220" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G220" s="26" t="s">
         <v>1820</v>
-      </c>
-      <c r="G220" s="26" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="24.95" customHeight="1">
@@ -34871,12 +34855,12 @@
         <v>VD</v>
       </c>
       <c r="B221" s="1">
-        <f>VALUE(RIGHT(F221,LEN(F221)-LEN(A221)))</f>
+        <f t="shared" si="6"/>
         <v>1652</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="1">
-        <f>LEN(E221)</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="E221" s="1" t="s">
@@ -34886,7 +34870,7 @@
         <v>1619</v>
       </c>
       <c r="G221" s="26" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="24.95" customHeight="1">
@@ -34895,12 +34879,12 @@
         <v>VD</v>
       </c>
       <c r="B222" s="1">
-        <f>VALUE(RIGHT(F222,LEN(F222)-LEN(A222)))</f>
+        <f t="shared" si="6"/>
         <v>1880</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1">
-        <f>LEN(E222)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E222" s="1" t="s">
@@ -34910,7 +34894,7 @@
         <v>1621</v>
       </c>
       <c r="G222" s="26" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="24.95" customHeight="1">
@@ -34919,12 +34903,12 @@
         <v>VW</v>
       </c>
       <c r="B223" s="14">
-        <f>VALUE(RIGHT(F223,LEN(F223)-LEN(A223)))</f>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="C223" s="14"/>
       <c r="D223" s="14">
-        <f>LEN(E223)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E223" s="14" t="s">
@@ -34943,12 +34927,12 @@
         <v>VW</v>
       </c>
       <c r="B224" s="14">
-        <f>VALUE(RIGHT(F224,LEN(F224)-LEN(A224)))</f>
+        <f t="shared" si="6"/>
         <v>104</v>
       </c>
       <c r="C224" s="14"/>
       <c r="D224" s="14">
-        <f>LEN(E224)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="E224" s="1" t="s">
@@ -34967,19 +34951,19 @@
         <v>VW</v>
       </c>
       <c r="B225" s="14">
-        <f>VALUE(RIGHT(F225,LEN(F225)-LEN(A225)))</f>
+        <f t="shared" si="6"/>
         <v>108</v>
       </c>
       <c r="C225" s="14"/>
       <c r="D225" s="14">
-        <f>LEN(E225)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>1398</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="G225" s="41" t="s">
         <v>1400</v>
@@ -34991,19 +34975,19 @@
         <v>VW</v>
       </c>
       <c r="B226" s="14">
-        <f>VALUE(RIGHT(F226,LEN(F226)-LEN(A226)))</f>
+        <f t="shared" si="6"/>
         <v>112</v>
       </c>
       <c r="C226" s="14"/>
       <c r="D226" s="14">
-        <f>LEN(E226)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>1401</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="G226" s="41" t="s">
         <v>1403</v>
@@ -35015,19 +34999,19 @@
         <v>VW</v>
       </c>
       <c r="B227" s="14">
-        <f>VALUE(RIGHT(F227,LEN(F227)-LEN(A227)))</f>
+        <f t="shared" si="6"/>
         <v>116</v>
       </c>
       <c r="C227" s="14"/>
       <c r="D227" s="14">
-        <f>LEN(E227)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>1404</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="G227" s="41" t="s">
         <v>1406</v>
@@ -35039,19 +35023,19 @@
         <v>VW</v>
       </c>
       <c r="B228" s="14">
-        <f>VALUE(RIGHT(F228,LEN(F228)-LEN(A228)))</f>
+        <f t="shared" si="6"/>
         <v>120</v>
       </c>
       <c r="C228" s="14"/>
       <c r="D228" s="14">
-        <f>LEN(E228)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>1407</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="G228" s="41" t="s">
         <v>1409</v>
@@ -35063,19 +35047,19 @@
         <v>VW</v>
       </c>
       <c r="B229" s="14">
-        <f>VALUE(RIGHT(F229,LEN(F229)-LEN(A229)))</f>
+        <f t="shared" si="6"/>
         <v>124</v>
       </c>
       <c r="C229" s="14"/>
       <c r="D229" s="14">
-        <f>LEN(E229)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>1410</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="G229" s="41" t="s">
         <v>1411</v>
@@ -35087,19 +35071,19 @@
         <v>VW</v>
       </c>
       <c r="B230" s="14">
-        <f>VALUE(RIGHT(F230,LEN(F230)-LEN(A230)))</f>
+        <f t="shared" si="6"/>
         <v>128</v>
       </c>
       <c r="C230" s="14"/>
       <c r="D230" s="14">
-        <f>LEN(E230)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>1412</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G230" s="41" t="s">
         <v>1414</v>
@@ -35111,19 +35095,19 @@
         <v>VW</v>
       </c>
       <c r="B231" s="14">
-        <f>VALUE(RIGHT(F231,LEN(F231)-LEN(A231)))</f>
+        <f t="shared" si="6"/>
         <v>132</v>
       </c>
       <c r="C231" s="14"/>
       <c r="D231" s="14">
-        <f>LEN(E231)</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>1415</v>
       </c>
       <c r="F231" s="7" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="G231" s="41" t="s">
         <v>1417</v>
@@ -35135,19 +35119,19 @@
         <v>VW</v>
       </c>
       <c r="B232" s="14">
-        <f>VALUE(RIGHT(F232,LEN(F232)-LEN(A232)))</f>
+        <f t="shared" si="6"/>
         <v>136</v>
       </c>
       <c r="C232" s="14"/>
       <c r="D232" s="14">
-        <f>LEN(E232)</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>1418</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="G232" s="41" t="s">
         <v>1420</v>
@@ -35159,22 +35143,22 @@
         <v>VW</v>
       </c>
       <c r="B233" s="14">
-        <f>VALUE(RIGHT(F233,LEN(F233)-LEN(A233)))</f>
+        <f t="shared" si="6"/>
         <v>138</v>
       </c>
       <c r="C233" s="14"/>
       <c r="D233" s="14">
-        <f>LEN(E233)</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="E233" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F233" s="7" t="s">
         <v>1824</v>
       </c>
-      <c r="F233" s="7" t="s">
+      <c r="G233" s="41" t="s">
         <v>1825</v>
-      </c>
-      <c r="G233" s="41" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="24.95" customHeight="1">
@@ -35183,22 +35167,22 @@
         <v>VW</v>
       </c>
       <c r="B234" s="14">
-        <f>VALUE(RIGHT(F234,LEN(F234)-LEN(A234)))</f>
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="14">
-        <f>LEN(E234)</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="E234" s="78" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F234" s="7" t="s">
         <v>1827</v>
       </c>
-      <c r="F234" s="7" t="s">
+      <c r="G234" s="77" t="s">
         <v>1828</v>
-      </c>
-      <c r="G234" s="77" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="14.25">
@@ -35207,22 +35191,22 @@
         <v>VW</v>
       </c>
       <c r="B235" s="14">
-        <f>VALUE(RIGHT(F235,LEN(F235)-LEN(A235)))</f>
+        <f t="shared" si="6"/>
         <v>142</v>
       </c>
       <c r="C235" s="14"/>
       <c r="D235" s="14">
-        <f>LEN(E235)</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="E235" s="14" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F235" s="14" t="s">
         <v>1830</v>
       </c>
-      <c r="F235" s="14" t="s">
+      <c r="G235" s="79" t="s">
         <v>1831</v>
-      </c>
-      <c r="G235" s="79" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="24.95" customHeight="1">
@@ -35231,22 +35215,22 @@
         <v>VW</v>
       </c>
       <c r="B236" s="14">
-        <f>VALUE(RIGHT(F236,LEN(F236)-LEN(A236)))</f>
+        <f t="shared" si="6"/>
         <v>144</v>
       </c>
       <c r="C236" s="14"/>
       <c r="D236" s="14">
-        <f>LEN(E236)</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="E236" s="14" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F236" s="14" t="s">
         <v>1833</v>
       </c>
-      <c r="F236" s="14" t="s">
+      <c r="G236" s="45" t="s">
         <v>1834</v>
-      </c>
-      <c r="G236" s="45" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="24.95" customHeight="1">
@@ -35255,22 +35239,22 @@
         <v>VW</v>
       </c>
       <c r="B237" s="14">
-        <f>VALUE(RIGHT(F237,LEN(F237)-LEN(A237)))</f>
+        <f t="shared" si="6"/>
         <v>154</v>
       </c>
       <c r="C237" s="14"/>
       <c r="D237" s="14">
-        <f>LEN(E237)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
-      <c r="E237" s="89" t="s">
+      <c r="E237" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F237" s="1" t="s">
         <v>1836</v>
       </c>
-      <c r="F237" s="90" t="s">
+      <c r="G237" s="26" t="s">
         <v>1837</v>
-      </c>
-      <c r="G237" s="91" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="24.95" customHeight="1">
@@ -35279,22 +35263,22 @@
         <v>VW</v>
       </c>
       <c r="B238" s="14">
-        <f>VALUE(RIGHT(F238,LEN(F238)-LEN(A238)))</f>
+        <f t="shared" si="6"/>
         <v>156</v>
       </c>
       <c r="C238" s="14"/>
       <c r="D238" s="14">
-        <f>LEN(E238)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
-      <c r="E238" s="89" t="s">
+      <c r="E238" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F238" s="1" t="s">
         <v>1839</v>
       </c>
-      <c r="F238" s="90" t="s">
+      <c r="G238" s="26" t="s">
         <v>1840</v>
-      </c>
-      <c r="G238" s="91" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="24.95" customHeight="1">
@@ -35303,21 +35287,21 @@
         <v>VW</v>
       </c>
       <c r="B239" s="14">
-        <f>VALUE(RIGHT(F239,LEN(F239)-LEN(A239)))</f>
+        <f t="shared" si="6"/>
         <v>528</v>
       </c>
       <c r="C239" s="14"/>
       <c r="D239" s="14">
-        <f>LEN(E239)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="E239" s="89" t="s">
+      <c r="E239" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="F239" s="90" t="s">
+      <c r="F239" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="G239" s="91" t="s">
+      <c r="G239" s="26" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -35327,21 +35311,21 @@
         <v>VW</v>
       </c>
       <c r="B240" s="14">
-        <f>VALUE(RIGHT(F240,LEN(F240)-LEN(A240)))</f>
+        <f t="shared" si="6"/>
         <v>532</v>
       </c>
       <c r="C240" s="14"/>
       <c r="D240" s="14">
-        <f>LEN(E240)</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="E240" s="89" t="s">
+      <c r="E240" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="F240" s="90" t="s">
+      <c r="F240" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="G240" s="91" t="s">
+      <c r="G240" s="26" t="s">
         <v>1010</v>
       </c>
     </row>
@@ -35351,21 +35335,21 @@
         <v>VW</v>
       </c>
       <c r="B241" s="14">
-        <f>VALUE(RIGHT(F241,LEN(F241)-LEN(A241)))</f>
+        <f t="shared" si="6"/>
         <v>536</v>
       </c>
       <c r="C241" s="14"/>
       <c r="D241" s="14">
-        <f>LEN(E241)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="E241" s="89" t="s">
+      <c r="E241" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="F241" s="90" t="s">
+      <c r="F241" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="G241" s="91" t="s">
+      <c r="G241" s="26" t="s">
         <v>1199</v>
       </c>
     </row>
@@ -35375,21 +35359,21 @@
         <v>VW</v>
       </c>
       <c r="B242" s="14">
-        <f>VALUE(RIGHT(F242,LEN(F242)-LEN(A242)))</f>
+        <f t="shared" si="6"/>
         <v>540</v>
       </c>
       <c r="C242" s="14"/>
       <c r="D242" s="14">
-        <f>LEN(E242)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E242" s="89" t="s">
+      <c r="E242" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="F242" s="90" t="s">
+      <c r="F242" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="G242" s="91" t="s">
+      <c r="G242" s="26" t="s">
         <v>1023</v>
       </c>
     </row>
@@ -35399,21 +35383,21 @@
         <v>VW</v>
       </c>
       <c r="B243" s="14">
-        <f>VALUE(RIGHT(F243,LEN(F243)-LEN(A243)))</f>
+        <f t="shared" si="6"/>
         <v>544</v>
       </c>
       <c r="C243" s="14"/>
       <c r="D243" s="14">
-        <f>LEN(E243)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E243" s="89" t="s">
+      <c r="E243" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="F243" s="90" t="s">
+      <c r="F243" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="G243" s="91" t="s">
+      <c r="G243" s="26" t="s">
         <v>1024</v>
       </c>
     </row>
@@ -35423,21 +35407,21 @@
         <v>VW</v>
       </c>
       <c r="B244" s="14">
-        <f>VALUE(RIGHT(F244,LEN(F244)-LEN(A244)))</f>
+        <f t="shared" si="6"/>
         <v>548</v>
       </c>
       <c r="C244" s="14"/>
       <c r="D244" s="14">
-        <f>LEN(E244)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E244" s="89" t="s">
+      <c r="E244" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="F244" s="90" t="s">
+      <c r="F244" s="1" t="s">
         <v>1463</v>
       </c>
-      <c r="G244" s="91" t="s">
+      <c r="G244" s="26" t="s">
         <v>1025</v>
       </c>
     </row>
@@ -35447,21 +35431,21 @@
         <v>VW</v>
       </c>
       <c r="B245" s="14">
-        <f>VALUE(RIGHT(F245,LEN(F245)-LEN(A245)))</f>
+        <f t="shared" si="6"/>
         <v>552</v>
       </c>
       <c r="C245" s="14"/>
       <c r="D245" s="14">
-        <f>LEN(E245)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E245" s="89" t="s">
+      <c r="E245" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="F245" s="90" t="s">
+      <c r="F245" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="G245" s="91" t="s">
+      <c r="G245" s="26" t="s">
         <v>1026</v>
       </c>
     </row>
@@ -35471,21 +35455,21 @@
         <v>VW</v>
       </c>
       <c r="B246" s="14">
-        <f>VALUE(RIGHT(F246,LEN(F246)-LEN(A246)))</f>
+        <f t="shared" si="6"/>
         <v>556</v>
       </c>
       <c r="C246" s="14"/>
       <c r="D246" s="14">
-        <f>LEN(E246)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E246" s="89" t="s">
+      <c r="E246" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="F246" s="90" t="s">
+      <c r="F246" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="G246" s="91" t="s">
+      <c r="G246" s="26" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -35495,21 +35479,21 @@
         <v>VW</v>
       </c>
       <c r="B247" s="14">
-        <f>VALUE(RIGHT(F247,LEN(F247)-LEN(A247)))</f>
+        <f t="shared" si="6"/>
         <v>560</v>
       </c>
       <c r="C247" s="14"/>
       <c r="D247" s="14">
-        <f>LEN(E247)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E247" s="89" t="s">
+      <c r="E247" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="F247" s="90" t="s">
+      <c r="F247" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="G247" s="91" t="s">
+      <c r="G247" s="26" t="s">
         <v>1028</v>
       </c>
     </row>
@@ -35519,21 +35503,21 @@
         <v>VW</v>
       </c>
       <c r="B248" s="14">
-        <f>VALUE(RIGHT(F248,LEN(F248)-LEN(A248)))</f>
+        <f t="shared" si="6"/>
         <v>564</v>
       </c>
       <c r="C248" s="14"/>
       <c r="D248" s="14">
-        <f>LEN(E248)</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
-      <c r="E248" s="89" t="s">
+      <c r="E248" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="F248" s="90" t="s">
+      <c r="F248" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="G248" s="91" t="s">
+      <c r="G248" s="26" t="s">
         <v>694</v>
       </c>
     </row>
@@ -35543,21 +35527,21 @@
         <v>VW</v>
       </c>
       <c r="B249" s="14">
-        <f>VALUE(RIGHT(F249,LEN(F249)-LEN(A249)))</f>
+        <f t="shared" si="6"/>
         <v>568</v>
       </c>
       <c r="C249" s="14"/>
       <c r="D249" s="14">
-        <f>LEN(E249)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
-      <c r="E249" s="89" t="s">
+      <c r="E249" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="F249" s="90" t="s">
+      <c r="F249" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="G249" s="91" t="s">
+      <c r="G249" s="26" t="s">
         <v>1493</v>
       </c>
     </row>
@@ -35567,21 +35551,21 @@
         <v>VW</v>
       </c>
       <c r="B250" s="14">
-        <f>VALUE(RIGHT(F250,LEN(F250)-LEN(A250)))</f>
+        <f t="shared" si="6"/>
         <v>572</v>
       </c>
       <c r="C250" s="14"/>
       <c r="D250" s="14">
-        <f>LEN(E250)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
-      <c r="E250" s="89" t="s">
+      <c r="E250" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="F250" s="90" t="s">
+      <c r="F250" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="G250" s="91" t="s">
+      <c r="G250" s="26" t="s">
         <v>1495</v>
       </c>
     </row>
@@ -35591,21 +35575,21 @@
         <v>VW</v>
       </c>
       <c r="B251" s="14">
-        <f>VALUE(RIGHT(F251,LEN(F251)-LEN(A251)))</f>
+        <f t="shared" si="6"/>
         <v>576</v>
       </c>
       <c r="C251" s="14"/>
       <c r="D251" s="14">
-        <f>LEN(E251)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E251" s="89" t="s">
+      <c r="E251" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="F251" s="90" t="s">
+      <c r="F251" s="1" t="s">
         <v>1517</v>
       </c>
-      <c r="G251" s="91" t="s">
+      <c r="G251" s="26" t="s">
         <v>1491</v>
       </c>
     </row>
@@ -35615,21 +35599,21 @@
         <v>VW</v>
       </c>
       <c r="B252" s="14">
-        <f>VALUE(RIGHT(F252,LEN(F252)-LEN(A252)))</f>
+        <f t="shared" si="6"/>
         <v>580</v>
       </c>
       <c r="C252" s="14"/>
       <c r="D252" s="14">
-        <f>LEN(E252)</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="E252" s="89" t="s">
+      <c r="E252" s="1" t="s">
         <v>1526</v>
       </c>
-      <c r="F252" s="90" t="s">
+      <c r="F252" s="1" t="s">
         <v>1527</v>
       </c>
-      <c r="G252" s="91" t="s">
+      <c r="G252" s="26" t="s">
         <v>1528</v>
       </c>
     </row>
@@ -35639,21 +35623,21 @@
         <v>VW</v>
       </c>
       <c r="B253" s="14">
-        <f>VALUE(RIGHT(F253,LEN(F253)-LEN(A253)))</f>
+        <f t="shared" si="6"/>
         <v>584</v>
       </c>
       <c r="C253" s="14"/>
       <c r="D253" s="14">
-        <f>LEN(E253)</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="E253" s="89" t="s">
+      <c r="E253" s="1" t="s">
         <v>1529</v>
       </c>
-      <c r="F253" s="90" t="s">
+      <c r="F253" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="G253" s="91" t="s">
+      <c r="G253" s="26" t="s">
         <v>1531</v>
       </c>
     </row>
@@ -35663,22 +35647,22 @@
         <v>VW</v>
       </c>
       <c r="B254" s="14">
-        <f>VALUE(RIGHT(F254,LEN(F254)-LEN(A254)))</f>
+        <f t="shared" si="6"/>
         <v>814</v>
       </c>
       <c r="C254" s="14"/>
       <c r="D254" s="14">
-        <f>LEN(E254)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="E254" s="89" t="s">
-        <v>1842</v>
-      </c>
-      <c r="F254" s="90" t="s">
-        <v>1711</v>
-      </c>
-      <c r="G254" s="92" t="s">
-        <v>1847</v>
+      <c r="E254" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G254" s="86" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="24.95" customHeight="1">
@@ -35687,22 +35671,22 @@
         <v>VW</v>
       </c>
       <c r="B255" s="14">
-        <f>VALUE(RIGHT(F255,LEN(F255)-LEN(A255)))</f>
+        <f t="shared" si="6"/>
         <v>816</v>
       </c>
       <c r="C255" s="14"/>
       <c r="D255" s="14">
-        <f>LEN(E255)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="E255" s="89" t="s">
-        <v>1843</v>
-      </c>
-      <c r="F255" s="90" t="s">
+      <c r="E255" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="G255" s="26" t="s">
         <v>1712</v>
-      </c>
-      <c r="G255" s="91" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="256" spans="1:7" ht="24.95" customHeight="1">
@@ -35711,22 +35695,22 @@
         <v>VW</v>
       </c>
       <c r="B256" s="14">
-        <f>VALUE(RIGHT(F256,LEN(F256)-LEN(A256)))</f>
+        <f t="shared" si="6"/>
         <v>1898</v>
       </c>
       <c r="C256" s="14"/>
       <c r="D256" s="14">
-        <f>LEN(E256)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="E256" s="89" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F256" s="90" t="s">
+      <c r="E256" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F256" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="G256" s="91" t="s">
-        <v>1707</v>
+      <c r="G256" s="26" t="s">
+        <v>1706</v>
       </c>
     </row>
     <row r="257" spans="1:7" ht="24.95" customHeight="1">
@@ -35735,22 +35719,22 @@
         <v>VW</v>
       </c>
       <c r="B257" s="14">
-        <f>VALUE(RIGHT(F257,LEN(F257)-LEN(A257)))</f>
+        <f t="shared" si="6"/>
         <v>1918</v>
       </c>
       <c r="C257" s="14"/>
       <c r="D257" s="14">
-        <f>LEN(E257)</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="E257" s="89" t="s">
+      <c r="E257" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G257" s="26" t="s">
         <v>1845</v>
-      </c>
-      <c r="F257" s="90" t="s">
-        <v>1636</v>
-      </c>
-      <c r="G257" s="91" t="s">
-        <v>1846</v>
       </c>
     </row>
   </sheetData>

--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\codes\04-electricity\01-plc\江铜\burnerControler_JXT\burnerController_JXXY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\02-PLC项目\江西沸腾炉烧嘴程序改造\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A437D8A-B21A-4B77-990D-8D67E3455F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE9DBC6-9712-4257-93B7-D59F20064349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="622" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="622" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
   </bookViews>
   <sheets>
     <sheet name="端子1-原始" sheetId="1" r:id="rId1"/>
@@ -20,26 +20,38 @@
     <sheet name="地址校验" sheetId="16" r:id="rId5"/>
     <sheet name="IO分配表" sheetId="14" r:id="rId6"/>
     <sheet name="远程通讯" sheetId="5" r:id="rId7"/>
-    <sheet name="江铜项目测试" sheetId="15" r:id="rId8"/>
+    <sheet name="项目测试" sheetId="15" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'端子1-原始'!$C$1:$E$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">符号表!$E$1:$G$74</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'端子1-原始'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">符号表!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">江铜项目测试!$A$1:$F$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">江铜项目测试!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">项目测试!$1:$1</definedName>
     <definedName name="VW区" localSheetId="3">符号表!#REF!</definedName>
     <definedName name="VW区">'端子1-原始'!#REF!</definedName>
     <definedName name="V区" localSheetId="3">符号表!#REF!</definedName>
     <definedName name="V区">'端子1-原始'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="1632">
   <si>
     <t>I</t>
   </si>
@@ -4812,7 +4824,13 @@
     <t>阀正常开启</t>
   </si>
   <si>
+    <t>温控启停</t>
+  </si>
+  <si>
     <t>调节当前温度为超过停机温度</t>
+  </si>
+  <si>
+    <t>超过设定温度，关闭主火阀、安全阀</t>
   </si>
   <si>
     <t>手动模式</t>
@@ -5267,6 +5285,11 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>第1步：调节阀在设定时间内（60s）关闭至0位，对比执行与反馈差值均在设定5%以内，进入第2步检测。
+第2步：调节阀在规定时间60s内打开至设定位置如70%，再次对比执行与反馈差值，也均在5%之内。检测结束</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>调节阀检测倒计时 显示正常
 调节阀检测指示灯 绿灯常亮</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -5310,37 +5333,27 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>温控停主火</t>
+    <t>前火检</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>温控开主火</t>
+    <t>停机——点火准备 之间，检测到火焰超过设定时长2秒，报警停机</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>在温控停主火状态下，调整温度低于开主火温度</t>
+    <t>报警停机，点火前发现火焰故障</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>低于开机温度3秒以上，开启主火</t>
+    <t>点火备用</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>超过设定温度保持3秒以上，在60秒内调整到1档，到位或超60秒后关闭主火阀、安全阀</t>
+    <t>如果确定炉膛内有火焰导致的报警，可在系统内，点击点火备用来允许本次点火。停机后置位点火备用。</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>备注</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>开机提醒，在检漏完成并且通过后自动消失</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>调节阀检测通过逻辑：在第1步和第2步检测中，全部通过，才算通过。
-第1步：调节阀在设定时间内（60s）关闭至0位，对比执行与反馈差值均在设定5%以内，进入第2步检测。
-第2步：调节阀在规定时间60s内打开至设定位置如70%，再次对比执行与反馈差值，也均在5%之内。检测结束</t>
+    <t>点火备用后，有火不再报警，可点火</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -5765,7 +5778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5979,6 +5992,9 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5997,13 +6013,28 @@
     <xf numFmtId="0" fontId="31" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6027,54 +6058,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 4 2" xfId="1" xr:uid="{C97CC49E-8548-40A7-B373-8E3F8F01BD97}"/>
   </cellStyles>
-  <dxfs count="69">
+  <dxfs count="66">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -6099,29 +6100,8 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -6134,12 +6114,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -6232,33 +6206,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -6271,6 +6218,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -7795,70 +7744,70 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF667D90-1EB1-4976-A8D5-70F378E47508}" name="表1" displayName="表1" ref="A1:F445" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF667D90-1EB1-4976-A8D5-70F378E47508}" name="表1" displayName="表1" ref="A1:F445" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62">
   <autoFilter ref="A1:F445" xr:uid="{EAEC5D8C-41E3-481D-8A3D-D139585DF349}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F445">
     <sortCondition ref="B1:B445"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="存储区" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="排序" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="符号" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="地址" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="注释" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="停电保持" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="存储区" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="排序" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="符号" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="地址" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="注释" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="停电保持" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BC6A3F09-E86C-49A8-B91A-E1B95FD203B0}" name="表8" displayName="表8" ref="A1:F23" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BC6A3F09-E86C-49A8-B91A-E1B95FD203B0}" name="表8" displayName="表8" ref="A1:F23" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52">
   <autoFilter ref="A1:F23" xr:uid="{31503A1A-3ED1-4869-9B93-C5ABFAC7625B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
     <sortCondition ref="A1:A21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="命名类型" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="名称" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="代码" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="存储区域" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="示例" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="说明" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="命名类型" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="名称" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="代码" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="存储区域" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="示例" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="说明" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G257" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{D9EB2FB0-C2BE-41FC-99FB-6CD331B6BC5E}" name="符号表" displayName="符号表" ref="A1:G257" totalsRowShown="0" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
   <autoFilter ref="A1:G257" xr:uid="{B3E6F695-5A5D-43F2-A4A9-C2D31569F3E9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G257">
     <sortCondition ref="A1:A257"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="存储区" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="排序" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="间隔校验" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="符号长度" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="符号" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="地址" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="注释" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6DC73BD-6F51-4BCF-84E1-56C5A6AFF38F}" name="表3" displayName="表3" ref="A1:C40" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6DC73BD-6F51-4BCF-84E1-56C5A6AFF38F}" name="表3" displayName="表3" ref="A1:C40" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="A1:C40" xr:uid="{B6DC73BD-6F51-4BCF-84E1-56C5A6AFF38F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
     <sortCondition ref="B1:B40"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C9EC5542-3176-4CF9-AACC-E9B37EB87292}" name="存储区" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{B8E7CB01-86AB-4B99-82DC-6E4AF1B67DCA}" name="地址" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{17BBCF5F-DF23-4029-9CA9-3FFC00CBE4FD}" name="差值" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{C9EC5542-3176-4CF9-AACC-E9B37EB87292}" name="存储区" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{B8E7CB01-86AB-4B99-82DC-6E4AF1B67DCA}" name="地址" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{17BBCF5F-DF23-4029-9CA9-3FFC00CBE4FD}" name="差值" dataDxfId="30">
       <calculatedColumnFormula>B2-N(B1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7867,49 +7816,48 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{03BE1E8C-8A27-4BF2-B5AD-7C3831A87FC9}" name="表37" displayName="表37" ref="A1:F21" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:F21" xr:uid="{E517E8B6-ADC0-4F95-930E-5AF82CCFF0B4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="现场设备" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="地址" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="映射" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="符号" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="类型" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="备注" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{819FCED7-92C0-4647-B4B4-EBF1A26CEDAE}" name="表46" displayName="表46" ref="B1:H17" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{819FCED7-92C0-4647-B4B4-EBF1A26CEDAE}" name="表46" displayName="表46" ref="B1:H17" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17">
   <autoFilter ref="B1:H17" xr:uid="{94000AEE-EA2C-4D0D-8C4C-2ABB18A8C2A9}"/>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="从站 HoldStar=500" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="符号" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="从站 HoldStar=1500" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="注释" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Modbus主站地址" dataDxfId="14"/>
-    <tableColumn id="1" xr3:uid="{BFEA06D1-5376-4D08-897B-7DC31E55C531}" name="数据类型" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="备注" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="从站 HoldStar=500" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="符号" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="从站 HoldStar=1500" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="注释" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Modbus主站地址" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{BFEA06D1-5376-4D08-897B-7DC31E55C531}" name="数据类型" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="备注" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}" name="表2" displayName="表2" ref="A1:G21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G21" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}"/>
-  <tableColumns count="7">
-    <tableColumn id="6" xr3:uid="{3CBECB6D-4D10-48D8-8796-E40255F9A9C5}" name="序号" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}" name="表2" displayName="表2" ref="A1:F19" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7">
+  <autoFilter ref="A1:F19" xr:uid="{28DDED1F-1C4B-4D84-8FD0-826AE3C701E6}"/>
+  <tableColumns count="6">
+    <tableColumn id="6" xr3:uid="{3CBECB6D-4D10-48D8-8796-E40255F9A9C5}" name="序号" dataDxfId="5">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{092C8F4C-750F-4A54-9775-0E878E7F692D}" name="测试类别" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{55E7343C-005A-47DD-BF51-A98FEB8687FA}" name="项目" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{E219FFED-DB05-4801-BA8C-E5182B5E135C}" name="测试内容" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{37775F0D-5709-4D26-8B0D-3C61F165FF43}" name="预期结果" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{1DD79E4F-C3FB-4EA3-8CB8-5707D129384D}" name="实测结果" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{B06FFC10-5F8E-4C29-897A-DCDCD65BF95B}" name="备注" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{092C8F4C-750F-4A54-9775-0E878E7F692D}" name="测试类别" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{55E7343C-005A-47DD-BF51-A98FEB8687FA}" name="项目" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{E219FFED-DB05-4801-BA8C-E5182B5E135C}" name="测试内容" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{37775F0D-5709-4D26-8B0D-3C61F165FF43}" name="预期结果" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{1DD79E4F-C3FB-4EA3-8CB8-5707D129384D}" name="实测结果" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16523,11 +16471,11 @@
         <v>840</v>
       </c>
       <c r="F1" s="21"/>
-      <c r="G1" s="82" t="s">
-        <v>1594</v>
-      </c>
-      <c r="I1" s="82" t="s">
-        <v>1604</v>
+      <c r="G1" s="88" t="s">
+        <v>1596</v>
+      </c>
+      <c r="I1" s="88" t="s">
+        <v>1606</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -16543,11 +16491,11 @@
         <v>841</v>
       </c>
       <c r="F2" s="21"/>
-      <c r="G2" s="82" t="s">
-        <v>1596</v>
-      </c>
-      <c r="I2" s="82" t="s">
-        <v>1605</v>
+      <c r="G2" s="88" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I2" s="88" t="s">
+        <v>1607</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -16563,11 +16511,11 @@
         <v>842</v>
       </c>
       <c r="F3" s="21"/>
-      <c r="G3" s="82" t="s">
-        <v>1595</v>
-      </c>
-      <c r="I3" s="82" t="s">
-        <v>1606</v>
+      <c r="G3" s="88" t="s">
+        <v>1597</v>
+      </c>
+      <c r="I3" s="88" t="s">
+        <v>1608</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -16579,8 +16527,8 @@
         <v>849</v>
       </c>
       <c r="F4" s="21"/>
-      <c r="G4" s="82" t="s">
-        <v>1598</v>
+      <c r="G4" s="88" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -16592,8 +16540,8 @@
         <v>864</v>
       </c>
       <c r="F5" s="21"/>
-      <c r="G5" s="82" t="s">
-        <v>1601</v>
+      <c r="G5" s="88" t="s">
+        <v>1603</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -16605,8 +16553,8 @@
         <v>865</v>
       </c>
       <c r="F6" s="21"/>
-      <c r="G6" s="82" t="s">
-        <v>1600</v>
+      <c r="G6" s="88" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -16692,10 +16640,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="83" t="s">
         <v>834</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="83" t="s">
         <v>798</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -16710,10 +16658,10 @@
       <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="82" t="s">
         <v>833</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="82" t="s">
         <v>802</v>
       </c>
       <c r="C3" s="23" t="s">
@@ -17004,28 +16952,28 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23" t="s">
+      <c r="A22" s="82"/>
+      <c r="B22" s="82" t="s">
         <v>872</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="82" t="s">
         <v>873</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
     </row>
     <row r="23" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26" t="s">
+      <c r="A23" s="84"/>
+      <c r="B23" s="84" t="s">
         <v>874</v>
       </c>
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="85" t="s">
         <v>875</v>
       </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -17401,13 +17349,13 @@
         <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24.95" customHeight="1">
@@ -17425,13 +17373,13 @@
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24.95" customHeight="1">
@@ -17449,13 +17397,13 @@
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24.95" customHeight="1">
@@ -17473,13 +17421,13 @@
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24.95" customHeight="1">
@@ -17503,7 +17451,7 @@
         <v>1108</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24.95" customHeight="1">
@@ -17929,13 +17877,13 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24.95" customHeight="1">
@@ -18313,13 +18261,13 @@
         <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>749</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="24.95" customHeight="1">
@@ -18361,13 +18309,13 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>207</v>
       </c>
       <c r="G55" s="25" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="24.95" customHeight="1">
@@ -18385,13 +18333,13 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>211</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="24.95" customHeight="1">
@@ -18409,13 +18357,13 @@
         <v>16</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="24.95" customHeight="1">
@@ -18433,13 +18381,13 @@
         <v>21</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>219</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="24.95" customHeight="1">
@@ -18697,7 +18645,7 @@
         <v>14</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>375</v>
@@ -18745,7 +18693,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>379</v>
@@ -18913,13 +18861,13 @@
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>390</v>
       </c>
       <c r="G78" s="33" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="24.95" customHeight="1">
@@ -19087,7 +19035,7 @@
         <v>40</v>
       </c>
       <c r="G85" s="25" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="24.95" customHeight="1">
@@ -19441,13 +19389,13 @@
         <v>17</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="F100" s="54" t="s">
         <v>156</v>
       </c>
       <c r="G100" s="59" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="24.95" customHeight="1">
@@ -19465,13 +19413,13 @@
         <v>22</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="F101" s="54" t="s">
         <v>160</v>
       </c>
       <c r="G101" s="59" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="24.95" customHeight="1">
@@ -19489,13 +19437,13 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="F102" s="54" t="s">
         <v>164</v>
       </c>
       <c r="G102" s="59" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="24.95" customHeight="1">
@@ -20353,13 +20301,13 @@
         <v>22</v>
       </c>
       <c r="E137" s="38" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="G137" s="25" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="24.95" customHeight="1">
@@ -20871,13 +20819,13 @@
         <v>20</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="24.95" customHeight="1">
@@ -20897,13 +20845,13 @@
         <v>20</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="G158" s="25" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="24.95" customHeight="1">
@@ -20923,13 +20871,13 @@
         <v>20</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="G159" s="25" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="24.95" customHeight="1">
@@ -22377,13 +22325,13 @@
         <v>20</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="G217" s="25" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="24.95" customHeight="1">
@@ -22452,10 +22400,10 @@
         <v>1176</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="G220" s="25" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="24.95" customHeight="1">
@@ -22479,7 +22427,7 @@
         <v>1381</v>
       </c>
       <c r="G221" s="25" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="24.95" customHeight="1">
@@ -22503,7 +22451,7 @@
         <v>1383</v>
       </c>
       <c r="G222" s="25" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="24.95" customHeight="1">
@@ -22761,13 +22709,13 @@
         <v>21</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="G233" s="33" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="24.95" customHeight="1">
@@ -22785,13 +22733,13 @@
         <v>13</v>
       </c>
       <c r="E234" s="66" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G234" s="65" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="24.95" customHeight="1">
@@ -22809,13 +22757,13 @@
         <v>14</v>
       </c>
       <c r="E235" s="14" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="F235" s="14" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="G235" s="67" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="24.95" customHeight="1">
@@ -22833,13 +22781,13 @@
         <v>15</v>
       </c>
       <c r="E236" s="14" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="F236" s="14" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="G236" s="37" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="24.95" customHeight="1">
@@ -22857,13 +22805,13 @@
         <v>23</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="G237" s="25" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="24.95" customHeight="1">
@@ -22881,13 +22829,13 @@
         <v>23</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="G238" s="25" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="24.95" customHeight="1">
@@ -23265,13 +23213,13 @@
         <v>12</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="G254" s="71" t="s">
-        <v>1588</v>
+      <c r="G254" s="72" t="s">
+        <v>1590</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="24.95" customHeight="1">
@@ -23289,7 +23237,7 @@
         <v>17</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>1473</v>
@@ -23313,7 +23261,7 @@
         <v>17</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>1294</v>
@@ -23337,13 +23285,13 @@
         <v>18</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>1397</v>
       </c>
       <c r="G257" s="25" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
   </sheetData>
@@ -23383,35 +23331,35 @@
   <sheetData>
     <row r="1" spans="1:15" ht="24.95" customHeight="1">
       <c r="A1" s="70" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B1" s="70" t="s">
         <v>1591</v>
       </c>
-      <c r="B1" s="70" t="s">
-        <v>1589</v>
-      </c>
       <c r="C1" s="70" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="I1" s="60" t="str">
         <f t="array" ref="I1">LEFT(N1, MIN(FIND({0,1,2,3,4,5,6,7,8,9}, N1 &amp; "0123456789")) - 1)</f>
         <v>VW</v>
       </c>
-      <c r="J1" s="75">
+      <c r="J1" s="76">
         <f>VALUE(RIGHT(N1,LEN(N1)-LEN(I1)))</f>
         <v>814</v>
       </c>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75">
+      <c r="K1" s="76"/>
+      <c r="L1" s="76">
         <f>LEN(M1)</f>
         <v>12</v>
       </c>
-      <c r="M1" s="74" t="s">
-        <v>1583</v>
-      </c>
-      <c r="N1" s="74" t="s">
+      <c r="M1" s="75" t="s">
+        <v>1585</v>
+      </c>
+      <c r="N1" s="75" t="s">
         <v>1472</v>
       </c>
-      <c r="O1" s="76" t="s">
-        <v>1588</v>
+      <c r="O1" s="77" t="s">
+        <v>1590</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24.95" customHeight="1">
@@ -23990,7 +23938,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.95" customHeight="1">
+    <row r="5" spans="1:6" ht="14.25">
       <c r="A5" s="42" t="s">
         <v>1331</v>
       </c>
@@ -24309,11 +24257,7 @@
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C
-&amp;A</oddHeader>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -24339,25 +24283,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" s="50" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="86" t="s">
         <v>1343</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="86" t="s">
         <v>536</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="86" t="s">
         <v>1345</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="86" t="s">
         <v>523</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="86" t="s">
         <v>1344</v>
       </c>
-      <c r="G1" s="80" t="s">
-        <v>1593</v>
-      </c>
-      <c r="H1" s="80" t="s">
+      <c r="G1" s="86" t="s">
+        <v>1595</v>
+      </c>
+      <c r="H1" s="86" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -24377,8 +24321,8 @@
       <c r="F2" s="53">
         <v>40061.08</v>
       </c>
-      <c r="G2" s="81" t="s">
-        <v>1602</v>
+      <c r="G2" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H2" s="54" t="s">
         <v>1394</v>
@@ -24400,8 +24344,8 @@
       <c r="F3" s="53">
         <v>40061.089999999997</v>
       </c>
-      <c r="G3" s="81" t="s">
-        <v>1602</v>
+      <c r="G3" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H3" s="54" t="s">
         <v>1394</v>
@@ -24423,8 +24367,8 @@
       <c r="F4" s="58">
         <v>40061.1</v>
       </c>
-      <c r="G4" s="83" t="s">
-        <v>1602</v>
+      <c r="G4" s="89" t="s">
+        <v>1604</v>
       </c>
       <c r="H4" s="54" t="s">
         <v>1394</v>
@@ -24446,8 +24390,8 @@
       <c r="F5" s="53">
         <v>40061.109999999986</v>
       </c>
-      <c r="G5" s="81" t="s">
-        <v>1602</v>
+      <c r="G5" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H5" s="54" t="s">
         <v>1394</v>
@@ -24469,8 +24413,8 @@
       <c r="F6" s="53">
         <v>40061.119999999981</v>
       </c>
-      <c r="G6" s="81" t="s">
-        <v>1602</v>
+      <c r="G6" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H6" s="54" t="s">
         <v>1394</v>
@@ -24492,8 +24436,8 @@
       <c r="F7" s="53">
         <v>40061.129999999976</v>
       </c>
-      <c r="G7" s="81" t="s">
-        <v>1602</v>
+      <c r="G7" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H7" s="54" t="s">
         <v>1395</v>
@@ -24515,8 +24459,8 @@
       <c r="F8" s="53">
         <v>40061.13999999997</v>
       </c>
-      <c r="G8" s="81" t="s">
-        <v>1602</v>
+      <c r="G8" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H8" s="54" t="s">
         <v>1395</v>
@@ -24538,8 +24482,8 @@
       <c r="F9" s="53">
         <v>40061.149999999965</v>
       </c>
-      <c r="G9" s="81" t="s">
-        <v>1602</v>
+      <c r="G9" s="87" t="s">
+        <v>1604</v>
       </c>
       <c r="H9" s="54" t="s">
         <v>1395</v>
@@ -24561,8 +24505,8 @@
       <c r="F10" s="56">
         <v>40061</v>
       </c>
-      <c r="G10" s="84" t="s">
-        <v>1602</v>
+      <c r="G10" s="90" t="s">
+        <v>1604</v>
       </c>
       <c r="H10" s="54" t="s">
         <v>1395</v>
@@ -24584,8 +24528,8 @@
       <c r="F11" s="55">
         <v>40061.1</v>
       </c>
-      <c r="G11" s="85" t="s">
-        <v>1602</v>
+      <c r="G11" s="91" t="s">
+        <v>1604</v>
       </c>
       <c r="H11" s="54" t="s">
         <v>1395</v>
@@ -24608,7 +24552,7 @@
         <v>40071</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="H12" s="54" t="s">
         <v>1394</v>
@@ -24631,7 +24575,7 @@
         <v>40073</v>
       </c>
       <c r="G13" s="55" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="H13" s="54" t="s">
         <v>1394</v>
@@ -24654,7 +24598,7 @@
         <v>40077</v>
       </c>
       <c r="G14" s="55" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="H14" s="54" t="s">
         <v>1394</v>
@@ -24664,7 +24608,7 @@
       <c r="B15" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="78" t="s">
         <v>1391</v>
       </c>
       <c r="D15" s="54" t="s">
@@ -24677,9 +24621,9 @@
         <v>40191</v>
       </c>
       <c r="G15" s="55" t="s">
-        <v>1599</v>
-      </c>
-      <c r="H15" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="H15" s="78" t="s">
         <v>1394</v>
       </c>
     </row>
@@ -24699,7 +24643,7 @@
         <v>40200</v>
       </c>
       <c r="G16" s="55" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="H16" s="54" t="s">
         <v>1393</v>
@@ -24721,7 +24665,7 @@
         <v>40210</v>
       </c>
       <c r="G17" s="55" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="H17" s="54" t="s">
         <v>1393</v>
@@ -24750,534 +24694,464 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8628761D-8897-4103-9A07-B5EE77259803}">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="2" defaultRowHeight="24.95" customHeight="1"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="38.125" style="34" customWidth="1"/>
-    <col min="5" max="5" width="34.625" style="34" customWidth="1"/>
-    <col min="6" max="6" width="21" style="73" customWidth="1"/>
-    <col min="7" max="7" width="45.75" style="2" customWidth="1"/>
-    <col min="8" max="54" width="5.625" style="2" customWidth="1"/>
-    <col min="55" max="16384" width="2" style="2"/>
+    <col min="1" max="1" width="6.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="5" width="35.625" style="34" customWidth="1"/>
+    <col min="6" max="6" width="26" style="74" customWidth="1"/>
+    <col min="7" max="7" width="16.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="12" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="34" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A1" s="89" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B1" s="90" t="s">
-        <v>1603</v>
-      </c>
-      <c r="C1" s="90" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" ht="35.1" customHeight="1">
+      <c r="A1" s="19" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E1" s="94" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="36" customFormat="1" ht="57">
+      <c r="A2" s="92">
+        <f t="shared" ref="A2:A19" si="0">ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="92" t="s">
         <v>1509</v>
       </c>
-      <c r="D1" s="90" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E1" s="91" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F1" s="92" t="s">
-        <v>1476</v>
-      </c>
-      <c r="G1" s="90" t="s">
-        <v>1628</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="36" customFormat="1" ht="57">
-      <c r="A2" s="93">
-        <f t="shared" ref="A2:A18" si="0">ROW()-1</f>
-        <v>1</v>
-      </c>
-      <c r="B2" s="86" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="79" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F2" s="92" t="s">
         <v>1611</v>
       </c>
-      <c r="D2" s="77" t="s">
-        <v>1610</v>
-      </c>
-      <c r="E2" s="77" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F2" s="94" t="s">
-        <v>1609</v>
-      </c>
-      <c r="G2" s="99" t="s">
-        <v>1629</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="57">
-      <c r="A3" s="64">
+      <c r="I2" s="81"/>
+    </row>
+    <row r="3" spans="1:10" ht="57">
+      <c r="A3" s="66">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" s="66" t="s">
         <v>1478</v>
       </c>
-      <c r="C3" s="77" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E3" s="77" t="s">
+      <c r="C3" s="79" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>1614</v>
       </c>
-      <c r="F3" s="95" t="s">
-        <v>1608</v>
-      </c>
-      <c r="G3" s="69"/>
-    </row>
-    <row r="4" spans="1:7" ht="114">
-      <c r="A4" s="96">
+      <c r="E3" s="79" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F3" s="93" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I3" s="80"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="85.5">
+      <c r="A4" s="68">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="68" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>1613</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>1630</v>
-      </c>
-      <c r="E4" s="77" t="s">
-        <v>1616</v>
-      </c>
-      <c r="F4" s="88" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C4" s="79" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D4" s="79" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E4" s="79" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F4" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G4" s="69"/>
-    </row>
-    <row r="5" spans="1:7" ht="128.25">
-      <c r="A5" s="97">
+      <c r="I4" s="34"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="114">
+      <c r="A5" s="69">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="69" t="s">
         <v>1478</v>
       </c>
-      <c r="C5" s="77" t="s">
-        <v>1613</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>1617</v>
-      </c>
-      <c r="E5" s="77" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F5" s="88" t="s">
+      <c r="C5" s="79" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D5" s="79" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E5" s="79" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F5" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G5" s="86"/>
-    </row>
-    <row r="6" spans="1:7" ht="42.75">
-      <c r="A6" s="96">
-        <f t="shared" si="0"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="28.5">
+      <c r="A6" s="69">
+        <f>ROW()-1</f>
         <v>5</v>
       </c>
-      <c r="B6" s="68" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D6" s="77" t="s">
-        <v>1620</v>
-      </c>
-      <c r="E6" s="77" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F6" s="88" t="s">
-        <v>1477</v>
-      </c>
-      <c r="G6" s="69"/>
-    </row>
-    <row r="7" spans="1:7" ht="42.75">
-      <c r="A7" s="64">
-        <f t="shared" si="0"/>
+      <c r="B6" s="69" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C6" s="79" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D6" s="79" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E6" s="79" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F6" s="92" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="42.75">
+      <c r="A7" s="96">
+        <f>ROW()-1</f>
         <v>6</v>
       </c>
-      <c r="B7" s="66" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>1480</v>
-      </c>
-      <c r="D7" s="77" t="s">
-        <v>1621</v>
-      </c>
-      <c r="E7" s="77" t="s">
-        <v>1622</v>
-      </c>
-      <c r="F7" s="88" t="s">
-        <v>1477</v>
-      </c>
-      <c r="G7" s="69"/>
-    </row>
-    <row r="8" spans="1:7" ht="28.5">
-      <c r="A8" s="64">
+      <c r="B7" s="69" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D7" s="79" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E7" s="79" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F7" s="92" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I7" s="34"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="42.75">
+      <c r="A8" s="68">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="66" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>1481</v>
-      </c>
-      <c r="E8" s="72" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F8" s="88" t="s">
-        <v>1477</v>
-      </c>
-      <c r="G8" s="69"/>
-    </row>
-    <row r="9" spans="1:7" ht="42.75">
-      <c r="A9" s="64">
+      <c r="B8" s="68" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D8" s="79" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E8" s="79" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F8" s="95" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I8" s="34"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="42.75">
+      <c r="A9" s="66">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>220</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>1483</v>
-      </c>
-      <c r="E9" s="72" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F9" s="88" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E9" s="79" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F9" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G9" s="69"/>
-    </row>
-    <row r="10" spans="1:7" ht="28.5">
-      <c r="A10" s="64">
+      <c r="I9" s="34"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="28.5">
+      <c r="A10" s="66">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D10" s="72" t="s">
-        <v>1486</v>
-      </c>
-      <c r="E10" s="72" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F10" s="88" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F10" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G10" s="69"/>
-    </row>
-    <row r="11" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A11" s="64">
+      <c r="I10" s="34"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="42.75">
+      <c r="A11" s="66">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C11" s="72" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>1489</v>
-      </c>
-      <c r="E11" s="72" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F11" s="88" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F11" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G11" s="69"/>
-    </row>
-    <row r="12" spans="1:7" ht="42.75">
-      <c r="A12" s="64">
+      <c r="I11" s="34"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.5">
+      <c r="A12" s="66">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D12" s="72" t="s">
-        <v>1491</v>
-      </c>
-      <c r="E12" s="77" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F12" s="88" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D12" s="73" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E12" s="73" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F12" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G12" s="69"/>
-    </row>
-    <row r="13" spans="1:7" ht="28.5">
-      <c r="A13" s="64">
-        <f>ROW()-1</f>
+      <c r="I12" s="34"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="24.95" customHeight="1">
+      <c r="A13" s="66">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>1624</v>
-      </c>
-      <c r="D13" s="77" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E13" s="77" t="s">
-        <v>1626</v>
-      </c>
-      <c r="F13" s="88" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D13" s="73" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E13" s="73" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F13" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G13" s="69"/>
-    </row>
-    <row r="14" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A14" s="64">
+      <c r="I13" s="34"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.25">
+      <c r="A14" s="66">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C14" s="72" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D14" s="73" t="s">
         <v>1492</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="E14" s="73" t="s">
         <v>1493</v>
       </c>
-      <c r="E14" s="72" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G14" s="69"/>
-    </row>
-    <row r="15" spans="1:7" ht="28.5">
-      <c r="A15" s="64">
+      <c r="I14" s="34"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="24.95" customHeight="1">
+      <c r="A15" s="66">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C15" s="72" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D15" s="73" t="s">
         <v>1495</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="E15" s="73" t="s">
         <v>1496</v>
       </c>
-      <c r="E15" s="72" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F15" s="88" t="s">
+      <c r="F15" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G15" s="69"/>
-    </row>
-    <row r="16" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A16" s="64">
+      <c r="I15" s="34"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="28.5">
+      <c r="A16" s="66">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C16" s="72" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D16" s="73" t="s">
         <v>1498</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="E16" s="73" t="s">
         <v>1499</v>
       </c>
-      <c r="E16" s="72" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G16" s="69"/>
-    </row>
-    <row r="17" spans="1:7" ht="71.25">
-      <c r="A17" s="64">
+      <c r="I16" s="34"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="24.95" customHeight="1">
+      <c r="A17" s="66">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C17" s="72" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D17" s="73" t="s">
         <v>1501</v>
       </c>
-      <c r="D17" s="71" t="s">
-        <v>1505</v>
-      </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="73" t="s">
         <v>1502</v>
       </c>
-      <c r="F17" s="88" t="s">
+      <c r="F17" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G17" s="69"/>
-    </row>
-    <row r="18" spans="1:7" ht="28.5">
-      <c r="A18" s="64">
+      <c r="I17" s="34"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="71.25">
+      <c r="A18" s="66">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="66" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D18" s="72" t="s">
         <v>1507</v>
       </c>
-      <c r="C18" s="72" t="s">
-        <v>1503</v>
-      </c>
-      <c r="D18" s="71" t="s">
+      <c r="E18" s="73" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F18" s="69" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.5">
+      <c r="A19" s="66">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D19" s="72" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E19" s="73" t="s">
         <v>1506</v>
       </c>
-      <c r="E18" s="72" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F18" s="88" t="s">
+      <c r="F19" s="69" t="s">
         <v>1477</v>
       </c>
-      <c r="G18" s="69"/>
-    </row>
-    <row r="19" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A19" s="87">
-        <f t="shared" ref="A19:A21" si="1">ROW()-1</f>
-        <v>18</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="69"/>
-    </row>
-    <row r="20" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A20" s="5">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-    </row>
-    <row r="21" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A21" s="5">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="100"/>
-    </row>
-    <row r="22" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A22" s="36"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="98"/>
-    </row>
-    <row r="23" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A23" s="36"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="98"/>
-    </row>
-    <row r="24" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A24" s="36"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="98"/>
-    </row>
-    <row r="25" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="98"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="98"/>
-    </row>
-    <row r="26" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A26" s="36"/>
-      <c r="B26" s="98"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="98"/>
-    </row>
-    <row r="27" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A27" s="36"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="98"/>
-    </row>
-    <row r="28" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A28" s="36"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="98"/>
-    </row>
-    <row r="29" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A29" s="36"/>
-      <c r="B29" s="98"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="98"/>
-    </row>
-    <row r="30" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A30" s="36"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="98"/>
-    </row>
-    <row r="31" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A31" s="36"/>
-      <c r="B31" s="98"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="98"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="24.95" customHeight="1">
+      <c r="A20" s="71"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="G20" s="71"/>
+    </row>
+    <row r="21" spans="1:10" ht="24.95" customHeight="1">
+      <c r="C21" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:F3">
@@ -25285,12 +25159,7 @@
   </sortState>
   <phoneticPr fontId="30" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="62" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;L
-日期：&amp;U                 &amp;C
-&amp;A</oddHeader>
-  </headerFooter>
+  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
+++ b/burnerController_JXXY/20260330_烧嘴控制改造程序-点表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\02-PLC项目\江西沸腾炉烧嘴程序改造\burnerController_JXXY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE9DBC6-9712-4257-93B7-D59F20064349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467F2F4F-A9F9-42D9-9866-89C658CFB9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="622" activeTab="7" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="622" activeTab="6" xr2:uid="{2BCBB78C-AFBE-4F13-8C2E-200396EF23E4}"/>
   </bookViews>
   <sheets>
     <sheet name="端子1-原始" sheetId="1" r:id="rId1"/>
@@ -5778,7 +5778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6069,6 +6069,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24271,18 +24277,18 @@
   <cols>
     <col min="1" max="1" width="4.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.5" style="2" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="23.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.875" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="28" style="2" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="19.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="28.25" style="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" customWidth="1"/>
+    <col min="7" max="7" width="18.375" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="57" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="50" customFormat="1" ht="35.1" customHeight="1">
+    <row r="1" spans="2:8" s="50" customFormat="1" ht="40.5">
       <c r="B1" s="86" t="s">
         <v>1343</v>
       </c>
@@ -24295,7 +24301,7 @@
       <c r="E1" s="86" t="s">
         <v>523</v>
       </c>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="98" t="s">
         <v>1344</v>
       </c>
       <c r="G1" s="86" t="s">
@@ -24627,7 +24633,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="24.95" customHeight="1">
+    <row r="16" spans="2:8" ht="28.5">
       <c r="B16" s="54"/>
       <c r="C16" s="54" t="s">
         <v>1362</v>
@@ -24645,11 +24651,11 @@
       <c r="G16" s="55" t="s">
         <v>1599</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="97" t="s">
         <v>1393</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="24.95" customHeight="1">
+    <row r="17" spans="2:8" ht="28.5">
       <c r="B17" s="54"/>
       <c r="C17" s="54" t="s">
         <v>1396</v>
@@ -24667,15 +24673,16 @@
       <c r="G17" s="55" t="s">
         <v>1599</v>
       </c>
-      <c r="H17" s="54" t="s">
+      <c r="H17" s="97" t="s">
         <v>1393</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
